--- a/result.xlsx
+++ b/result.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U145"/>
+  <dimension ref="A1:U119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -613,17 +613,17 @@
       </c>
       <c r="M2" s="1" t="inlineStr">
         <is>
-          <t>침입의 방지, 보안, 그리고 미관상의 목적으로 설치한다.</t>
+          <t> 가설울타리 가설울타리는 현장의 주위를 둘러싸는 담장을 말하며, 공사 범위를 명확히 하고 도난이나 침입의 방지, 보안, 그리고 미관상의 목적으로 설치한다.</t>
         </is>
       </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
-          <t>침입의 방지, 보안, 그리고 미관상의 목적으로 설치한다.</t>
+          <t> 가설울타리 가설울타리는 현장의 주위를 둘러싸는 담장을 말하며, 공사 범위를 명확히 하고 도난이나 침입의 방지, 보안, 그리고 미관상의 목적으로 설치한다.</t>
         </is>
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>침입의 방지, 보안, 그리고 미관상의 목적으로 설치한다.</t>
+          <t> 가설울타리 가설울타리는 현장의 주위를 둘러싸는 담장을 말하며, 공사 범위를 명확히 하고 도난이나 침입의 방지, 보안, 그리고 미관상의 목적으로 설치한다.</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr">
@@ -702,17 +702,17 @@
       </c>
       <c r="M3" s="1" t="inlineStr">
         <is>
-          <t>철망 등을 사용할 수 있으나 최근에는 EGI 자재를 가장 많이 사용한다.</t>
+          <t>가설울타리용 자재로는 합판, 철판, 철망 등을 사용할 수 있으나 최근에는 EGI 자재를 가장 많이 사용한다.</t>
         </is>
       </c>
       <c r="N3" s="1" t="inlineStr">
         <is>
-          <t>철망 등을 사용할 수 있으나 최근에는 EGI 자재를 가장 많이 사용한다.</t>
+          <t>가설울타리용 자재로는 합판, 철판, 철망 등을 사용할 수 있으나 최근에는 EGI 자재를 가장 많이 사용한다.</t>
         </is>
       </c>
       <c r="O3" s="1" t="inlineStr">
         <is>
-          <t>철망 등을 사용할 수 있으나 최근에는 EGI 자재를 가장 많이 사용한다.</t>
+          <t>가설울타리용 자재로는 합판, 철판, 철망 등을 사용할 수 있으나 최근에는 EGI 자재를 가장 많이 사용한다.</t>
         </is>
       </c>
       <c r="P3" s="1" t="inlineStr">
@@ -791,17 +791,17 @@
       </c>
       <c r="M4" s="1" t="inlineStr">
         <is>
-          <t>가설울타리의 높이는 1.</t>
+          <t>가설울타리의 높이는 1.8m 이상으로 하고, 야간에도 잘 보이도록 발광시설을 설치해야 하 며, 차량과 사람이 출입할 문을 두어 자물쇠를 채울 수 있게 한다.</t>
         </is>
       </c>
       <c r="N4" s="1" t="inlineStr">
         <is>
-          <t>가설울타리의 높이는 1.</t>
+          <t>가설울타리의 높이는 1.8m 이상으로 하고, 야간에도 잘 보이도록 발광시설을 설치해야 하 며, 차량과 사람이 출입할 문을 두어 자물쇠를 채울 수 있게 한다.</t>
         </is>
       </c>
       <c r="O4" s="1" t="inlineStr">
         <is>
-          <t>가설울타리의 높이는 1.</t>
+          <t>가설울타리의 높이는 1.8m 이상으로 하고, 야간에도 잘 보이도록 발광시설을 설치해야 하 며, 차량과 사람이 출입할 문을 두어 자물쇠를 채울 수 있게 한다.</t>
         </is>
       </c>
       <c r="P4" s="1" t="inlineStr">
@@ -880,22 +880,22 @@
       </c>
       <c r="M5" s="1" t="inlineStr">
         <is>
-          <t>며, 차량과 사람이 출입할 문을 두어 자물쇠를 채울 수 있게 한다.</t>
+          <t>다만, 공사장 부지 경계선 으로부터 50m 이내에 주거·상가건물이 있는 경우에는 높이 3m 이상으로 설치해야 한다.</t>
         </is>
       </c>
       <c r="N5" s="1" t="inlineStr">
         <is>
-          <t>며, 차량과 사람이 출입할 문을 두어 자물쇠를 채울 수 있게 한다.</t>
+          <t>다만, 공사장 부지 경계선 으로부터 50m 이내에 주거·상가건물이 있는 경우에는 높이 3m 이상으로 설치해야 한다.</t>
         </is>
       </c>
       <c r="O5" s="1" t="inlineStr">
         <is>
-          <t>며, 차량과 사람이 출입할 문을 두어 자물쇠를 채울 수 있게 한다.</t>
+          <t>다만, 공사장 부지 경계선 으로부터 50m 이내에 주거·상가건물이 있는 경우에는 높이 3m 이상으로 설치해야 한다.</t>
         </is>
       </c>
       <c r="P5" s="1" t="inlineStr">
         <is>
-          <t>특징</t>
+          <t>수치</t>
         </is>
       </c>
       <c r="Q5" s="1" t="inlineStr"/>
@@ -969,22 +969,22 @@
       </c>
       <c r="M6" s="1" t="inlineStr">
         <is>
-          <t>으로부터 50m 이내에 주거·상가건물이 있는 경우에는 높이 3m 이상으로 설치해야 한다.</t>
+          <t>가 설울타리는 다.</t>
         </is>
       </c>
       <c r="N6" s="1" t="inlineStr">
         <is>
-          <t>으로부터 50m 이내에 주거·상가건물이 있는 경우에는 높이 3m 이상으로 설치해야 한다.</t>
+          <t>가 설울타리는 다.</t>
         </is>
       </c>
       <c r="O6" s="1" t="inlineStr">
         <is>
-          <t>으로부터 50m 이내에 주거·상가건물이 있는 경우에는 높이 3m 이상으로 설치해야 한다.</t>
+          <t>가 설울타리는 다.</t>
         </is>
       </c>
       <c r="P6" s="1" t="inlineStr">
         <is>
-          <t>수치</t>
+          <t>특징</t>
         </is>
       </c>
       <c r="Q6" s="1" t="inlineStr"/>
@@ -1147,17 +1147,17 @@
       </c>
       <c r="M8" s="1" t="inlineStr">
         <is>
-          <t>벽을 설치해야 한다.</t>
+          <t>특히, 건설현장의 발파작업 및 공사장비 가동 시에는 공사소음을 저감할 수 있도록 가설방음 벽을 설치해야 한다.</t>
         </is>
       </c>
       <c r="N8" s="1" t="inlineStr">
         <is>
-          <t>벽을 설치해야 한다.</t>
+          <t>특히, 건설현장의 발파작업 및 공사장비 가동 시에는 공사소음을 저감할 수 있도록 가설방음 벽을 설치해야 한다.</t>
         </is>
       </c>
       <c r="O8" s="1" t="inlineStr">
         <is>
-          <t>벽을 설치해야 한다.</t>
+          <t>특히, 건설현장의 발파작업 및 공사장비 가동 시에는 공사소음을 저감할 수 있도록 가설방음 벽을 설치해야 한다.</t>
         </is>
       </c>
       <c r="P8" s="1" t="inlineStr">
@@ -1236,17 +1236,17 @@
       </c>
       <c r="M9" s="1" t="inlineStr">
         <is>
-          <t>는 가설방음벽을 설치하지 않을 수 있다.</t>
+          <t>다만, 건설현장의 공사소음이 인근 지역 등에 영향을 미치지 않는 경우에 는 가설방음벽을 설치하지 않을 수 있다.</t>
         </is>
       </c>
       <c r="N9" s="1" t="inlineStr">
         <is>
-          <t>는 가설방음벽을 설치하지 않을 수 있다.</t>
+          <t>다만, 건설현장의 공사소음이 인근 지역 등에 영향을 미치지 않는 경우에 는 가설방음벽을 설치하지 않을 수 있다.</t>
         </is>
       </c>
       <c r="O9" s="1" t="inlineStr">
         <is>
-          <t>는 가설방음벽을 설치하지 않을 수 있다.</t>
+          <t>다만, 건설현장의 공사소음이 인근 지역 등에 영향을 미치지 않는 경우에 는 가설방음벽을 설치하지 않을 수 있다.</t>
         </is>
       </c>
       <c r="P9" s="1" t="inlineStr">
@@ -1325,17 +1325,17 @@
       </c>
       <c r="M10" s="1" t="inlineStr">
         <is>
-          <t>설치한다.</t>
+          <t>가설방음벽의 설치위치 및 높이는 수음점의 위치와 소음 발생량에 따 라 결정되므로 현 장 여건을 고려해 설치한다.</t>
         </is>
       </c>
       <c r="N10" s="1" t="inlineStr">
         <is>
-          <t>설치한다.</t>
+          <t>가설방음벽의 설치위치 및 높이는 수음점의 위치와 소음 발생량에 따 라 결정되므로 현 장 여건을 고려해 설치한다.</t>
         </is>
       </c>
       <c r="O10" s="1" t="inlineStr">
         <is>
-          <t>설치한다.</t>
+          <t>가설방음벽의 설치위치 및 높이는 수음점의 위치와 소음 발생량에 따 라 결정되므로 현 장 여건을 고려해 설치한다.</t>
         </is>
       </c>
       <c r="P10" s="1" t="inlineStr">
@@ -1414,17 +1414,17 @@
       </c>
       <c r="M11" s="1" t="inlineStr">
         <is>
-          <t>를 결정해 설치한다.</t>
+          <t>가설울타리 출처 : www.kscnews.co.kr/  가설출입문 가설출입문은 현장에 작업 자 등과 같은 사람의 통행과 자재의 출입을 위해서 작업 동 선, 가설도로, 주변 도로와의 가설출입문 관계 등을 고려해 수량과 위치 를 결정해 설치한다.</t>
         </is>
       </c>
       <c r="N11" s="1" t="inlineStr">
         <is>
-          <t>를 결정해 설치한다.</t>
+          <t>가설울타리 출처 : www.kscnews.co.kr/  가설출입문 가설출입문은 현장에 작업 자 등과 같은 사람의 통행과 자재의 출입을 위해서 작업 동 선, 가설도로, 주변 도로와의 가설출입문 관계 등을 고려해 수량과 위치 를 결정해 설치한다.</t>
         </is>
       </c>
       <c r="O11" s="1" t="inlineStr">
         <is>
-          <t>를 결정해 설치한다.</t>
+          <t>가설울타리 출처 : www.kscnews.co.kr/  가설출입문 가설출입문은 현장에 작업 자 등과 같은 사람의 통행과 자재의 출입을 위해서 작업 동 선, 가설도로, 주변 도로와의 가설출입문 관계 등을 고려해 수량과 위치 를 결정해 설치한다.</t>
         </is>
       </c>
       <c r="P11" s="1" t="inlineStr">
@@ -1503,22 +1503,22 @@
       </c>
       <c r="M12" s="1" t="inlineStr">
         <is>
-          <t>식 문을 열어서 사용하며, 사람만 통행할 경우는 쪽문을 활용한다.</t>
+          <t>출입문은 접이식 문과 쪽문으로 구성되어서 차량 등이 통행할 때는 접이 식 문을 열어서 사용하며, 사람만 통행할 경우는 쪽문을 활용한다.</t>
         </is>
       </c>
       <c r="N12" s="1" t="inlineStr">
         <is>
-          <t>식 문을 열어서 사용하며, 사람만 통행할 경우는 쪽문을 활용한다.</t>
+          <t>출입문은 접이식 문과 쪽문으로 구성되어서 차량 등이 통행할 때는 접이 식 문을 열어서 사용하며, 사람만 통행할 경우는 쪽문을 활용한다.</t>
         </is>
       </c>
       <c r="O12" s="1" t="inlineStr">
         <is>
-          <t>식 문을 열어서 사용하며, 사람만 통행할 경우는 쪽문을 활용한다.</t>
+          <t>출입문은 접이식 문과 쪽문으로 구성되어서 차량 등이 통행할 때는 접이 식 문을 열어서 사용하며, 사람만 통행할 경우는 쪽문을 활용한다.</t>
         </is>
       </c>
       <c r="P12" s="1" t="inlineStr">
         <is>
-          <t>특징</t>
+          <t>분류</t>
         </is>
       </c>
       <c r="Q12" s="1" t="inlineStr"/>
@@ -1592,17 +1592,17 @@
       </c>
       <c r="M13" s="1" t="inlineStr">
         <is>
-          <t>너비로 하며 대개 6m 이상의 폭으로 한다.</t>
+          <t>이러한 출입문의 폭은 현장을 출입하게 될 차량의 크기와 차량의 통행에 방해가 되지 않는 너비로 하며 대개 6m 이상의 폭으로 한다.</t>
         </is>
       </c>
       <c r="N13" s="1" t="inlineStr">
         <is>
-          <t>너비로 하며 대개 6m 이상의 폭으로 한다.</t>
+          <t>이러한 출입문의 폭은 현장을 출입하게 될 차량의 크기와 차량의 통행에 방해가 되지 않는 너비로 하며 대개 6m 이상의 폭으로 한다.</t>
         </is>
       </c>
       <c r="O13" s="1" t="inlineStr">
         <is>
-          <t>너비로 하며 대개 6m 이상의 폭으로 한다.</t>
+          <t>이러한 출입문의 폭은 현장을 출입하게 될 차량의 크기와 차량의 통행에 방해가 되지 않는 너비로 하며 대개 6m 이상의 폭으로 한다.</t>
         </is>
       </c>
       <c r="P13" s="1" t="inlineStr">
@@ -1681,17 +1681,17 @@
       </c>
       <c r="M14" s="1" t="inlineStr">
         <is>
-          <t>휴게실 등이 부속되어 있다.</t>
+          <t>가설건물에는 현장사무소, 경비실, 실험실, 현장 내 식당, 창고 그리고 화장실 등이 해당된 다.</t>
         </is>
       </c>
       <c r="N14" s="1" t="inlineStr">
         <is>
-          <t>휴게실 등이 부속되어 있다.</t>
+          <t>가설건물에는 현장사무소, 경비실, 실험실, 현장 내 식당, 창고 그리고 화장실 등이 해당된 다.</t>
         </is>
       </c>
       <c r="O14" s="1" t="inlineStr">
         <is>
-          <t>휴게실 등이 부속되어 있다.</t>
+          <t>가설건물에는 현장사무소, 경비실, 실험실, 현장 내 식당, 창고 그리고 화장실 등이 해당된 다.</t>
         </is>
       </c>
       <c r="P14" s="1" t="inlineStr">
@@ -1770,22 +1770,22 @@
       </c>
       <c r="M15" s="1" t="inlineStr">
         <is>
-          <t>의 설치를 철저히 해서 취약한 가설건물의 안전시설과 인명 보호에 신중을 기해야 한다.</t>
+          <t>현장사무소에는 현장 감독을 위한 감독사무소, 감리를 위한 감리사무소, 현장 건설회사인 시공자를 위한 시공자 현장사무소, 그리고 협력업체 사무소 등으로 구분할 수 있으며 회의실, 휴게실 등이 부속되어 있다.</t>
         </is>
       </c>
       <c r="N15" s="1" t="inlineStr">
         <is>
-          <t>의 설치를 철저히 해서 취약한 가설건물의 안전시설과 인명 보호에 신중을 기해야 한다.</t>
+          <t>현장사무소에는 현장 감독을 위한 감독사무소, 감리를 위한 감리사무소, 현장 건설회사인 시공자를 위한 시공자 현장사무소, 그리고 협력업체 사무소 등으로 구분할 수 있으며 회의실, 휴게실 등이 부속되어 있다.</t>
         </is>
       </c>
       <c r="O15" s="1" t="inlineStr">
         <is>
-          <t>의 설치를 철저히 해서 취약한 가설건물의 안전시설과 인명 보호에 신중을 기해야 한다.</t>
+          <t>현장사무소에는 현장 감독을 위한 감독사무소, 감리를 위한 감리사무소, 현장 건설회사인 시공자를 위한 시공자 현장사무소, 그리고 협력업체 사무소 등으로 구분할 수 있으며 회의실, 휴게실 등이 부속되어 있다.</t>
         </is>
       </c>
       <c r="P15" s="1" t="inlineStr">
         <is>
-          <t>특징</t>
+          <t>분류</t>
         </is>
       </c>
       <c r="Q15" s="1" t="inlineStr"/>
@@ -1859,22 +1859,22 @@
       </c>
       <c r="M16" s="1" t="inlineStr">
         <is>
-          <t>물을 현장 내 설치하고 사용하기 위해서는 신고 절차를 거쳐야 한다.</t>
+          <t>특히 가설건물 중에서 사무소나 숙소는 소화설비나 누전차단기 등 의 설치를 철저히 해서 취약한 가설건물의 안전시설과 인명 보호에 신중을 기해야 한다.</t>
         </is>
       </c>
       <c r="N16" s="1" t="inlineStr">
         <is>
-          <t>물을 현장 내 설치하고 사용하기 위해서는 신고 절차를 거쳐야 한다.</t>
+          <t>특히 가설건물 중에서 사무소나 숙소는 소화설비나 누전차단기 등 의 설치를 철저히 해서 취약한 가설건물의 안전시설과 인명 보호에 신중을 기해야 한다.</t>
         </is>
       </c>
       <c r="O16" s="1" t="inlineStr">
         <is>
-          <t>물을 현장 내 설치하고 사용하기 위해서는 신고 절차를 거쳐야 한다.</t>
+          <t>특히 가설건물 중에서 사무소나 숙소는 소화설비나 누전차단기 등 의 설치를 철저히 해서 취약한 가설건물의 안전시설과 인명 보호에 신중을 기해야 한다.</t>
         </is>
       </c>
       <c r="P16" s="1" t="inlineStr">
         <is>
-          <t>순서</t>
+          <t>특징</t>
         </is>
       </c>
       <c r="Q16" s="1" t="inlineStr"/>
@@ -1948,22 +1948,22 @@
       </c>
       <c r="M17" s="1" t="inlineStr">
         <is>
-          <t>지 진입이 가능한 곳에 위치하도록 한다.</t>
+          <t>가설건 물을 현장 내 설치하고 사용하기 위해서는 신고 절차를 거쳐야 한다.  현장사무소 현장사무소의 위치는 가급적 현장 전체가 모두 시야에 들어오는 위치가 좋으며, 외부 방문 객 등의 출입을 고려해 출입문에서 가깝고, 본 공사가 진행되는 곳을 거치지 않고 사무소까 지 진입이 가능한 곳에 위치하도록 한다.</t>
         </is>
       </c>
       <c r="N17" s="1" t="inlineStr">
         <is>
-          <t>지 진입이 가능한 곳에 위치하도록 한다.</t>
+          <t>가설건 물을 현장 내 설치하고 사용하기 위해서는 신고 절차를 거쳐야 한다.  현장사무소 현장사무소의 위치는 가급적 현장 전체가 모두 시야에 들어오는 위치가 좋으며, 외부 방문 객 등의 출입을 고려해 출입문에서 가깝고, 본 공사가 진행되는 곳을 거치지 않고 사무소까 지 진입이 가능한 곳에 위치하도록 한다.</t>
         </is>
       </c>
       <c r="O17" s="1" t="inlineStr">
         <is>
-          <t>지 진입이 가능한 곳에 위치하도록 한다.</t>
+          <t>가설건 물을 현장 내 설치하고 사용하기 위해서는 신고 절차를 거쳐야 한다.  현장사무소 현장사무소의 위치는 가급적 현장 전체가 모두 시야에 들어오는 위치가 좋으며, 외부 방문 객 등의 출입을 고려해 출입문에서 가깝고, 본 공사가 진행되는 곳을 거치지 않고 사무소까 지 진입이 가능한 곳에 위치하도록 한다.</t>
         </is>
       </c>
       <c r="P17" s="1" t="inlineStr">
         <is>
-          <t>특징</t>
+          <t>순서</t>
         </is>
       </c>
       <c r="Q17" s="1" t="inlineStr"/>
@@ -2037,17 +2037,17 @@
       </c>
       <c r="M18" s="1" t="inlineStr">
         <is>
-          <t>널이나 컨테이너를 사용한다.</t>
+          <t>가설건물의 축조를 위한 자재는 경량 샌드위치 패 널이나 컨테이너를 사용한다.</t>
         </is>
       </c>
       <c r="N18" s="1" t="inlineStr">
         <is>
-          <t>널이나 컨테이너를 사용한다.</t>
+          <t>가설건물의 축조를 위한 자재는 경량 샌드위치 패 널이나 컨테이너를 사용한다.</t>
         </is>
       </c>
       <c r="O18" s="1" t="inlineStr">
         <is>
-          <t>널이나 컨테이너를 사용한다.</t>
+          <t>가설건물의 축조를 위한 자재는 경량 샌드위치 패 널이나 컨테이너를 사용한다.</t>
         </is>
       </c>
       <c r="P18" s="1" t="inlineStr">
@@ -2126,17 +2126,17 @@
       </c>
       <c r="M19" s="1" t="inlineStr">
         <is>
-          <t>사용한다.</t>
+          <t>최근에는 전용성이 높고 설치·해체가 용이한 컨테이너를 많이 사용한다.</t>
         </is>
       </c>
       <c r="N19" s="1" t="inlineStr">
         <is>
-          <t>사용한다.</t>
+          <t>최근에는 전용성이 높고 설치·해체가 용이한 컨테이너를 많이 사용한다.</t>
         </is>
       </c>
       <c r="O19" s="1" t="inlineStr">
         <is>
-          <t>사용한다.</t>
+          <t>최근에는 전용성이 높고 설치·해체가 용이한 컨테이너를 많이 사용한다.</t>
         </is>
       </c>
       <c r="P19" s="1" t="inlineStr">
@@ -2215,17 +2215,17 @@
       </c>
       <c r="M20" s="1" t="inlineStr">
         <is>
-          <t>최근에는 건설현장에 시멘트 창고를 설치하는 경우가 극히 드물다고 할 수 있다.</t>
+          <t>현장사무소 예  시멘트 창고 최근에는 건설현장에 시멘트 창고를 설치하는 경우가 극히 드물다고 할 수 있다.</t>
         </is>
       </c>
       <c r="N20" s="1" t="inlineStr">
         <is>
-          <t>최근에는 건설현장에 시멘트 창고를 설치하는 경우가 극히 드물다고 할 수 있다.</t>
+          <t>현장사무소 예  시멘트 창고 최근에는 건설현장에 시멘트 창고를 설치하는 경우가 극히 드물다고 할 수 있다.</t>
         </is>
       </c>
       <c r="O20" s="1" t="inlineStr">
         <is>
-          <t>최근에는 건설현장에 시멘트 창고를 설치하는 경우가 극히 드물다고 할 수 있다.</t>
+          <t>현장사무소 예  시멘트 창고 최근에는 건설현장에 시멘트 창고를 설치하는 경우가 극히 드물다고 할 수 있다.</t>
         </is>
       </c>
       <c r="P20" s="1" t="inlineStr">
@@ -2304,17 +2304,17 @@
       </c>
       <c r="M21" s="1" t="inlineStr">
         <is>
-          <t>중 흡습에 의한 시멘트 품질 저하를 방지하기 위해 방습을 가장 중요한 목적으로 한다.</t>
+          <t>그렇다고 하더라도 현장에서 사용하는 시멘트를 저장하기 위한 창고를 설치하는 경우 그 구조는 보관 중 흡습에 의한 시멘트 품질 저하를 방지하기 위해 방습을 가장 중요한 목적으로 한다.</t>
         </is>
       </c>
       <c r="N21" s="1" t="inlineStr">
         <is>
-          <t>중 흡습에 의한 시멘트 품질 저하를 방지하기 위해 방습을 가장 중요한 목적으로 한다.</t>
+          <t>그렇다고 하더라도 현장에서 사용하는 시멘트를 저장하기 위한 창고를 설치하는 경우 그 구조는 보관 중 흡습에 의한 시멘트 품질 저하를 방지하기 위해 방습을 가장 중요한 목적으로 한다.</t>
         </is>
       </c>
       <c r="O21" s="1" t="inlineStr">
         <is>
-          <t>중 흡습에 의한 시멘트 품질 저하를 방지하기 위해 방습을 가장 중요한 목적으로 한다.</t>
+          <t>그렇다고 하더라도 현장에서 사용하는 시멘트를 저장하기 위한 창고를 설치하는 경우 그 구조는 보관 중 흡습에 의한 시멘트 품질 저하를 방지하기 위해 방습을 가장 중요한 목적으로 한다.</t>
         </is>
       </c>
       <c r="P21" s="1" t="inlineStr">
@@ -2482,22 +2482,22 @@
       </c>
       <c r="M23" s="1" t="inlineStr">
         <is>
-          <t>설치해 물빠짐을 좋게 한다.</t>
+          <t>장기간 사용하 는 창고는 마루널 위 철판 깔기로 하고 바닥 높이는 30cm 이상으로 하며, 주위에는 배수구를 설치해 물빠짐을 좋게 한다.</t>
         </is>
       </c>
       <c r="N23" s="1" t="inlineStr">
         <is>
-          <t>설치해 물빠짐을 좋게 한다.</t>
+          <t>장기간 사용하 는 창고는 마루널 위 철판 깔기로 하고 바닥 높이는 30cm 이상으로 하며, 주위에는 배수구를 설치해 물빠짐을 좋게 한다.</t>
         </is>
       </c>
       <c r="O23" s="1" t="inlineStr">
         <is>
-          <t>설치해 물빠짐을 좋게 한다.</t>
+          <t>장기간 사용하 는 창고는 마루널 위 철판 깔기로 하고 바닥 높이는 30cm 이상으로 하며, 주위에는 배수구를 설치해 물빠짐을 좋게 한다.</t>
         </is>
       </c>
       <c r="P23" s="1" t="inlineStr">
         <is>
-          <t>특징</t>
+          <t>수치</t>
         </is>
       </c>
       <c r="Q23" s="1" t="inlineStr"/>
@@ -2571,17 +2571,17 @@
       </c>
       <c r="M24" s="1" t="inlineStr">
         <is>
-          <t>또한 벽에는 공기의 유통을 최소화하기 위해서 개구부를 될 수 있는 한 작게 한다.</t>
+          <t>벽은 널판 붙임으로 하고 장기간 사용하는 것은 함석붙이기로 한 다.</t>
         </is>
       </c>
       <c r="N24" s="1" t="inlineStr">
         <is>
-          <t>또한 벽에는 공기의 유통을 최소화하기 위해서 개구부를 될 수 있는 한 작게 한다.</t>
+          <t>벽은 널판 붙임으로 하고 장기간 사용하는 것은 함석붙이기로 한 다.</t>
         </is>
       </c>
       <c r="O24" s="1" t="inlineStr">
         <is>
-          <t>또한 벽에는 공기의 유통을 최소화하기 위해서 개구부를 될 수 있는 한 작게 한다.</t>
+          <t>벽은 널판 붙임으로 하고 장기간 사용하는 것은 함석붙이기로 한 다.</t>
         </is>
       </c>
       <c r="P24" s="1" t="inlineStr">
@@ -2660,17 +2660,17 @@
       </c>
       <c r="M25" s="1" t="inlineStr">
         <is>
-          <t>에 약 50포대를 적재한다.</t>
+          <t>또한 벽에는 공기의 유통을 최소화하기 위해서 개구부를 될 수 있는 한 작게 한다.</t>
         </is>
       </c>
       <c r="N25" s="1" t="inlineStr">
         <is>
-          <t>에 약 50포대를 적재한다.</t>
+          <t>또한 벽에는 공기의 유통을 최소화하기 위해서 개구부를 될 수 있는 한 작게 한다.</t>
         </is>
       </c>
       <c r="O25" s="1" t="inlineStr">
         <is>
-          <t>에 약 50포대를 적재한다.</t>
+          <t>또한 벽에는 공기의 유통을 최소화하기 위해서 개구부를 될 수 있는 한 작게 한다.</t>
         </is>
       </c>
       <c r="P25" s="1" t="inlineStr">
@@ -2749,17 +2749,17 @@
       </c>
       <c r="M26" s="1" t="inlineStr">
         <is>
-          <t>즉 창고의 크기는 대략 100포당 2~3m2로 하는 것이 바람직하다.</t>
+          <t>시멘트 창고에 시멘트를 보관할 때 시멘트 쌓기 높이는 13포대를 한도로 하고 바닥 면적 1m2 에 약 50포대를 적재한다.</t>
         </is>
       </c>
       <c r="N26" s="1" t="inlineStr">
         <is>
-          <t>즉 창고의 크기는 대략 100포당 2~3m2로 하는 것이 바람직하다.</t>
+          <t>시멘트 창고에 시멘트를 보관할 때 시멘트 쌓기 높이는 13포대를 한도로 하고 바닥 면적 1m2 에 약 50포대를 적재한다.</t>
         </is>
       </c>
       <c r="O26" s="1" t="inlineStr">
         <is>
-          <t>즉 창고의 크기는 대략 100포당 2~3m2로 하는 것이 바람직하다.</t>
+          <t>시멘트 창고에 시멘트를 보관할 때 시멘트 쌓기 높이는 13포대를 한도로 하고 바닥 면적 1m2 에 약 50포대를 적재한다.</t>
         </is>
       </c>
       <c r="P26" s="1" t="inlineStr">
@@ -2838,22 +2838,22 @@
       </c>
       <c r="M27" s="1" t="inlineStr">
         <is>
-          <t>건축적산기준에 의한 시멘트 창고의 면적은 다음 식을 사용해 산출한다.</t>
+          <t>즉 창고의 크기는 대략 100포당 2~3m2로 하는 것이 바람직하다.</t>
         </is>
       </c>
       <c r="N27" s="1" t="inlineStr">
         <is>
-          <t>건축적산기준에 의한 시멘트 창고의 면적은 다음 식을 사용해 산출한다.</t>
+          <t>즉 창고의 크기는 대략 100포당 2~3m2로 하는 것이 바람직하다.</t>
         </is>
       </c>
       <c r="O27" s="1" t="inlineStr">
         <is>
-          <t>건축적산기준에 의한 시멘트 창고의 면적은 다음 식을 사용해 산출한다.</t>
+          <t>즉 창고의 크기는 대략 100포당 2~3m2로 하는 것이 바람직하다.</t>
         </is>
       </c>
       <c r="P27" s="1" t="inlineStr">
         <is>
-          <t>특징</t>
+          <t>수치</t>
         </is>
       </c>
       <c r="Q27" s="1" t="inlineStr"/>
@@ -2927,17 +2927,17 @@
       </c>
       <c r="M28" s="1" t="inlineStr">
         <is>
-          <t>비, 그리고 인력을 갖추어야 한다.</t>
+          <t>건축적산기준에 의한 시멘트 창고의 면적은 다음 식을 사용해 산출한다.</t>
         </is>
       </c>
       <c r="N28" s="1" t="inlineStr">
         <is>
-          <t>비, 그리고 인력을 갖추어야 한다.</t>
+          <t>건축적산기준에 의한 시멘트 창고의 면적은 다음 식을 사용해 산출한다.</t>
         </is>
       </c>
       <c r="O28" s="1" t="inlineStr">
         <is>
-          <t>비, 그리고 인력을 갖추어야 한다.</t>
+          <t>건축적산기준에 의한 시멘트 창고의 면적은 다음 식을 사용해 산출한다.</t>
         </is>
       </c>
       <c r="P28" s="1" t="inlineStr">
@@ -3016,22 +3016,22 @@
       </c>
       <c r="M29" s="1" t="inlineStr">
         <is>
-          <t>실을 확보해야 한다.</t>
+          <t>여기서, N : 시멘트 저장량(포대) n : 높이 쌓기 단수(최고 13포대)  현장시험실 건설현장에는 건설기술 진흥법 기준에 적합하도록 관리시험을 실시할 수 있는 실험실, 장 비, 그리고 인력을 갖추어야 한다.</t>
         </is>
       </c>
       <c r="N29" s="1" t="inlineStr">
         <is>
-          <t>실을 확보해야 한다.</t>
+          <t>여기서, N : 시멘트 저장량(포대) n : 높이 쌓기 단수(최고 13포대)  현장시험실 건설현장에는 건설기술 진흥법 기준에 적합하도록 관리시험을 실시할 수 있는 실험실, 장 비, 그리고 인력을 갖추어야 한다.</t>
         </is>
       </c>
       <c r="O29" s="1" t="inlineStr">
         <is>
-          <t>실을 확보해야 한다.</t>
+          <t>여기서, N : 시멘트 저장량(포대) n : 높이 쌓기 단수(최고 13포대)  현장시험실 건설현장에는 건설기술 진흥법 기준에 적합하도록 관리시험을 실시할 수 있는 실험실, 장 비, 그리고 인력을 갖추어야 한다.</t>
         </is>
       </c>
       <c r="P29" s="1" t="inlineStr">
         <is>
-          <t>특징</t>
+          <t>수치</t>
         </is>
       </c>
       <c r="Q29" s="1" t="inlineStr"/>
@@ -3105,17 +3105,17 @@
       </c>
       <c r="M30" s="1" t="inlineStr">
         <is>
-          <t>시험 작업대 및 시험기기 등을 준비해야 한다.</t>
+          <t>따라서 이에 해당하는 현장의 적정 규모 이상의 품질실험 실을 확보해야 한다.</t>
         </is>
       </c>
       <c r="N30" s="1" t="inlineStr">
         <is>
-          <t>시험 작업대 및 시험기기 등을 준비해야 한다.</t>
+          <t>따라서 이에 해당하는 현장의 적정 규모 이상의 품질실험 실을 확보해야 한다.</t>
         </is>
       </c>
       <c r="O30" s="1" t="inlineStr">
         <is>
-          <t>시험 작업대 및 시험기기 등을 준비해야 한다.</t>
+          <t>따라서 이에 해당하는 현장의 적정 규모 이상의 품질실험 실을 확보해야 한다.</t>
         </is>
       </c>
       <c r="P30" s="1" t="inlineStr">
@@ -3179,32 +3179,32 @@
       </c>
       <c r="J31" s="1" t="inlineStr">
         <is>
-          <t>2.3.3</t>
+          <t>2.3.2</t>
         </is>
       </c>
       <c r="K31" s="1" t="inlineStr">
         <is>
-          <t>대지측량과 현황측량</t>
+          <t>가설건물</t>
         </is>
       </c>
       <c r="L31" s="1" t="inlineStr">
         <is>
-          <t>대지측량과 현황측량</t>
+          <t>가설건물</t>
         </is>
       </c>
       <c r="M31" s="1" t="inlineStr">
         <is>
-          <t>하고, 설계도면의 배치도와 실제 대지가 일치하는지 확인한다.</t>
+          <t>또한 현장시험에 필요한 시험실, 양식함, 시료 보관대, 공시체 양생수조, 시험 작업대 및 시험기기 등을 준비해야 한다.</t>
         </is>
       </c>
       <c r="N31" s="1" t="inlineStr">
         <is>
-          <t>하고, 설계도면의 배치도와 실제 대지가 일치하는지 확인한다.</t>
+          <t>또한 현장시험에 필요한 시험실, 양식함, 시료 보관대, 공시체 양생수조, 시험 작업대 및 시험기기 등을 준비해야 한다.</t>
         </is>
       </c>
       <c r="O31" s="1" t="inlineStr">
         <is>
-          <t>하고, 설계도면의 배치도와 실제 대지가 일치하는지 확인한다.</t>
+          <t>또한 현장시험에 필요한 시험실, 양식함, 시료 보관대, 공시체 양생수조, 시험 작업대 및 시험기기 등을 준비해야 한다.</t>
         </is>
       </c>
       <c r="P31" s="1" t="inlineStr">
@@ -3283,17 +3283,17 @@
       </c>
       <c r="M32" s="1" t="inlineStr">
         <is>
-          <t>으므로 신중을 기할 필요가 있다.</t>
+          <t> 경계측량 현장에서 공사를 수행하기에 앞서 공사대지에 대한 경계복원측량을 시행해 대지 경계를 명확히 하고, 설계도면의 배치도와 실제 대지가 일치하는지 확인한다.</t>
         </is>
       </c>
       <c r="N32" s="1" t="inlineStr">
         <is>
-          <t>으므로 신중을 기할 필요가 있다.</t>
+          <t> 경계측량 현장에서 공사를 수행하기에 앞서 공사대지에 대한 경계복원측량을 시행해 대지 경계를 명확히 하고, 설계도면의 배치도와 실제 대지가 일치하는지 확인한다.</t>
         </is>
       </c>
       <c r="O32" s="1" t="inlineStr">
         <is>
-          <t>으므로 신중을 기할 필요가 있다.</t>
+          <t> 경계측량 현장에서 공사를 수행하기에 앞서 공사대지에 대한 경계복원측량을 시행해 대지 경계를 명확히 하고, 설계도면의 배치도와 실제 대지가 일치하는지 확인한다.</t>
         </is>
       </c>
       <c r="P32" s="1" t="inlineStr">
@@ -3372,17 +3372,17 @@
       </c>
       <c r="M33" s="1" t="inlineStr">
         <is>
-          <t>당 공사의 건축주, 감독자, 건설사업관리자 등을 입회시켜 명확히 할 필요가 있다.</t>
+          <t>이는 공사 준공과 밀접한 관계가 있 으므로 신중을 기할 필요가 있다.</t>
         </is>
       </c>
       <c r="N33" s="1" t="inlineStr">
         <is>
-          <t>당 공사의 건축주, 감독자, 건설사업관리자 등을 입회시켜 명확히 할 필요가 있다.</t>
+          <t>이는 공사 준공과 밀접한 관계가 있 으므로 신중을 기할 필요가 있다.</t>
         </is>
       </c>
       <c r="O33" s="1" t="inlineStr">
         <is>
-          <t>당 공사의 건축주, 감독자, 건설사업관리자 등을 입회시켜 명확히 할 필요가 있다.</t>
+          <t>이는 공사 준공과 밀접한 관계가 있 으므로 신중을 기할 필요가 있다.</t>
         </is>
       </c>
       <c r="P33" s="1" t="inlineStr">
@@ -3461,17 +3461,17 @@
       </c>
       <c r="M34" s="1" t="inlineStr">
         <is>
-          <t>측량이 진행되는 과정은 및 .</t>
+          <t>측량의 신청은 관할지역 지적공사에 신청해 실시하게 되며, 측량과정에서 인접 대지의 주인과 해 당 공사의 건축주, 감독자, 건설사업관리자 등을 입회시켜 명확히 할 필요가 있다.</t>
         </is>
       </c>
       <c r="N34" s="1" t="inlineStr">
         <is>
-          <t>측량이 진행되는 과정은 및 .</t>
+          <t>측량의 신청은 관할지역 지적공사에 신청해 실시하게 되며, 측량과정에서 인접 대지의 주인과 해 당 공사의 건축주, 감독자, 건설사업관리자 등을 입회시켜 명확히 할 필요가 있다.</t>
         </is>
       </c>
       <c r="O34" s="1" t="inlineStr">
         <is>
-          <t>측량이 진행되는 과정은 및 .</t>
+          <t>측량의 신청은 관할지역 지적공사에 신청해 실시하게 되며, 측량과정에서 인접 대지의 주인과 해 당 공사의 건축주, 감독자, 건설사업관리자 등을 입회시켜 명확히 할 필요가 있다.</t>
         </is>
       </c>
       <c r="P34" s="1" t="inlineStr">
@@ -3550,22 +3550,22 @@
       </c>
       <c r="M35" s="1" t="inlineStr">
         <is>
-          <t>확히 해서 공사계획 시에 토공량의 산출과 기준점(bench mark)의 확정 등을 위해서 실시한다.</t>
+          <t>측량의 종류와 측량이 진행되는 과정은 및 .  현황(현상)측량 이는 에 제시된 LX 한국국토정보공사에서 시행하는 현황측량과 다르게 측량전문 용역업 체에 의해 시행하는 것으로서 대지의 고저, 지상물의 현황, 그리고 인접 건물과의 이격거리 등을 명 확히 해서 공사계획 시에 토공량의 산출과 기준점(bench mark)의 확정 등을 위해서 실시한다.</t>
         </is>
       </c>
       <c r="N35" s="1" t="inlineStr">
         <is>
-          <t>확히 해서 공사계획 시에 토공량의 산출과 기준점(bench mark)의 확정 등을 위해서 실시한다.</t>
+          <t>측량의 종류와 측량이 진행되는 과정은 및 .  현황(현상)측량 이는 에 제시된 LX 한국국토정보공사에서 시행하는 현황측량과 다르게 측량전문 용역업 체에 의해 시행하는 것으로서 대지의 고저, 지상물의 현황, 그리고 인접 건물과의 이격거리 등을 명 확히 해서 공사계획 시에 토공량의 산출과 기준점(bench mark)의 확정 등을 위해서 실시한다.</t>
         </is>
       </c>
       <c r="O35" s="1" t="inlineStr">
         <is>
-          <t>확히 해서 공사계획 시에 토공량의 산출과 기준점(bench mark)의 확정 등을 위해서 실시한다.</t>
+          <t>측량의 종류와 측량이 진행되는 과정은 및 .  현황(현상)측량 이는 에 제시된 LX 한국국토정보공사에서 시행하는 현황측량과 다르게 측량전문 용역업 체에 의해 시행하는 것으로서 대지의 고저, 지상물의 현황, 그리고 인접 건물과의 이격거리 등을 명 확히 해서 공사계획 시에 토공량의 산출과 기준점(bench mark)의 확정 등을 위해서 실시한다.</t>
         </is>
       </c>
       <c r="P35" s="1" t="inlineStr">
         <is>
-          <t>특징</t>
+          <t>분류</t>
         </is>
       </c>
       <c r="Q35" s="1" t="inlineStr"/>
@@ -3639,22 +3639,22 @@
       </c>
       <c r="M36" s="1" t="inlineStr">
         <is>
-          <t>료 시까지 존치시켜야 하는 중요 요소이다.</t>
+          <t>측량의 종류 구 분 내 용 •지적공부상에 등록된 경계를 지표상에 복원하는 측량 경계복원측량 •건축물을 신축·증축·개축하거나 인접한 토지와의 경계를 확인하고자 할 때 주로 하는 측량 •지 상구조물 또는 지형, 지물이 점유하는 위치 현황을 지적도 또는 임야도에 등록된 경계와 대비해 그 관계 위치를 지적현황측량 표시 및 면적을 알기 위한 측량 •건축물을 신축하고 준공검사를 신청하거나, 인접 토지에서 점유토지의 면적을 지적측량성과도로 확인받기 위한 때 •지적공부에 등록된 한 필지의 토지를 두 필지 이상으로 나누기 위해 실시하는 측량 분할측량 •한 필지 토지를 두 필지 이상으로 나누어서 매매할 때 •임야대장 및 임야도에 등록된 토지를 토지대장 및 지적도에 등록하기 위한 측량 등록전환측량 •임야대장에 등록된 토지가 형질이 변경되어서 토지대장에 등록하고자 할 때 신규등록측량 •지적공부에 등록되지 않은 토지를 새로 등록하기 위해 실시하는 측량 지적기준점측량 •세부측량 시 기준점이 필요한 경우에 실시하는 측량 (1) 기준점 기준점(bench mark)은 모든 공사 높이의 기준이 되는 것으로서, 공사 착수 전에 설정해 공사 종 료 시까지 존치시켜야 하는 중요 요소이다.</t>
         </is>
       </c>
       <c r="N36" s="1" t="inlineStr">
         <is>
-          <t>료 시까지 존치시켜야 하는 중요 요소이다.</t>
+          <t>측량의 종류 구 분 내 용 •지적공부상에 등록된 경계를 지표상에 복원하는 측량 경계복원측량 •건축물을 신축·증축·개축하거나 인접한 토지와의 경계를 확인하고자 할 때 주로 하는 측량 •지 상구조물 또는 지형, 지물이 점유하는 위치 현황을 지적도 또는 임야도에 등록된 경계와 대비해 그 관계 위치를 지적현황측량 표시 및 면적을 알기 위한 측량 •건축물을 신축하고 준공검사를 신청하거나, 인접 토지에서 점유토지의 면적을 지적측량성과도로 확인받기 위한 때 •지적공부에 등록된 한 필지의 토지를 두 필지 이상으로 나누기 위해 실시하는 측량 분할측량 •한 필지 토지를 두 필지 이상으로 나누어서 매매할 때 •임야대장 및 임야도에 등록된 토지를 토지대장 및 지적도에 등록하기 위한 측량 등록전환측량 •임야대장에 등록된 토지가 형질이 변경되어서 토지대장에 등록하고자 할 때 신규등록측량 •지적공부에 등록되지 않은 토지를 새로 등록하기 위해 실시하는 측량 지적기준점측량 •세부측량 시 기준점이 필요한 경우에 실시하는 측량 (1) 기준점 기준점(bench mark)은 모든 공사 높이의 기준이 되는 것으로서, 공사 착수 전에 설정해 공사 종 료 시까지 존치시켜야 하는 중요 요소이다.</t>
         </is>
       </c>
       <c r="O36" s="1" t="inlineStr">
         <is>
-          <t>료 시까지 존치시켜야 하는 중요 요소이다.</t>
+          <t>측량의 종류 구 분 내 용 •지적공부상에 등록된 경계를 지표상에 복원하는 측량 경계복원측량 •건축물을 신축·증축·개축하거나 인접한 토지와의 경계를 확인하고자 할 때 주로 하는 측량 •지 상구조물 또는 지형, 지물이 점유하는 위치 현황을 지적도 또는 임야도에 등록된 경계와 대비해 그 관계 위치를 지적현황측량 표시 및 면적을 알기 위한 측량 •건축물을 신축하고 준공검사를 신청하거나, 인접 토지에서 점유토지의 면적을 지적측량성과도로 확인받기 위한 때 •지적공부에 등록된 한 필지의 토지를 두 필지 이상으로 나누기 위해 실시하는 측량 분할측량 •한 필지 토지를 두 필지 이상으로 나누어서 매매할 때 •임야대장 및 임야도에 등록된 토지를 토지대장 및 지적도에 등록하기 위한 측량 등록전환측량 •임야대장에 등록된 토지가 형질이 변경되어서 토지대장에 등록하고자 할 때 신규등록측량 •지적공부에 등록되지 않은 토지를 새로 등록하기 위해 실시하는 측량 지적기준점측량 •세부측량 시 기준점이 필요한 경우에 실시하는 측량 (1) 기준점 기준점(bench mark)은 모든 공사 높이의 기준이 되는 것으로서, 공사 착수 전에 설정해 공사 종 료 시까지 존치시켜야 하는 중요 요소이다.</t>
         </is>
       </c>
       <c r="P36" s="1" t="inlineStr">
         <is>
-          <t>특징</t>
+          <t>수치</t>
         </is>
       </c>
       <c r="Q36" s="1" t="inlineStr"/>
@@ -3728,17 +3728,17 @@
       </c>
       <c r="M37" s="1" t="inlineStr">
         <is>
-          <t>따라 보조 기준점을 1~2개소 설치한다.</t>
+          <t>기준점의 위치, 기타 사항은 따로 기록해 두고, 필요에 따라 보조 기준점을 1~2개소 설치한다.</t>
         </is>
       </c>
       <c r="N37" s="1" t="inlineStr">
         <is>
-          <t>따라 보조 기준점을 1~2개소 설치한다.</t>
+          <t>기준점의 위치, 기타 사항은 따로 기록해 두고, 필요에 따라 보조 기준점을 1~2개소 설치한다.</t>
         </is>
       </c>
       <c r="O37" s="1" t="inlineStr">
         <is>
-          <t>따라 보조 기준점을 1~2개소 설치한다.</t>
+          <t>기준점의 위치, 기타 사항은 따로 기록해 두고, 필요에 따라 보조 기준점을 1~2개소 설치한다.</t>
         </is>
       </c>
       <c r="P37" s="1" t="inlineStr">
@@ -3817,17 +3817,17 @@
       </c>
       <c r="M38" s="1" t="inlineStr">
         <is>
-          <t>보호조치를 해야 한다.</t>
+          <t>기준점은 이동 및 변형되지 않도록 그 주위를 감싸는 등의 보호조치를 해야 한다.</t>
         </is>
       </c>
       <c r="N38" s="1" t="inlineStr">
         <is>
-          <t>보호조치를 해야 한다.</t>
+          <t>기준점은 이동 및 변형되지 않도록 그 주위를 감싸는 등의 보호조치를 해야 한다.</t>
         </is>
       </c>
       <c r="O38" s="1" t="inlineStr">
         <is>
-          <t>보호조치를 해야 한다.</t>
+          <t>기준점은 이동 및 변형되지 않도록 그 주위를 감싸는 등의 보호조치를 해야 한다.</t>
         </is>
       </c>
       <c r="P38" s="1" t="inlineStr">
@@ -3906,17 +3906,17 @@
       </c>
       <c r="M39" s="1" t="inlineStr">
         <is>
-          <t>띄우는 것을 줄쳐보기(줄띄우기)라 한다.</t>
+          <t>(2) 줄쳐보기 띄우는 것을 줄쳐보기(줄띄우기)라 한다.</t>
         </is>
       </c>
       <c r="N39" s="1" t="inlineStr">
         <is>
-          <t>띄우는 것을 줄쳐보기(줄띄우기)라 한다.</t>
+          <t>(2) 줄쳐보기 띄우는 것을 줄쳐보기(줄띄우기)라 한다.</t>
         </is>
       </c>
       <c r="O39" s="1" t="inlineStr">
         <is>
-          <t>띄우는 것을 줄쳐보기(줄띄우기)라 한다.</t>
+          <t>(2) 줄쳐보기 띄우는 것을 줄쳐보기(줄띄우기)라 한다.</t>
         </is>
       </c>
       <c r="P39" s="1" t="inlineStr">
@@ -3995,17 +3995,17 @@
       </c>
       <c r="M40" s="1" t="inlineStr">
         <is>
-          <t>거리를 검토한다.</t>
+          <t>이것에 의해 건물과 도로, 그리고 인접대지 경계선에서의 거리를 검토한다.</t>
         </is>
       </c>
       <c r="N40" s="1" t="inlineStr">
         <is>
-          <t>거리를 검토한다.</t>
+          <t>이것에 의해 건물과 도로, 그리고 인접대지 경계선에서의 거리를 검토한다.</t>
         </is>
       </c>
       <c r="O40" s="1" t="inlineStr">
         <is>
-          <t>거리를 검토한다.</t>
+          <t>이것에 의해 건물과 도로, 그리고 인접대지 경계선에서의 거리를 검토한다.</t>
         </is>
       </c>
       <c r="P40" s="1" t="inlineStr">
@@ -4173,22 +4173,22 @@
       </c>
       <c r="M42" s="1" t="inlineStr">
         <is>
-          <t>이므로 이동이나 변형이 없게 견고하게 설치해야 한다.</t>
+          <t>건축주 LX 한국국토정보공사 시, 군, 구청 측량 절차 건건물물 다름추를 이용한 위치잡기(좌) 줄쳐보기(우) (3) 규준틀 규준틀은 건물 각부의 위치 및 높이, 기초의 너비 또는 길이 등을 정확히 결정하기 위한 것 이므로 이동이나 변형이 없게 견고하게 설치해야 한다.</t>
         </is>
       </c>
       <c r="N42" s="1" t="inlineStr">
         <is>
-          <t>이므로 이동이나 변형이 없게 견고하게 설치해야 한다.</t>
+          <t>건축주 LX 한국국토정보공사 시, 군, 구청 측량 절차 건건물물 다름추를 이용한 위치잡기(좌) 줄쳐보기(우) (3) 규준틀 규준틀은 건물 각부의 위치 및 높이, 기초의 너비 또는 길이 등을 정확히 결정하기 위한 것 이므로 이동이나 변형이 없게 견고하게 설치해야 한다.</t>
         </is>
       </c>
       <c r="O42" s="1" t="inlineStr">
         <is>
-          <t>이므로 이동이나 변형이 없게 견고하게 설치해야 한다.</t>
+          <t>건축주 LX 한국국토정보공사 시, 군, 구청 측량 절차 건건물물 다름추를 이용한 위치잡기(좌) 줄쳐보기(우) (3) 규준틀 규준틀은 건물 각부의 위치 및 높이, 기초의 너비 또는 길이 등을 정확히 결정하기 위한 것 이므로 이동이나 변형이 없게 견고하게 설치해야 한다.</t>
         </is>
       </c>
       <c r="P42" s="1" t="inlineStr">
         <is>
-          <t>특징</t>
+          <t>수치</t>
         </is>
       </c>
       <c r="Q42" s="1" t="inlineStr"/>
@@ -4262,22 +4262,22 @@
       </c>
       <c r="M43" s="1" t="inlineStr">
         <is>
-          <t>고, 규준대에는 벽의 중심, 벽의 폭, 기초폭 등이 표시된다.</t>
+          <t>수평 규준틀은 규준말뚝과 규준대(수 평꿸대)로 구성되며, 규준대는 규준말뚝에 수평보기나 레벨에 의해 수평하게 견고히 설치하 고, 규준대에는 벽의 중심, 벽의 폭, 기초폭 등이 표시된다.</t>
         </is>
       </c>
       <c r="N43" s="1" t="inlineStr">
         <is>
-          <t>고, 규준대에는 벽의 중심, 벽의 폭, 기초폭 등이 표시된다.</t>
+          <t>수평 규준틀은 규준말뚝과 규준대(수 평꿸대)로 구성되며, 규준대는 규준말뚝에 수평보기나 레벨에 의해 수평하게 견고히 설치하 고, 규준대에는 벽의 중심, 벽의 폭, 기초폭 등이 표시된다.</t>
         </is>
       </c>
       <c r="O43" s="1" t="inlineStr">
         <is>
-          <t>고, 규준대에는 벽의 중심, 벽의 폭, 기초폭 등이 표시된다.</t>
+          <t>수평 규준틀은 규준말뚝과 규준대(수 평꿸대)로 구성되며, 규준대는 규준말뚝에 수평보기나 레벨에 의해 수평하게 견고히 설치하 고, 규준대에는 벽의 중심, 벽의 폭, 기초폭 등이 표시된다.</t>
         </is>
       </c>
       <c r="P43" s="1" t="inlineStr">
         <is>
-          <t>특징</t>
+          <t>분류</t>
         </is>
       </c>
       <c r="Q43" s="1" t="inlineStr"/>
@@ -4351,17 +4351,17 @@
       </c>
       <c r="M44" s="1" t="inlineStr">
         <is>
-          <t>규준틀에는 평 규준틀, 귀 규준틀, 그리고 세로 규준틀 등이 있다.</t>
+          <t>수평꿸대 &lt;평면&gt; &lt;입면&gt; 규준틀에는 평 규준틀, 귀 규준틀, 그리고 세로 규준틀 등이 있다.</t>
         </is>
       </c>
       <c r="N44" s="1" t="inlineStr">
         <is>
-          <t>규준틀에는 평 규준틀, 귀 규준틀, 그리고 세로 규준틀 등이 있다.</t>
+          <t>수평꿸대 &lt;평면&gt; &lt;입면&gt; 규준틀에는 평 규준틀, 귀 규준틀, 그리고 세로 규준틀 등이 있다.</t>
         </is>
       </c>
       <c r="O44" s="1" t="inlineStr">
         <is>
-          <t>규준틀에는 평 규준틀, 귀 규준틀, 그리고 세로 규준틀 등이 있다.</t>
+          <t>수평꿸대 &lt;평면&gt; &lt;입면&gt; 규준틀에는 평 규준틀, 귀 규준틀, 그리고 세로 규준틀 등이 있다.</t>
         </is>
       </c>
       <c r="P44" s="1" t="inlineStr">
@@ -4440,17 +4440,17 @@
       </c>
       <c r="M45" s="1" t="inlineStr">
         <is>
-          <t>설치하며, 귀 규준틀은 건물의 외곽 모서리 기둥, 계단실 기타 돌출부분에 설치한다.</t>
+          <t>평 규준틀은 건물의 외곽 기둥 중 모서리 기둥(계단실 기타 돌출부분 포함)을 제외한 각 기둥, 옹벽, 기타 주요부 위치에 설치하며, 귀 규준틀은 건물의 외곽 모서리 기둥, 계단실 기타 돌출부분에 설치한다.</t>
         </is>
       </c>
       <c r="N45" s="1" t="inlineStr">
         <is>
-          <t>설치하며, 귀 규준틀은 건물의 외곽 모서리 기둥, 계단실 기타 돌출부분에 설치한다.</t>
+          <t>평 규준틀은 건물의 외곽 기둥 중 모서리 기둥(계단실 기타 돌출부분 포함)을 제외한 각 기둥, 옹벽, 기타 주요부 위치에 설치하며, 귀 규준틀은 건물의 외곽 모서리 기둥, 계단실 기타 돌출부분에 설치한다.</t>
         </is>
       </c>
       <c r="O45" s="1" t="inlineStr">
         <is>
-          <t>설치하며, 귀 규준틀은 건물의 외곽 모서리 기둥, 계단실 기타 돌출부분에 설치한다.</t>
+          <t>평 규준틀은 건물의 외곽 기둥 중 모서리 기둥(계단실 기타 돌출부분 포함)을 제외한 각 기둥, 옹벽, 기타 주요부 위치에 설치하며, 귀 규준틀은 건물의 외곽 모서리 기둥, 계단실 기타 돌출부분에 설치한다.</t>
         </is>
       </c>
       <c r="P45" s="1" t="inlineStr">
@@ -4529,17 +4529,17 @@
       </c>
       <c r="M46" s="1" t="inlineStr">
         <is>
-          <t>수 등을 표시한다.</t>
+          <t>그리고 세로 규준틀은 내외 내력벽의 상호 접합부 등에 수직으로 설치해 벽돌 또는 블럭의 단 수 등을 표시한다.</t>
         </is>
       </c>
       <c r="N46" s="1" t="inlineStr">
         <is>
-          <t>수 등을 표시한다.</t>
+          <t>그리고 세로 규준틀은 내외 내력벽의 상호 접합부 등에 수직으로 설치해 벽돌 또는 블럭의 단 수 등을 표시한다.</t>
         </is>
       </c>
       <c r="O46" s="1" t="inlineStr">
         <is>
-          <t>수 등을 표시한다.</t>
+          <t>그리고 세로 규준틀은 내외 내력벽의 상호 접합부 등에 수직으로 설치해 벽돌 또는 블럭의 단 수 등을 표시한다.</t>
         </is>
       </c>
       <c r="P46" s="1" t="inlineStr">
@@ -4618,22 +4618,22 @@
       </c>
       <c r="M47" s="1" t="inlineStr">
         <is>
-          <t>기준선을 먹매김해 각종 창호류 및 각 부위별 마감공사 높이의 기준이 되게 한다.</t>
+          <t>평 규준틀 규준틀의 배치와 종류 (4) 기준선 먹매김(먹줄치기) 건물 각 구조부의 위치, 간벽의 분할 배치선, 수직·수평의 기준에 대해 먹매김하고, 각 층 각 실 등의 기둥 또는 벽면 등에는 각 층 마감기준 상단 레벨로부터 보통 약 1m 선상에 수평 기준선을 먹매김해 각종 창호류 및 각 부위별 마감공사 높이의 기준이 되게 한다.</t>
         </is>
       </c>
       <c r="N47" s="1" t="inlineStr">
         <is>
-          <t>기준선을 먹매김해 각종 창호류 및 각 부위별 마감공사 높이의 기준이 되게 한다.</t>
+          <t>평 규준틀 규준틀의 배치와 종류 (4) 기준선 먹매김(먹줄치기) 건물 각 구조부의 위치, 간벽의 분할 배치선, 수직·수평의 기준에 대해 먹매김하고, 각 층 각 실 등의 기둥 또는 벽면 등에는 각 층 마감기준 상단 레벨로부터 보통 약 1m 선상에 수평 기준선을 먹매김해 각종 창호류 및 각 부위별 마감공사 높이의 기준이 되게 한다.</t>
         </is>
       </c>
       <c r="O47" s="1" t="inlineStr">
         <is>
-          <t>기준선을 먹매김해 각종 창호류 및 각 부위별 마감공사 높이의 기준이 되게 한다.</t>
+          <t>평 규준틀 규준틀의 배치와 종류 (4) 기준선 먹매김(먹줄치기) 건물 각 구조부의 위치, 간벽의 분할 배치선, 수직·수평의 기준에 대해 먹매김하고, 각 층 각 실 등의 기둥 또는 벽면 등에는 각 층 마감기준 상단 레벨로부터 보통 약 1m 선상에 수평 기준선을 먹매김해 각종 창호류 및 각 부위별 마감공사 높이의 기준이 되게 한다.</t>
         </is>
       </c>
       <c r="P47" s="1" t="inlineStr">
         <is>
-          <t>특징</t>
+          <t>수치</t>
         </is>
       </c>
       <c r="Q47" s="1" t="inlineStr"/>
@@ -4707,22 +4707,22 @@
       </c>
       <c r="M48" s="1" t="inlineStr">
         <is>
-          <t>한 비산먼지, 그리고 골조 및 마감공사 시에 발생하는 비산먼지가 대부분이다.</t>
+          <t>건설현장에서 문제가 되는 대기오염은 터파기 시 각종 장비나 드릴 등 건설장비에 의한 비 산먼지, 굴토작업에 의한 토사의 상차·운반·야적 등에 의한 비산먼지, 현장 내 콘크리트 부 어넣기를 위한 레미콘 믹서트럭의 이동에 의한 비산먼지, 각종 자재 반입차량 등의 이동에 의 한 비산먼지, 그리고 골조 및 마감공사 시에 발생하는 비산먼지가 대부분이다.</t>
         </is>
       </c>
       <c r="N48" s="1" t="inlineStr">
         <is>
-          <t>한 비산먼지, 그리고 골조 및 마감공사 시에 발생하는 비산먼지가 대부분이다.</t>
+          <t>건설현장에서 문제가 되는 대기오염은 터파기 시 각종 장비나 드릴 등 건설장비에 의한 비 산먼지, 굴토작업에 의한 토사의 상차·운반·야적 등에 의한 비산먼지, 현장 내 콘크리트 부 어넣기를 위한 레미콘 믹서트럭의 이동에 의한 비산먼지, 각종 자재 반입차량 등의 이동에 의 한 비산먼지, 그리고 골조 및 마감공사 시에 발생하는 비산먼지가 대부분이다.</t>
         </is>
       </c>
       <c r="O48" s="1" t="inlineStr">
         <is>
-          <t>한 비산먼지, 그리고 골조 및 마감공사 시에 발생하는 비산먼지가 대부분이다.</t>
+          <t>건설현장에서 문제가 되는 대기오염은 터파기 시 각종 장비나 드릴 등 건설장비에 의한 비 산먼지, 굴토작업에 의한 토사의 상차·운반·야적 등에 의한 비산먼지, 현장 내 콘크리트 부 어넣기를 위한 레미콘 믹서트럭의 이동에 의한 비산먼지, 각종 자재 반입차량 등의 이동에 의 한 비산먼지, 그리고 골조 및 마감공사 시에 발생하는 비산먼지가 대부분이다.</t>
         </is>
       </c>
       <c r="P48" s="1" t="inlineStr">
         <is>
-          <t>특징</t>
+          <t>단점</t>
         </is>
       </c>
       <c r="Q48" s="1" t="inlineStr"/>
@@ -4796,22 +4796,22 @@
       </c>
       <c r="M49" s="1" t="inlineStr">
         <is>
-          <t>시하고 필요에 따라 적절한 방지시설을 설치한다.</t>
+          <t>비산먼지의 저 감기준 및 지침을 준수해 인근 주민에 피해를 입히지 않도록 하며, 지속적인 지도와 점검을 실 시하고 필요에 따라 적절한 방지시설을 설치한다.  운반작업에 따른 비산먼지 및 대책 ① 공사용 차량에 의한 도로에의 토사유출을 방지하기 위해 공사장 출입구에 세륜 및 세차시설을 설치하 고 진입도로 및 차량 이동로에는 1일 3회 이상 살수 차를 운행해 비산먼지의 발생을 최대한 억제한다.</t>
         </is>
       </c>
       <c r="N49" s="1" t="inlineStr">
         <is>
-          <t>시하고 필요에 따라 적절한 방지시설을 설치한다.</t>
+          <t>비산먼지의 저 감기준 및 지침을 준수해 인근 주민에 피해를 입히지 않도록 하며, 지속적인 지도와 점검을 실 시하고 필요에 따라 적절한 방지시설을 설치한다.  운반작업에 따른 비산먼지 및 대책 ① 공사용 차량에 의한 도로에의 토사유출을 방지하기 위해 공사장 출입구에 세륜 및 세차시설을 설치하 고 진입도로 및 차량 이동로에는 1일 3회 이상 살수 차를 운행해 비산먼지의 발생을 최대한 억제한다.</t>
         </is>
       </c>
       <c r="O49" s="1" t="inlineStr">
         <is>
-          <t>시하고 필요에 따라 적절한 방지시설을 설치한다.</t>
+          <t>비산먼지의 저 감기준 및 지침을 준수해 인근 주민에 피해를 입히지 않도록 하며, 지속적인 지도와 점검을 실 시하고 필요에 따라 적절한 방지시설을 설치한다.  운반작업에 따른 비산먼지 및 대책 ① 공사용 차량에 의한 도로에의 토사유출을 방지하기 위해 공사장 출입구에 세륜 및 세차시설을 설치하 고 진입도로 및 차량 이동로에는 1일 3회 이상 살수 차를 운행해 비산먼지의 발생을 최대한 억제한다.</t>
         </is>
       </c>
       <c r="P49" s="1" t="inlineStr">
         <is>
-          <t>특징</t>
+          <t>수치</t>
         </is>
       </c>
       <c r="Q49" s="1" t="inlineStr"/>
@@ -4885,22 +4885,22 @@
       </c>
       <c r="M50" s="1" t="inlineStr">
         <is>
-          <t>차를 운행해 비산먼지의 발생을 최대한 억제한다.</t>
+          <t>② 토사 및 골재 운반 시 덮개를 씌워 운행한다.</t>
         </is>
       </c>
       <c r="N50" s="1" t="inlineStr">
         <is>
-          <t>차를 운행해 비산먼지의 발생을 최대한 억제한다.</t>
+          <t>② 토사 및 골재 운반 시 덮개를 씌워 운행한다.</t>
         </is>
       </c>
       <c r="O50" s="1" t="inlineStr">
         <is>
-          <t>차를 운행해 비산먼지의 발생을 최대한 억제한다.</t>
+          <t>② 토사 및 골재 운반 시 덮개를 씌워 운행한다.</t>
         </is>
       </c>
       <c r="P50" s="1" t="inlineStr">
         <is>
-          <t>단점</t>
+          <t>특징</t>
         </is>
       </c>
       <c r="Q50" s="1" t="inlineStr"/>
@@ -4974,17 +4974,17 @@
       </c>
       <c r="M51" s="1" t="inlineStr">
         <is>
-          <t>② 토사 및 골재 운반 시 덮개를 씌워 운행한다.</t>
+          <t>③ 골재 야적장에는 덮개를 씌워 둔다.</t>
         </is>
       </c>
       <c r="N51" s="1" t="inlineStr">
         <is>
-          <t>② 토사 및 골재 운반 시 덮개를 씌워 운행한다.</t>
+          <t>③ 골재 야적장에는 덮개를 씌워 둔다.</t>
         </is>
       </c>
       <c r="O51" s="1" t="inlineStr">
         <is>
-          <t>② 토사 및 골재 운반 시 덮개를 씌워 운행한다.</t>
+          <t>③ 골재 야적장에는 덮개를 씌워 둔다.</t>
         </is>
       </c>
       <c r="P51" s="1" t="inlineStr">
@@ -5063,17 +5063,17 @@
       </c>
       <c r="M52" s="1" t="inlineStr">
         <is>
-          <t>③ 골재 야적장에는 덮개를 씌워 둔다.</t>
+          <t>④ 공사장과 접해 있는 지역은 가설울타리 위에 방진 가설울타리 상부 방진막 막을 설치한다.</t>
         </is>
       </c>
       <c r="N52" s="1" t="inlineStr">
         <is>
-          <t>③ 골재 야적장에는 덮개를 씌워 둔다.</t>
+          <t>④ 공사장과 접해 있는 지역은 가설울타리 위에 방진 가설울타리 상부 방진막 막을 설치한다.</t>
         </is>
       </c>
       <c r="O52" s="1" t="inlineStr">
         <is>
-          <t>③ 골재 야적장에는 덮개를 씌워 둔다.</t>
+          <t>④ 공사장과 접해 있는 지역은 가설울타리 위에 방진 가설울타리 상부 방진막 막을 설치한다.</t>
         </is>
       </c>
       <c r="P52" s="1" t="inlineStr">
@@ -5152,17 +5152,17 @@
       </c>
       <c r="M53" s="1" t="inlineStr">
         <is>
-          <t>막을 설치한다.</t>
+          <t>⑤ 공사차량 주행도로는 주기적으로 살수를 실시하 고 떨어진 흙은 발생 즉시 청소한다.</t>
         </is>
       </c>
       <c r="N53" s="1" t="inlineStr">
         <is>
-          <t>막을 설치한다.</t>
+          <t>⑤ 공사차량 주행도로는 주기적으로 살수를 실시하 고 떨어진 흙은 발생 즉시 청소한다.</t>
         </is>
       </c>
       <c r="O53" s="1" t="inlineStr">
         <is>
-          <t>막을 설치한다.</t>
+          <t>⑤ 공사차량 주행도로는 주기적으로 살수를 실시하 고 떨어진 흙은 발생 즉시 청소한다.</t>
         </is>
       </c>
       <c r="P53" s="1" t="inlineStr">
@@ -5241,22 +5241,22 @@
       </c>
       <c r="M54" s="1" t="inlineStr">
         <is>
-          <t>고 떨어진 흙은 발생 즉시 청소한다.</t>
+          <t>⑥ 공사장 출입구에는 환경관리 전담요원을 배치해 공 사차량의 세륜 상태 및 덮개 상태를 점검토록 하 고, 주변에 청소원을 배치해 관리토록 한다.  건설장비 운용 및 골조공사 시 비산먼지 공사현장에 설치된 방진망 ① 건 설공사장인 경우 방진벽 또는 방진망을 설치하 고 4층 이하의 건물인 경우 1일 3회 이상 살수를 실시한다.</t>
         </is>
       </c>
       <c r="N54" s="1" t="inlineStr">
         <is>
-          <t>고 떨어진 흙은 발생 즉시 청소한다.</t>
+          <t>⑥ 공사장 출입구에는 환경관리 전담요원을 배치해 공 사차량의 세륜 상태 및 덮개 상태를 점검토록 하 고, 주변에 청소원을 배치해 관리토록 한다.  건설장비 운용 및 골조공사 시 비산먼지 공사현장에 설치된 방진망 ① 건 설공사장인 경우 방진벽 또는 방진망을 설치하 고 4층 이하의 건물인 경우 1일 3회 이상 살수를 실시한다.</t>
         </is>
       </c>
       <c r="O54" s="1" t="inlineStr">
         <is>
-          <t>고 떨어진 흙은 발생 즉시 청소한다.</t>
+          <t>⑥ 공사장 출입구에는 환경관리 전담요원을 배치해 공 사차량의 세륜 상태 및 덮개 상태를 점검토록 하 고, 주변에 청소원을 배치해 관리토록 한다.  건설장비 운용 및 골조공사 시 비산먼지 공사현장에 설치된 방진망 ① 건 설공사장인 경우 방진벽 또는 방진망을 설치하 고 4층 이하의 건물인 경우 1일 3회 이상 살수를 실시한다.</t>
         </is>
       </c>
       <c r="P54" s="1" t="inlineStr">
         <is>
-          <t>특징</t>
+          <t>수치</t>
         </is>
       </c>
       <c r="Q54" s="1" t="inlineStr"/>
@@ -5330,17 +5330,17 @@
       </c>
       <c r="M55" s="1" t="inlineStr">
         <is>
-          <t>고, 주변에 청소원을 배치해 관리토록 한다.</t>
+          <t>② 현장에서 운용되는 건설장비(크롤러 드릴 등)는 대기오염 방지장치의 부착을 의무화한다.</t>
         </is>
       </c>
       <c r="N55" s="1" t="inlineStr">
         <is>
-          <t>고, 주변에 청소원을 배치해 관리토록 한다.</t>
+          <t>② 현장에서 운용되는 건설장비(크롤러 드릴 등)는 대기오염 방지장치의 부착을 의무화한다.</t>
         </is>
       </c>
       <c r="O55" s="1" t="inlineStr">
         <is>
-          <t>고, 주변에 청소원을 배치해 관리토록 한다.</t>
+          <t>② 현장에서 운용되는 건설장비(크롤러 드릴 등)는 대기오염 방지장치의 부착을 의무화한다.</t>
         </is>
       </c>
       <c r="P55" s="1" t="inlineStr">
@@ -5380,7 +5380,7 @@
         </is>
       </c>
       <c r="E56" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F56" s="1" t="inlineStr">
         <is>
@@ -5404,32 +5404,32 @@
       </c>
       <c r="J56" s="1" t="inlineStr">
         <is>
-          <t>2.3.4</t>
+          <t>2.3.5</t>
         </is>
       </c>
       <c r="K56" s="1" t="inlineStr">
         <is>
-          <t>비산먼지 발생원인 및 대책</t>
+          <t>가설용수</t>
         </is>
       </c>
       <c r="L56" s="1" t="inlineStr">
         <is>
-          <t>비산먼지 발생원인 및 대책</t>
+          <t>가설용수</t>
         </is>
       </c>
       <c r="M56" s="1" t="inlineStr">
         <is>
-          <t>실시한다.</t>
+          <t>공사용, 방화용, 음용, 위생설비용, 청소용으로 지하수를 개발해 사용하거나 상수도를 현장 에 인입해 공사용 용수로 사용한다.</t>
         </is>
       </c>
       <c r="N56" s="1" t="inlineStr">
         <is>
-          <t>실시한다.</t>
+          <t>공사용, 방화용, 음용, 위생설비용, 청소용으로 지하수를 개발해 사용하거나 상수도를 현장 에 인입해 공사용 용수로 사용한다.</t>
         </is>
       </c>
       <c r="O56" s="1" t="inlineStr">
         <is>
-          <t>실시한다.</t>
+          <t>공사용, 방화용, 음용, 위생설비용, 청소용으로 지하수를 개발해 사용하거나 상수도를 현장 에 인입해 공사용 용수로 사용한다.</t>
         </is>
       </c>
       <c r="P56" s="1" t="inlineStr">
@@ -5469,7 +5469,7 @@
         </is>
       </c>
       <c r="E57" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F57" s="1" t="inlineStr">
         <is>
@@ -5493,32 +5493,32 @@
       </c>
       <c r="J57" s="1" t="inlineStr">
         <is>
-          <t>2.3.4</t>
+          <t>2.3.5</t>
         </is>
       </c>
       <c r="K57" s="1" t="inlineStr">
         <is>
-          <t>비산먼지 발생원인 및 대책</t>
+          <t>가설용수</t>
         </is>
       </c>
       <c r="L57" s="1" t="inlineStr">
         <is>
-          <t>비산먼지 발생원인 및 대책</t>
+          <t>가설용수</t>
         </is>
       </c>
       <c r="M57" s="1" t="inlineStr">
         <is>
-          <t>② 현장에서 운용되는 건설장비(크롤러 드릴 등)는 대기오염 방지장치의 부착을 의무화한다.</t>
+          <t>일반적으로 현장에서 지하수 개발이 가능할 경우는 지하 수를 공사용수로 사용하고, 지하수 개발이 어려울 경우에는 상수도를 사용한다.</t>
         </is>
       </c>
       <c r="N57" s="1" t="inlineStr">
         <is>
-          <t>② 현장에서 운용되는 건설장비(크롤러 드릴 등)는 대기오염 방지장치의 부착을 의무화한다.</t>
+          <t>일반적으로 현장에서 지하수 개발이 가능할 경우는 지하 수를 공사용수로 사용하고, 지하수 개발이 어려울 경우에는 상수도를 사용한다.</t>
         </is>
       </c>
       <c r="O57" s="1" t="inlineStr">
         <is>
-          <t>② 현장에서 운용되는 건설장비(크롤러 드릴 등)는 대기오염 방지장치의 부착을 의무화한다.</t>
+          <t>일반적으로 현장에서 지하수 개발이 가능할 경우는 지하 수를 공사용수로 사용하고, 지하수 개발이 어려울 경우에는 상수도를 사용한다.</t>
         </is>
       </c>
       <c r="P57" s="1" t="inlineStr">
@@ -5558,7 +5558,7 @@
         </is>
       </c>
       <c r="E58" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F58" s="1" t="inlineStr">
         <is>
@@ -5582,32 +5582,32 @@
       </c>
       <c r="J58" s="1" t="inlineStr">
         <is>
-          <t>2.3.4</t>
+          <t>2.3.5</t>
         </is>
       </c>
       <c r="K58" s="1" t="inlineStr">
         <is>
-          <t>비산먼지 발생원인 및 대책</t>
+          <t>가설용수</t>
         </is>
       </c>
       <c r="L58" s="1" t="inlineStr">
         <is>
-          <t>비산먼지 발생원인 및 대책</t>
+          <t>가설용수</t>
         </is>
       </c>
       <c r="M58" s="1" t="inlineStr">
         <is>
-          <t>쓰레기 슈트를 설치해 쓰레기를 처리한다.</t>
+          <t>기존 상수도에 연결할 경우에는 배관을 연장하고 급수전을 두어서 나사로 연결되는 호스로 물을 사용할 수 있게 해야 하며, 동결방지를 위해 보온을 하거나 동결방지 밸브를 설치하는 등 적절한 조치를 취해야 한다.</t>
         </is>
       </c>
       <c r="N58" s="1" t="inlineStr">
         <is>
-          <t>쓰레기 슈트를 설치해 쓰레기를 처리한다.</t>
+          <t>기존 상수도에 연결할 경우에는 배관을 연장하고 급수전을 두어서 나사로 연결되는 호스로 물을 사용할 수 있게 해야 하며, 동결방지를 위해 보온을 하거나 동결방지 밸브를 설치하는 등 적절한 조치를 취해야 한다.</t>
         </is>
       </c>
       <c r="O58" s="1" t="inlineStr">
         <is>
-          <t>쓰레기 슈트를 설치해 쓰레기를 처리한다.</t>
+          <t>기존 상수도에 연결할 경우에는 배관을 연장하고 급수전을 두어서 나사로 연결되는 호스로 물을 사용할 수 있게 해야 하며, 동결방지를 위해 보온을 하거나 동결방지 밸브를 설치하는 등 적절한 조치를 취해야 한다.</t>
         </is>
       </c>
       <c r="P58" s="1" t="inlineStr">
@@ -5647,7 +5647,7 @@
         </is>
       </c>
       <c r="E59" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F59" s="1" t="inlineStr">
         <is>
@@ -5671,32 +5671,32 @@
       </c>
       <c r="J59" s="1" t="inlineStr">
         <is>
-          <t>2.3.4</t>
+          <t>2.3.5</t>
         </is>
       </c>
       <c r="K59" s="1" t="inlineStr">
         <is>
-          <t>비산먼지 발생원인 및 대책</t>
+          <t>가설용수</t>
         </is>
       </c>
       <c r="L59" s="1" t="inlineStr">
         <is>
-          <t>비산먼지 발생원인 및 대책</t>
+          <t>가설용수</t>
         </is>
       </c>
       <c r="M59" s="1" t="inlineStr">
         <is>
-          <t>•이동식 덮개를 덮고 운행</t>
+          <t>공사 용수로 사용하는 운반장치 및 배 관에는 식수 불가 경고표시를 해 야 한다.</t>
         </is>
       </c>
       <c r="N59" s="1" t="inlineStr">
         <is>
-          <t>•이동식 덮개를 덮고 운행</t>
+          <t>공사 용수로 사용하는 운반장치 및 배 관에는 식수 불가 경고표시를 해 야 한다.</t>
         </is>
       </c>
       <c r="O59" s="1" t="inlineStr">
         <is>
-          <t>•이동식 덮개를 덮고 운행</t>
+          <t>공사 용수로 사용하는 운반장치 및 배 관에는 식수 불가 경고표시를 해 야 한다.</t>
         </is>
       </c>
       <c r="P59" s="1" t="inlineStr">
@@ -5775,17 +5775,17 @@
       </c>
       <c r="M60" s="1" t="inlineStr">
         <is>
-          <t>에 인입해 공사용 용수로 사용한다.</t>
+          <t>현장 내의 가설용수 인입공사가 마무리되면 공사 착수와 동시에 현장 내 가설급수 설비공사를 진 행하며, 우선적으로 가설사무실과 가설화장실, 그리고 세륜세차시설 의 가설급수 공사를 한다.</t>
         </is>
       </c>
       <c r="N60" s="1" t="inlineStr">
         <is>
-          <t>에 인입해 공사용 용수로 사용한다.</t>
+          <t>현장 내의 가설용수 인입공사가 마무리되면 공사 착수와 동시에 현장 내 가설급수 설비공사를 진 행하며, 우선적으로 가설사무실과 가설화장실, 그리고 세륜세차시설 의 가설급수 공사를 한다.</t>
         </is>
       </c>
       <c r="O60" s="1" t="inlineStr">
         <is>
-          <t>에 인입해 공사용 용수로 사용한다.</t>
+          <t>현장 내의 가설용수 인입공사가 마무리되면 공사 착수와 동시에 현장 내 가설급수 설비공사를 진 행하며, 우선적으로 가설사무실과 가설화장실, 그리고 세륜세차시설 의 가설급수 공사를 한다.</t>
         </is>
       </c>
       <c r="P60" s="1" t="inlineStr">
@@ -5864,17 +5864,17 @@
       </c>
       <c r="M61" s="1" t="inlineStr">
         <is>
-          <t>수를 공사용수로 사용하고, 지하수 개발이 어려울 경우에는 상수도를 사용한다.</t>
+          <t>그 후 공사의 진행에 따라서 공사를 진 지하수 굴착 현장 내 가설물탱크 행한다.</t>
         </is>
       </c>
       <c r="N61" s="1" t="inlineStr">
         <is>
-          <t>수를 공사용수로 사용하고, 지하수 개발이 어려울 경우에는 상수도를 사용한다.</t>
+          <t>그 후 공사의 진행에 따라서 공사를 진 지하수 굴착 현장 내 가설물탱크 행한다.</t>
         </is>
       </c>
       <c r="O61" s="1" t="inlineStr">
         <is>
-          <t>수를 공사용수로 사용하고, 지하수 개발이 어려울 경우에는 상수도를 사용한다.</t>
+          <t>그 후 공사의 진행에 따라서 공사를 진 지하수 굴착 현장 내 가설물탱크 행한다.</t>
         </is>
       </c>
       <c r="P61" s="1" t="inlineStr">
@@ -5938,37 +5938,37 @@
       </c>
       <c r="J62" s="1" t="inlineStr">
         <is>
-          <t>2.3.5</t>
+          <t>2.3.6</t>
         </is>
       </c>
       <c r="K62" s="1" t="inlineStr">
         <is>
-          <t>가설용수</t>
+          <t>가설전기</t>
         </is>
       </c>
       <c r="L62" s="1" t="inlineStr">
         <is>
-          <t>가설용수</t>
+          <t>가설전기</t>
         </is>
       </c>
       <c r="M62" s="1" t="inlineStr">
         <is>
-          <t>적절한 조치를 취해야 한다.</t>
+          <t>건설공사 시의 가설전기설비는 빌딩, 공장, 아파트, 터널 등을 신설 또는 증개축하는 경우 임시로 수전해 단기간 사용하고 철거하는 전기설비를 말한다.</t>
         </is>
       </c>
       <c r="N62" s="1" t="inlineStr">
         <is>
-          <t>적절한 조치를 취해야 한다.</t>
+          <t>건설공사 시의 가설전기설비는 빌딩, 공장, 아파트, 터널 등을 신설 또는 증개축하는 경우 임시로 수전해 단기간 사용하고 철거하는 전기설비를 말한다.</t>
         </is>
       </c>
       <c r="O62" s="1" t="inlineStr">
         <is>
-          <t>적절한 조치를 취해야 한다.</t>
+          <t>건설공사 시의 가설전기설비는 빌딩, 공장, 아파트, 터널 등을 신설 또는 증개축하는 경우 임시로 수전해 단기간 사용하고 철거하는 전기설비를 말한다.</t>
         </is>
       </c>
       <c r="P62" s="1" t="inlineStr">
         <is>
-          <t>특징</t>
+          <t>정의</t>
         </is>
       </c>
       <c r="Q62" s="1" t="inlineStr"/>
@@ -6027,32 +6027,32 @@
       </c>
       <c r="J63" s="1" t="inlineStr">
         <is>
-          <t>2.3.5</t>
+          <t>2.3.6</t>
         </is>
       </c>
       <c r="K63" s="1" t="inlineStr">
         <is>
-          <t>가설용수</t>
+          <t>가설전기</t>
         </is>
       </c>
       <c r="L63" s="1" t="inlineStr">
         <is>
-          <t>가설용수</t>
+          <t>가설전기</t>
         </is>
       </c>
       <c r="M63" s="1" t="inlineStr">
         <is>
-          <t>야 한다.</t>
+          <t>가설전기 인입은 현장 개설과 동시에 시작하는 것이 좋다.</t>
         </is>
       </c>
       <c r="N63" s="1" t="inlineStr">
         <is>
-          <t>야 한다.</t>
+          <t>가설전기 인입은 현장 개설과 동시에 시작하는 것이 좋다.</t>
         </is>
       </c>
       <c r="O63" s="1" t="inlineStr">
         <is>
-          <t>야 한다.</t>
+          <t>가설전기 인입은 현장 개설과 동시에 시작하는 것이 좋다.</t>
         </is>
       </c>
       <c r="P63" s="1" t="inlineStr">
@@ -6116,32 +6116,32 @@
       </c>
       <c r="J64" s="1" t="inlineStr">
         <is>
-          <t>2.3.5</t>
+          <t>2.3.6</t>
         </is>
       </c>
       <c r="K64" s="1" t="inlineStr">
         <is>
-          <t>가설용수</t>
+          <t>가설전기</t>
         </is>
       </c>
       <c r="L64" s="1" t="inlineStr">
         <is>
-          <t>가설용수</t>
+          <t>가설전기</t>
         </is>
       </c>
       <c r="M64" s="1" t="inlineStr">
         <is>
-          <t>의 가설급수 공사를 한다.</t>
+          <t>가설변대의 위치는 한전주와의 거리, 부지 내 가설전기의 동선관계, 공터, 안전성, 공사비 등을 종합적으로 고려해 선정해야 하며, 임시전력 총용량(kW)을 산출한 후 가설전기 인입공사 대행업체에 의뢰해 시행한다.</t>
         </is>
       </c>
       <c r="N64" s="1" t="inlineStr">
         <is>
-          <t>의 가설급수 공사를 한다.</t>
+          <t>가설변대의 위치는 한전주와의 거리, 부지 내 가설전기의 동선관계, 공터, 안전성, 공사비 등을 종합적으로 고려해 선정해야 하며, 임시전력 총용량(kW)을 산출한 후 가설전기 인입공사 대행업체에 의뢰해 시행한다.</t>
         </is>
       </c>
       <c r="O64" s="1" t="inlineStr">
         <is>
-          <t>의 가설급수 공사를 한다.</t>
+          <t>가설변대의 위치는 한전주와의 거리, 부지 내 가설전기의 동선관계, 공터, 안전성, 공사비 등을 종합적으로 고려해 선정해야 하며, 임시전력 총용량(kW)을 산출한 후 가설전기 인입공사 대행업체에 의뢰해 시행한다.</t>
         </is>
       </c>
       <c r="P64" s="1" t="inlineStr">
@@ -6205,37 +6205,37 @@
       </c>
       <c r="J65" s="1" t="inlineStr">
         <is>
-          <t>2.3.5</t>
+          <t>2.3.6</t>
         </is>
       </c>
       <c r="K65" s="1" t="inlineStr">
         <is>
-          <t>가설용수</t>
+          <t>가설전기</t>
         </is>
       </c>
       <c r="L65" s="1" t="inlineStr">
         <is>
-          <t>가설용수</t>
+          <t>가설전기</t>
         </is>
       </c>
       <c r="M65" s="1" t="inlineStr">
         <is>
-          <t>행한다.</t>
+          <t>또한 착공 전 최대전력량을 산정해 사용전력량을 결정해야 하는데, 그 요령은 ① 동시사용 계수는 최대전력량의 60% 정도로 하고, ② 통상 호이스트는 대당 30kW, 집크레인은 50kW, 타워크레인은 75kW로 하며, ③ 양중기계는 스타트 시 전력이 많이 필요하므로 그때의 소요전 력량을 감안한다.</t>
         </is>
       </c>
       <c r="N65" s="1" t="inlineStr">
         <is>
-          <t>행한다.</t>
+          <t>또한 착공 전 최대전력량을 산정해 사용전력량을 결정해야 하는데, 그 요령은 ① 동시사용 계수는 최대전력량의 60% 정도로 하고, ② 통상 호이스트는 대당 30kW, 집크레인은 50kW, 타워크레인은 75kW로 하며, ③ 양중기계는 스타트 시 전력이 많이 필요하므로 그때의 소요전 력량을 감안한다.</t>
         </is>
       </c>
       <c r="O65" s="1" t="inlineStr">
         <is>
-          <t>행한다.</t>
+          <t>또한 착공 전 최대전력량을 산정해 사용전력량을 결정해야 하는데, 그 요령은 ① 동시사용 계수는 최대전력량의 60% 정도로 하고, ② 통상 호이스트는 대당 30kW, 집크레인은 50kW, 타워크레인은 75kW로 하며, ③ 양중기계는 스타트 시 전력이 많이 필요하므로 그때의 소요전 력량을 감안한다.</t>
         </is>
       </c>
       <c r="P65" s="1" t="inlineStr">
         <is>
-          <t>특징</t>
+          <t>수치</t>
         </is>
       </c>
       <c r="Q65" s="1" t="inlineStr"/>
@@ -6309,22 +6309,22 @@
       </c>
       <c r="M66" s="1" t="inlineStr">
         <is>
-          <t>임시로 수전해 단기간 사용하고 철거하는 전기설비를 말한다.</t>
+          <t>그리고 기간별 사 용전력량은 누계 후 최대사용량을 산출해 낸다.</t>
         </is>
       </c>
       <c r="N66" s="1" t="inlineStr">
         <is>
-          <t>임시로 수전해 단기간 사용하고 철거하는 전기설비를 말한다.</t>
+          <t>그리고 기간별 사 용전력량은 누계 후 최대사용량을 산출해 낸다.</t>
         </is>
       </c>
       <c r="O66" s="1" t="inlineStr">
         <is>
-          <t>임시로 수전해 단기간 사용하고 철거하는 전기설비를 말한다.</t>
+          <t>그리고 기간별 사 용전력량은 누계 후 최대사용량을 산출해 낸다.</t>
         </is>
       </c>
       <c r="P66" s="1" t="inlineStr">
         <is>
-          <t>정의</t>
+          <t>특징</t>
         </is>
       </c>
       <c r="Q66" s="1" t="inlineStr"/>
@@ -6359,7 +6359,7 @@
         </is>
       </c>
       <c r="E67" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F67" s="1" t="inlineStr">
         <is>
@@ -6383,32 +6383,32 @@
       </c>
       <c r="J67" s="1" t="inlineStr">
         <is>
-          <t>2.3.6</t>
+          <t>2.3.7</t>
         </is>
       </c>
       <c r="K67" s="1" t="inlineStr">
         <is>
-          <t>가설전기</t>
+          <t>양중장비</t>
         </is>
       </c>
       <c r="L67" s="1" t="inlineStr">
         <is>
-          <t>가설전기</t>
+          <t>양중장비</t>
         </is>
       </c>
       <c r="M67" s="1" t="inlineStr">
         <is>
-          <t>가설전기 인입은 현장 개설과 동시에 시작하는 것이 좋다.</t>
+          <t>현장에서 공사를 수행하기 위해서 중량물을 상하 및 좌우로 운반하고, 또한 작업자와 자재 를 건물의 상층부로 이동시키기 위해서 주로 사용하고 있는 양중장비로는 타워크레인(tower crane)과 호이스트(hoist) 등이 있다.</t>
         </is>
       </c>
       <c r="N67" s="1" t="inlineStr">
         <is>
-          <t>가설전기 인입은 현장 개설과 동시에 시작하는 것이 좋다.</t>
+          <t>현장에서 공사를 수행하기 위해서 중량물을 상하 및 좌우로 운반하고, 또한 작업자와 자재 를 건물의 상층부로 이동시키기 위해서 주로 사용하고 있는 양중장비로는 타워크레인(tower crane)과 호이스트(hoist) 등이 있다.</t>
         </is>
       </c>
       <c r="O67" s="1" t="inlineStr">
         <is>
-          <t>가설전기 인입은 현장 개설과 동시에 시작하는 것이 좋다.</t>
+          <t>현장에서 공사를 수행하기 위해서 중량물을 상하 및 좌우로 운반하고, 또한 작업자와 자재 를 건물의 상층부로 이동시키기 위해서 주로 사용하고 있는 양중장비로는 타워크레인(tower crane)과 호이스트(hoist) 등이 있다.</t>
         </is>
       </c>
       <c r="P67" s="1" t="inlineStr">
@@ -6448,7 +6448,7 @@
         </is>
       </c>
       <c r="E68" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F68" s="1" t="inlineStr">
         <is>
@@ -6472,37 +6472,37 @@
       </c>
       <c r="J68" s="1" t="inlineStr">
         <is>
-          <t>2.3.6</t>
+          <t>2.3.7</t>
         </is>
       </c>
       <c r="K68" s="1" t="inlineStr">
         <is>
-          <t>가설전기</t>
+          <t>양중장비</t>
         </is>
       </c>
       <c r="L68" s="1" t="inlineStr">
         <is>
-          <t>가설전기</t>
+          <t>양중장비</t>
         </is>
       </c>
       <c r="M68" s="1" t="inlineStr">
         <is>
-          <t>하며, 임시전력 총용량(kW)을 산출한 후 가설전기 인입공사 대행업체에 의뢰해 시행한다.</t>
+          <t>최근에는 건축물의 고층화 현상에 따라 이러한 양중장비 의 중요성이 날로 증가하고 있다.  타워크레인 타워크레인은 붐(boom)의 작동 방식과 상승방식에 따라 다음과 같이 분류할 수 있다.</t>
         </is>
       </c>
       <c r="N68" s="1" t="inlineStr">
         <is>
-          <t>하며, 임시전력 총용량(kW)을 산출한 후 가설전기 인입공사 대행업체에 의뢰해 시행한다.</t>
+          <t>최근에는 건축물의 고층화 현상에 따라 이러한 양중장비 의 중요성이 날로 증가하고 있다.  타워크레인 타워크레인은 붐(boom)의 작동 방식과 상승방식에 따라 다음과 같이 분류할 수 있다.</t>
         </is>
       </c>
       <c r="O68" s="1" t="inlineStr">
         <is>
-          <t>하며, 임시전력 총용량(kW)을 산출한 후 가설전기 인입공사 대행업체에 의뢰해 시행한다.</t>
+          <t>최근에는 건축물의 고층화 현상에 따라 이러한 양중장비 의 중요성이 날로 증가하고 있다.  타워크레인 타워크레인은 붐(boom)의 작동 방식과 상승방식에 따라 다음과 같이 분류할 수 있다.</t>
         </is>
       </c>
       <c r="P68" s="1" t="inlineStr">
         <is>
-          <t>특징</t>
+          <t>분류</t>
         </is>
       </c>
       <c r="Q68" s="1" t="inlineStr"/>
@@ -6537,7 +6537,7 @@
         </is>
       </c>
       <c r="E69" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F69" s="1" t="inlineStr">
         <is>
@@ -6561,37 +6561,37 @@
       </c>
       <c r="J69" s="1" t="inlineStr">
         <is>
-          <t>2.3.6</t>
+          <t>2.3.7</t>
         </is>
       </c>
       <c r="K69" s="1" t="inlineStr">
         <is>
-          <t>가설전기</t>
+          <t>양중장비</t>
         </is>
       </c>
       <c r="L69" s="1" t="inlineStr">
         <is>
-          <t>가설전기</t>
+          <t>양중장비</t>
         </is>
       </c>
       <c r="M69" s="1" t="inlineStr">
         <is>
-          <t>력량을 감안한다.</t>
+          <t>(1) 붐의 작동방식에 따른 종류 ① 수평형 타워크레인 (horizontal type tower crane) ② 기복형 타워크레인 (luffing type tower crane) 수평형 타워크레인 기복형 타워크레인 (2) 타워크레인의 배치 배치위치 건물 안 건물 밖 대지 상황 대지의 여유가 없는 건물 대지의 여유가 충분한 건물 마감공사 마감공사가 복잡 영향이 없음 적정 건물 일반 상업용 건물과 같이 마감이 단순한 건물 호텔 또는 공동주택 등 복잡한 건물 (3) 상승과 이동에 따른 종류 구분 고정식(stationary type) 상승식(climbing type) 이동식(travelling type) ① 건물의 외측에 설치 시 ① 건물 내부에 설치 시 ① 저층의 넓은 현장 ② 건 물 높이가 고층일 때 텔레스코핑 ② 상승 시 T/C 자체의 유압장치를 이용 ② 이동 가능하며 적은 수의 (telescoping) 작업 필요 ③ 건물 내부 슬래브에 개구부 형성 타워크레인으로 넓은 지역을 ③ 자립고 이상 작업 시는 가새(bracing) 보강 ④ 구조체에 발생하는 하중과 응력에 대한 작업하고자 할 때 사용 ④ 해체는 텔레스코핑의 역순으로 자체 작업 본 구조체의 보강 필요 ③ 레일을 설치하기 전에 지면지내력을 조사 ⑤ 건물 골조에 영향 적음 ⑤ 해체 시 별도의 T/C 해체용 크레인을 이용 하고, 지면의 요철을 제거 (4) 타워크레인 기초 지반에 기초 앵커를 기초 콘크리트로 고정시키고 타워크레인을 설치하는 기본적인 설치방법 으로 대체로 건물의 높이가 낮은 건축물에 주로 활용되고 있다.</t>
         </is>
       </c>
       <c r="N69" s="1" t="inlineStr">
         <is>
-          <t>력량을 감안한다.</t>
+          <t>(1) 붐의 작동방식에 따른 종류 ① 수평형 타워크레인 (horizontal type tower crane) ② 기복형 타워크레인 (luffing type tower crane) 수평형 타워크레인 기복형 타워크레인 (2) 타워크레인의 배치 배치위치 건물 안 건물 밖 대지 상황 대지의 여유가 없는 건물 대지의 여유가 충분한 건물 마감공사 마감공사가 복잡 영향이 없음 적정 건물 일반 상업용 건물과 같이 마감이 단순한 건물 호텔 또는 공동주택 등 복잡한 건물 (3) 상승과 이동에 따른 종류 구분 고정식(stationary type) 상승식(climbing type) 이동식(travelling type) ① 건물의 외측에 설치 시 ① 건물 내부에 설치 시 ① 저층의 넓은 현장 ② 건 물 높이가 고층일 때 텔레스코핑 ② 상승 시 T/C 자체의 유압장치를 이용 ② 이동 가능하며 적은 수의 (telescoping) 작업 필요 ③ 건물 내부 슬래브에 개구부 형성 타워크레인으로 넓은 지역을 ③ 자립고 이상 작업 시는 가새(bracing) 보강 ④ 구조체에 발생하는 하중과 응력에 대한 작업하고자 할 때 사용 ④ 해체는 텔레스코핑의 역순으로 자체 작업 본 구조체의 보강 필요 ③ 레일을 설치하기 전에 지면지내력을 조사 ⑤ 건물 골조에 영향 적음 ⑤ 해체 시 별도의 T/C 해체용 크레인을 이용 하고, 지면의 요철을 제거 (4) 타워크레인 기초 지반에 기초 앵커를 기초 콘크리트로 고정시키고 타워크레인을 설치하는 기본적인 설치방법 으로 대체로 건물의 높이가 낮은 건축물에 주로 활용되고 있다.</t>
         </is>
       </c>
       <c r="O69" s="1" t="inlineStr">
         <is>
-          <t>력량을 감안한다.</t>
+          <t>(1) 붐의 작동방식에 따른 종류 ① 수평형 타워크레인 (horizontal type tower crane) ② 기복형 타워크레인 (luffing type tower crane) 수평형 타워크레인 기복형 타워크레인 (2) 타워크레인의 배치 배치위치 건물 안 건물 밖 대지 상황 대지의 여유가 없는 건물 대지의 여유가 충분한 건물 마감공사 마감공사가 복잡 영향이 없음 적정 건물 일반 상업용 건물과 같이 마감이 단순한 건물 호텔 또는 공동주택 등 복잡한 건물 (3) 상승과 이동에 따른 종류 구분 고정식(stationary type) 상승식(climbing type) 이동식(travelling type) ① 건물의 외측에 설치 시 ① 건물 내부에 설치 시 ① 저층의 넓은 현장 ② 건 물 높이가 고층일 때 텔레스코핑 ② 상승 시 T/C 자체의 유압장치를 이용 ② 이동 가능하며 적은 수의 (telescoping) 작업 필요 ③ 건물 내부 슬래브에 개구부 형성 타워크레인으로 넓은 지역을 ③ 자립고 이상 작업 시는 가새(bracing) 보강 ④ 구조체에 발생하는 하중과 응력에 대한 작업하고자 할 때 사용 ④ 해체는 텔레스코핑의 역순으로 자체 작업 본 구조체의 보강 필요 ③ 레일을 설치하기 전에 지면지내력을 조사 ⑤ 건물 골조에 영향 적음 ⑤ 해체 시 별도의 T/C 해체용 크레인을 이용 하고, 지면의 요철을 제거 (4) 타워크레인 기초 지반에 기초 앵커를 기초 콘크리트로 고정시키고 타워크레인을 설치하는 기본적인 설치방법 으로 대체로 건물의 높이가 낮은 건축물에 주로 활용되고 있다.</t>
         </is>
       </c>
       <c r="P69" s="1" t="inlineStr">
         <is>
-          <t>특징</t>
+          <t>수치</t>
         </is>
       </c>
       <c r="Q69" s="1" t="inlineStr"/>
@@ -6626,7 +6626,7 @@
         </is>
       </c>
       <c r="E70" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F70" s="1" t="inlineStr">
         <is>
@@ -6650,32 +6650,32 @@
       </c>
       <c r="J70" s="1" t="inlineStr">
         <is>
-          <t>2.3.6</t>
+          <t>2.3.7</t>
         </is>
       </c>
       <c r="K70" s="1" t="inlineStr">
         <is>
-          <t>가설전기</t>
+          <t>양중장비</t>
         </is>
       </c>
       <c r="L70" s="1" t="inlineStr">
         <is>
-          <t>가설전기</t>
+          <t>양중장비</t>
         </is>
       </c>
       <c r="M70" s="1" t="inlineStr">
         <is>
-          <t>산출해 낸다.</t>
+          <t>기초 콘크리트용 콘크리트 강 도와 철근 규격 및 강도는 제조업체에서 제공하는 시방을 준수해 설치한다.</t>
         </is>
       </c>
       <c r="N70" s="1" t="inlineStr">
         <is>
-          <t>산출해 낸다.</t>
+          <t>기초 콘크리트용 콘크리트 강 도와 철근 규격 및 강도는 제조업체에서 제공하는 시방을 준수해 설치한다.</t>
         </is>
       </c>
       <c r="O70" s="1" t="inlineStr">
         <is>
-          <t>산출해 낸다.</t>
+          <t>기초 콘크리트용 콘크리트 강 도와 철근 규격 및 강도는 제조업체에서 제공하는 시방을 준수해 설치한다.</t>
         </is>
       </c>
       <c r="P70" s="1" t="inlineStr">
@@ -6715,7 +6715,7 @@
         </is>
       </c>
       <c r="E71" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F71" s="1" t="inlineStr">
         <is>
@@ -6739,37 +6739,37 @@
       </c>
       <c r="J71" s="1" t="inlineStr">
         <is>
-          <t>2.3.6</t>
+          <t>2.3.7</t>
         </is>
       </c>
       <c r="K71" s="1" t="inlineStr">
         <is>
-          <t>가설전기</t>
+          <t>양중장비</t>
         </is>
       </c>
       <c r="L71" s="1" t="inlineStr">
         <is>
-          <t>가설전기</t>
+          <t>양중장비</t>
         </is>
       </c>
       <c r="M71" s="1" t="inlineStr">
         <is>
-          <t>가설변대 가설변대 주위 울타리</t>
+          <t>또한 소정의 지내 력이 나오지 않을 시에는 별도의 말뚝박기 등과 같은 보강작업을 사전에 시행해야 한다.</t>
         </is>
       </c>
       <c r="N71" s="1" t="inlineStr">
         <is>
-          <t>가설변대 가설변대 주위 울타리</t>
+          <t>또한 소정의 지내 력이 나오지 않을 시에는 별도의 말뚝박기 등과 같은 보강작업을 사전에 시행해야 한다.</t>
         </is>
       </c>
       <c r="O71" s="1" t="inlineStr">
         <is>
-          <t>가설변대 가설변대 주위 울타리</t>
+          <t>또한 소정의 지내 력이 나오지 않을 시에는 별도의 말뚝박기 등과 같은 보강작업을 사전에 시행해야 한다.</t>
         </is>
       </c>
       <c r="P71" s="1" t="inlineStr">
         <is>
-          <t>특징</t>
+          <t>정의</t>
         </is>
       </c>
       <c r="Q71" s="1" t="inlineStr"/>
@@ -6843,22 +6843,22 @@
       </c>
       <c r="M72" s="1" t="inlineStr">
         <is>
-          <t>crane)과 호이스트(hoist) 등이 있다.</t>
+          <t>다음의 그림과 같은 순서로 타워크레인의 기초를 설치한다.</t>
         </is>
       </c>
       <c r="N72" s="1" t="inlineStr">
         <is>
-          <t>crane)과 호이스트(hoist) 등이 있다.</t>
+          <t>다음의 그림과 같은 순서로 타워크레인의 기초를 설치한다.</t>
         </is>
       </c>
       <c r="O72" s="1" t="inlineStr">
         <is>
-          <t>crane)과 호이스트(hoist) 등이 있다.</t>
+          <t>다음의 그림과 같은 순서로 타워크레인의 기초를 설치한다.</t>
         </is>
       </c>
       <c r="P72" s="1" t="inlineStr">
         <is>
-          <t>특징</t>
+          <t>순서</t>
         </is>
       </c>
       <c r="Q72" s="1" t="inlineStr"/>
@@ -6932,17 +6932,17 @@
       </c>
       <c r="M73" s="1" t="inlineStr">
         <is>
-          <t>의 중요성이 날로 증가하고 있다.</t>
+          <t>기초 버림 콘크리트 타설 기초 앵커 설치 기초 철근 배근 설치 타워크레인용 마스트(mast) T/C와이어 브레이싱  호이스트(hoist) 호이스트는 가이드 레일을 따라 움직이는 적재함을 사용해 자 재만을 움직이는 화물용 호이스트와, 적재함 내에 조작 스위치나 비상정지장치 등의 조작장치가 설치되어 있는 인화물 겸용 호이 스트로 나누어진다.</t>
         </is>
       </c>
       <c r="N73" s="1" t="inlineStr">
         <is>
-          <t>의 중요성이 날로 증가하고 있다.</t>
+          <t>기초 버림 콘크리트 타설 기초 앵커 설치 기초 철근 배근 설치 타워크레인용 마스트(mast) T/C와이어 브레이싱  호이스트(hoist) 호이스트는 가이드 레일을 따라 움직이는 적재함을 사용해 자 재만을 움직이는 화물용 호이스트와, 적재함 내에 조작 스위치나 비상정지장치 등의 조작장치가 설치되어 있는 인화물 겸용 호이 스트로 나누어진다.</t>
         </is>
       </c>
       <c r="O73" s="1" t="inlineStr">
         <is>
-          <t>의 중요성이 날로 증가하고 있다.</t>
+          <t>기초 버림 콘크리트 타설 기초 앵커 설치 기초 철근 배근 설치 타워크레인용 마스트(mast) T/C와이어 브레이싱  호이스트(hoist) 호이스트는 가이드 레일을 따라 움직이는 적재함을 사용해 자 재만을 움직이는 화물용 호이스트와, 적재함 내에 조작 스위치나 비상정지장치 등의 조작장치가 설치되어 있는 인화물 겸용 호이 스트로 나누어진다.</t>
         </is>
       </c>
       <c r="P73" s="1" t="inlineStr">
@@ -7021,22 +7021,22 @@
       </c>
       <c r="M74" s="1" t="inlineStr">
         <is>
-          <t>같이 분류할 수 있다.</t>
+          <t>일반적으로는 인화물 겸용이 사용된다.</t>
         </is>
       </c>
       <c r="N74" s="1" t="inlineStr">
         <is>
-          <t>같이 분류할 수 있다.</t>
+          <t>일반적으로는 인화물 겸용이 사용된다.</t>
         </is>
       </c>
       <c r="O74" s="1" t="inlineStr">
         <is>
-          <t>같이 분류할 수 있다.</t>
+          <t>일반적으로는 인화물 겸용이 사용된다.</t>
         </is>
       </c>
       <c r="P74" s="1" t="inlineStr">
         <is>
-          <t>분류</t>
+          <t>특징</t>
         </is>
       </c>
       <c r="Q74" s="1" t="inlineStr"/>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="E75" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F75" s="1" t="inlineStr">
         <is>
@@ -7095,37 +7095,37 @@
       </c>
       <c r="J75" s="1" t="inlineStr">
         <is>
-          <t>2.3.7</t>
+          <t>2.3.8</t>
         </is>
       </c>
       <c r="K75" s="1" t="inlineStr">
         <is>
-          <t>양중장비</t>
+          <t>비계</t>
         </is>
       </c>
       <c r="L75" s="1" t="inlineStr">
         <is>
-          <t>양중장비</t>
+          <t>비계</t>
         </is>
       </c>
       <c r="M75" s="1" t="inlineStr">
         <is>
-          <t>으로 대체로 건물의 높이가 낮은 건축물에 주로 활용되고 있다.</t>
+          <t>건물 내외부에는 공사 시행에 편리하고 구조적으로 안전하며 외관이 흉하지 않은 구조로 비계 또는 재해안전시설 등을 설치해 호이스트 수시로 점검하며 안전사고를 예방해야 한다.  비계의 구비요건 ① 작업 또는 통행에 충분한 면적일 것 ② 자재의 운반과 적치가 가능할 것 ③ 작업 대상물에 가능한 한 접근할 수 있을 것 ④ 작업자의 추락방지와 재료의 낙하방지 조치가 있을 것 ⑤ 작업과 통행에 방해되는 부재가 없을 것 ⑥ 조립과 해체가 용이할 것 ⑦ 사람과 적치 자재의 하중에 대해 충분한 내력이 있을 것  비계의 재료 비계에 사용되는 재료의 종류로는 통나무, 강관파이프, 그리고 강관틀이 주로 사용된다.</t>
         </is>
       </c>
       <c r="N75" s="1" t="inlineStr">
         <is>
-          <t>으로 대체로 건물의 높이가 낮은 건축물에 주로 활용되고 있다.</t>
+          <t>건물 내외부에는 공사 시행에 편리하고 구조적으로 안전하며 외관이 흉하지 않은 구조로 비계 또는 재해안전시설 등을 설치해 호이스트 수시로 점검하며 안전사고를 예방해야 한다.  비계의 구비요건 ① 작업 또는 통행에 충분한 면적일 것 ② 자재의 운반과 적치가 가능할 것 ③ 작업 대상물에 가능한 한 접근할 수 있을 것 ④ 작업자의 추락방지와 재료의 낙하방지 조치가 있을 것 ⑤ 작업과 통행에 방해되는 부재가 없을 것 ⑥ 조립과 해체가 용이할 것 ⑦ 사람과 적치 자재의 하중에 대해 충분한 내력이 있을 것  비계의 재료 비계에 사용되는 재료의 종류로는 통나무, 강관파이프, 그리고 강관틀이 주로 사용된다.</t>
         </is>
       </c>
       <c r="O75" s="1" t="inlineStr">
         <is>
-          <t>으로 대체로 건물의 높이가 낮은 건축물에 주로 활용되고 있다.</t>
+          <t>건물 내외부에는 공사 시행에 편리하고 구조적으로 안전하며 외관이 흉하지 않은 구조로 비계 또는 재해안전시설 등을 설치해 호이스트 수시로 점검하며 안전사고를 예방해야 한다.  비계의 구비요건 ① 작업 또는 통행에 충분한 면적일 것 ② 자재의 운반과 적치가 가능할 것 ③ 작업 대상물에 가능한 한 접근할 수 있을 것 ④ 작업자의 추락방지와 재료의 낙하방지 조치가 있을 것 ⑤ 작업과 통행에 방해되는 부재가 없을 것 ⑥ 조립과 해체가 용이할 것 ⑦ 사람과 적치 자재의 하중에 대해 충분한 내력이 있을 것  비계의 재료 비계에 사용되는 재료의 종류로는 통나무, 강관파이프, 그리고 강관틀이 주로 사용된다.</t>
         </is>
       </c>
       <c r="P75" s="1" t="inlineStr">
         <is>
-          <t>특징</t>
+          <t>분류</t>
         </is>
       </c>
       <c r="Q75" s="1" t="inlineStr"/>
@@ -7160,7 +7160,7 @@
         </is>
       </c>
       <c r="E76" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F76" s="1" t="inlineStr">
         <is>
@@ -7184,32 +7184,32 @@
       </c>
       <c r="J76" s="1" t="inlineStr">
         <is>
-          <t>2.3.7</t>
+          <t>2.3.8</t>
         </is>
       </c>
       <c r="K76" s="1" t="inlineStr">
         <is>
-          <t>양중장비</t>
+          <t>비계</t>
         </is>
       </c>
       <c r="L76" s="1" t="inlineStr">
         <is>
-          <t>양중장비</t>
+          <t>비계</t>
         </is>
       </c>
       <c r="M76" s="1" t="inlineStr">
         <is>
-          <t>도와 철근 규격 및 강도는 제조업체에서 제공하는 시방을 준수해 설치한다.</t>
+          <t>그 러나 통나무는 비계 재료로서 거의 사용되지 않고 있는 실정이다.</t>
         </is>
       </c>
       <c r="N76" s="1" t="inlineStr">
         <is>
-          <t>도와 철근 규격 및 강도는 제조업체에서 제공하는 시방을 준수해 설치한다.</t>
+          <t>그 러나 통나무는 비계 재료로서 거의 사용되지 않고 있는 실정이다.</t>
         </is>
       </c>
       <c r="O76" s="1" t="inlineStr">
         <is>
-          <t>도와 철근 규격 및 강도는 제조업체에서 제공하는 시방을 준수해 설치한다.</t>
+          <t>그 러나 통나무는 비계 재료로서 거의 사용되지 않고 있는 실정이다.</t>
         </is>
       </c>
       <c r="P76" s="1" t="inlineStr">
@@ -7249,7 +7249,7 @@
         </is>
       </c>
       <c r="E77" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F77" s="1" t="inlineStr">
         <is>
@@ -7273,32 +7273,32 @@
       </c>
       <c r="J77" s="1" t="inlineStr">
         <is>
-          <t>2.3.7</t>
+          <t>2.3.8</t>
         </is>
       </c>
       <c r="K77" s="1" t="inlineStr">
         <is>
-          <t>양중장비</t>
+          <t>비계</t>
         </is>
       </c>
       <c r="L77" s="1" t="inlineStr">
         <is>
-          <t>양중장비</t>
+          <t>비계</t>
         </is>
       </c>
       <c r="M77" s="1" t="inlineStr">
         <is>
-          <t>력이 나오지 않을 시에는 별도의 말뚝박기 등과 같은 보강작업을 사전에 시행해야 한다.</t>
+          <t>비계 재료의 안전성은 건설 안전과 직결되므로 강관비계와 부속재는 한국공업규격(KS)의 KSF 8002 기준에, 강관틀비계 는 KSF 8003의 기준에 합격한 재료를 사용한다.</t>
         </is>
       </c>
       <c r="N77" s="1" t="inlineStr">
         <is>
-          <t>력이 나오지 않을 시에는 별도의 말뚝박기 등과 같은 보강작업을 사전에 시행해야 한다.</t>
+          <t>비계 재료의 안전성은 건설 안전과 직결되므로 강관비계와 부속재는 한국공업규격(KS)의 KSF 8002 기준에, 강관틀비계 는 KSF 8003의 기준에 합격한 재료를 사용한다.</t>
         </is>
       </c>
       <c r="O77" s="1" t="inlineStr">
         <is>
-          <t>력이 나오지 않을 시에는 별도의 말뚝박기 등과 같은 보강작업을 사전에 시행해야 한다.</t>
+          <t>비계 재료의 안전성은 건설 안전과 직결되므로 강관비계와 부속재는 한국공업규격(KS)의 KSF 8002 기준에, 강관틀비계 는 KSF 8003의 기준에 합격한 재료를 사용한다.</t>
         </is>
       </c>
       <c r="P77" s="1" t="inlineStr">
@@ -7338,7 +7338,7 @@
         </is>
       </c>
       <c r="E78" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F78" s="1" t="inlineStr">
         <is>
@@ -7362,37 +7362,37 @@
       </c>
       <c r="J78" s="1" t="inlineStr">
         <is>
-          <t>2.3.7</t>
+          <t>2.3.8</t>
         </is>
       </c>
       <c r="K78" s="1" t="inlineStr">
         <is>
-          <t>양중장비</t>
+          <t>비계</t>
         </is>
       </c>
       <c r="L78" s="1" t="inlineStr">
         <is>
-          <t>양중장비</t>
+          <t>비계</t>
         </is>
       </c>
       <c r="M78" s="1" t="inlineStr">
         <is>
-          <t>다음의 그림과 같은 순서로 타워크레인의 기초를 설치한다.</t>
+          <t>강관(단관)비계의 재료는 수직재와 수평재, 그리고 가새의 재료로 사용되는 강관파이프, 강관파이프를 연 결하는 연결핀, 수직재와 수평재, 가새와 수직재 또는 수평재를 고정시키는 크램프, 그리고 비계기둥의 침하 를 방지하는 받침판 등으로 구성된다.</t>
         </is>
       </c>
       <c r="N78" s="1" t="inlineStr">
         <is>
-          <t>다음의 그림과 같은 순서로 타워크레인의 기초를 설치한다.</t>
+          <t>강관(단관)비계의 재료는 수직재와 수평재, 그리고 가새의 재료로 사용되는 강관파이프, 강관파이프를 연 결하는 연결핀, 수직재와 수평재, 가새와 수직재 또는 수평재를 고정시키는 크램프, 그리고 비계기둥의 침하 를 방지하는 받침판 등으로 구성된다.</t>
         </is>
       </c>
       <c r="O78" s="1" t="inlineStr">
         <is>
-          <t>다음의 그림과 같은 순서로 타워크레인의 기초를 설치한다.</t>
+          <t>강관(단관)비계의 재료는 수직재와 수평재, 그리고 가새의 재료로 사용되는 강관파이프, 강관파이프를 연 결하는 연결핀, 수직재와 수평재, 가새와 수직재 또는 수평재를 고정시키는 크램프, 그리고 비계기둥의 침하 를 방지하는 받침판 등으로 구성된다.</t>
         </is>
       </c>
       <c r="P78" s="1" t="inlineStr">
         <is>
-          <t>순서</t>
+          <t>분류</t>
         </is>
       </c>
       <c r="Q78" s="1" t="inlineStr"/>
@@ -7427,7 +7427,7 @@
         </is>
       </c>
       <c r="E79" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F79" s="1" t="inlineStr">
         <is>
@@ -7451,37 +7451,37 @@
       </c>
       <c r="J79" s="1" t="inlineStr">
         <is>
-          <t>2.3.7</t>
+          <t>2.3.8</t>
         </is>
       </c>
       <c r="K79" s="1" t="inlineStr">
         <is>
-          <t>양중장비</t>
+          <t>비계</t>
         </is>
       </c>
       <c r="L79" s="1" t="inlineStr">
         <is>
-          <t>양중장비</t>
+          <t>비계</t>
         </is>
       </c>
       <c r="M79" s="1" t="inlineStr">
         <is>
-          <t>스트로 나누어진다.</t>
+          <t>강관비계 하중의 한계는, 띠장은 비계기둥의 간격이 1.8m일 때 비계기둥 사이의 하중을 400kgf을 한도로 하고 비계기둥 1개당의 하중한도를 700kgf 이내로 한다.</t>
         </is>
       </c>
       <c r="N79" s="1" t="inlineStr">
         <is>
-          <t>스트로 나누어진다.</t>
+          <t>강관비계 하중의 한계는, 띠장은 비계기둥의 간격이 1.8m일 때 비계기둥 사이의 하중을 400kgf을 한도로 하고 비계기둥 1개당의 하중한도를 700kgf 이내로 한다.</t>
         </is>
       </c>
       <c r="O79" s="1" t="inlineStr">
         <is>
-          <t>스트로 나누어진다.</t>
+          <t>강관비계 하중의 한계는, 띠장은 비계기둥의 간격이 1.8m일 때 비계기둥 사이의 하중을 400kgf을 한도로 하고 비계기둥 1개당의 하중한도를 700kgf 이내로 한다.</t>
         </is>
       </c>
       <c r="P79" s="1" t="inlineStr">
         <is>
-          <t>특징</t>
+          <t>수치</t>
         </is>
       </c>
       <c r="Q79" s="1" t="inlineStr"/>
@@ -7516,7 +7516,7 @@
         </is>
       </c>
       <c r="E80" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F80" s="1" t="inlineStr">
         <is>
@@ -7540,37 +7540,37 @@
       </c>
       <c r="J80" s="1" t="inlineStr">
         <is>
-          <t>2.3.7</t>
+          <t>2.3.8</t>
         </is>
       </c>
       <c r="K80" s="1" t="inlineStr">
         <is>
-          <t>양중장비</t>
+          <t>비계</t>
         </is>
       </c>
       <c r="L80" s="1" t="inlineStr">
         <is>
-          <t>양중장비</t>
+          <t>비계</t>
         </is>
       </c>
       <c r="M80" s="1" t="inlineStr">
         <is>
-          <t>일반적으로는 인화물 겸용이 사용된다.</t>
+          <t>틀비계는 비계기둥 역할을 하는 수직틀, 2개의 수직 단관파이프 회전크램프 단관비계 고정크램프 Ø42 X 95 Ø48.6 X 48.6(0.68kg) 받침판 합판 단관(강관)비계의 부속재 출처 : www.gaseol.co.kr 틀을 잡아주는 가새, 수직틀 위에 올려놓는 수평틀, 그리고 강관비계의 부속자재인 받침대로 구성된다.</t>
         </is>
       </c>
       <c r="N80" s="1" t="inlineStr">
         <is>
-          <t>일반적으로는 인화물 겸용이 사용된다.</t>
+          <t>틀비계는 비계기둥 역할을 하는 수직틀, 2개의 수직 단관파이프 회전크램프 단관비계 고정크램프 Ø42 X 95 Ø48.6 X 48.6(0.68kg) 받침판 합판 단관(강관)비계의 부속재 출처 : www.gaseol.co.kr 틀을 잡아주는 가새, 수직틀 위에 올려놓는 수평틀, 그리고 강관비계의 부속자재인 받침대로 구성된다.</t>
         </is>
       </c>
       <c r="O80" s="1" t="inlineStr">
         <is>
-          <t>일반적으로는 인화물 겸용이 사용된다.</t>
+          <t>틀비계는 비계기둥 역할을 하는 수직틀, 2개의 수직 단관파이프 회전크램프 단관비계 고정크램프 Ø42 X 95 Ø48.6 X 48.6(0.68kg) 받침판 합판 단관(강관)비계의 부속재 출처 : www.gaseol.co.kr 틀을 잡아주는 가새, 수직틀 위에 올려놓는 수평틀, 그리고 강관비계의 부속자재인 받침대로 구성된다.</t>
         </is>
       </c>
       <c r="P80" s="1" t="inlineStr">
         <is>
-          <t>특징</t>
+          <t>분류</t>
         </is>
       </c>
       <c r="Q80" s="1" t="inlineStr"/>
@@ -7644,22 +7644,22 @@
       </c>
       <c r="M81" s="1" t="inlineStr">
         <is>
-          <t>수시로 점검하며 안전사고를 예방해야 한다.</t>
+          <t>그리고 틀비계가 높은 곳의 작업을 위한 작업대로 사용할 경우에는 작업대의 이동 에 쓰이는 바퀴, 작업틀의 안전한 위치 고정에 사용되는 삼각지지대, 작업자의 오르내림에 사 용되는 사다리, 작업자의 추락을 방지하는 안전난간대, 그리고 작업자의 발판으로 사용되는 유공발판 등이 추가된다.  비계의 종류 구조별로 살펴보면 지주비계, 달비계, 이동식 틀비계, 브라켓 비계 등으로 분류할 수 있는 데, 각각의 용도는 다음과 같다. •지 주비계 : 외줄비계, 겹비계, 쌍줄비계(틀비계) •달 비계 : 외부마감공사, 외벽청소, 고층 건물의 유리창 청소 등에 사용하는 비계 •이 동식 틀비계 : 하단부에 바퀴 를 달아 이동시키면서 사용하 는 비계 •브 라켓 비계 : 지상에서 띄우고 구조체에 브라켓을 달아서 설 치하는 비계 • 말 비계 : 2개의 일정한 모양의 형태를 가진 사다리를 정상부 에서 결합하고 다리를 벌린 모 양으로 해서 발판으로 사용되 는 것으로, 건축공사에서 실내 외줄비계 겹비계 의 마무리, 도장작업 등의 발 와 돌출보 샤클 판으로 사용하는 비계 트 • 내부수평비계 : 마감공사 시 강 설비용 덕트 및 배관시설, 건 축용 천장 마감공사 등을 하기 위해 비계기둥을 바닥에 그리 250~ 드 형태로 배치하고, 입체적으 손 권 로 조립한 비계 이 기 쌍줄비계 달비계  단관(강관)비계의 설치 비계의 설치에 있어서 작업자가 발판으로 사용하는 경우는 필히 쌍 줄비계로 설치해야 하며, 외줄비계 는 기타 방호시설의 용도로 사용되 는 것이 바람직하다.</t>
         </is>
       </c>
       <c r="N81" s="1" t="inlineStr">
         <is>
-          <t>수시로 점검하며 안전사고를 예방해야 한다.</t>
+          <t>그리고 틀비계가 높은 곳의 작업을 위한 작업대로 사용할 경우에는 작업대의 이동 에 쓰이는 바퀴, 작업틀의 안전한 위치 고정에 사용되는 삼각지지대, 작업자의 오르내림에 사 용되는 사다리, 작업자의 추락을 방지하는 안전난간대, 그리고 작업자의 발판으로 사용되는 유공발판 등이 추가된다.  비계의 종류 구조별로 살펴보면 지주비계, 달비계, 이동식 틀비계, 브라켓 비계 등으로 분류할 수 있는 데, 각각의 용도는 다음과 같다. •지 주비계 : 외줄비계, 겹비계, 쌍줄비계(틀비계) •달 비계 : 외부마감공사, 외벽청소, 고층 건물의 유리창 청소 등에 사용하는 비계 •이 동식 틀비계 : 하단부에 바퀴 를 달아 이동시키면서 사용하 는 비계 •브 라켓 비계 : 지상에서 띄우고 구조체에 브라켓을 달아서 설 치하는 비계 • 말 비계 : 2개의 일정한 모양의 형태를 가진 사다리를 정상부 에서 결합하고 다리를 벌린 모 양으로 해서 발판으로 사용되 는 것으로, 건축공사에서 실내 외줄비계 겹비계 의 마무리, 도장작업 등의 발 와 돌출보 샤클 판으로 사용하는 비계 트 • 내부수평비계 : 마감공사 시 강 설비용 덕트 및 배관시설, 건 축용 천장 마감공사 등을 하기 위해 비계기둥을 바닥에 그리 250~ 드 형태로 배치하고, 입체적으 손 권 로 조립한 비계 이 기 쌍줄비계 달비계  단관(강관)비계의 설치 비계의 설치에 있어서 작업자가 발판으로 사용하는 경우는 필히 쌍 줄비계로 설치해야 하며, 외줄비계 는 기타 방호시설의 용도로 사용되 는 것이 바람직하다.</t>
         </is>
       </c>
       <c r="O81" s="1" t="inlineStr">
         <is>
-          <t>수시로 점검하며 안전사고를 예방해야 한다.</t>
+          <t>그리고 틀비계가 높은 곳의 작업을 위한 작업대로 사용할 경우에는 작업대의 이동 에 쓰이는 바퀴, 작업틀의 안전한 위치 고정에 사용되는 삼각지지대, 작업자의 오르내림에 사 용되는 사다리, 작업자의 추락을 방지하는 안전난간대, 그리고 작업자의 발판으로 사용되는 유공발판 등이 추가된다.  비계의 종류 구조별로 살펴보면 지주비계, 달비계, 이동식 틀비계, 브라켓 비계 등으로 분류할 수 있는 데, 각각의 용도는 다음과 같다. •지 주비계 : 외줄비계, 겹비계, 쌍줄비계(틀비계) •달 비계 : 외부마감공사, 외벽청소, 고층 건물의 유리창 청소 등에 사용하는 비계 •이 동식 틀비계 : 하단부에 바퀴 를 달아 이동시키면서 사용하 는 비계 •브 라켓 비계 : 지상에서 띄우고 구조체에 브라켓을 달아서 설 치하는 비계 • 말 비계 : 2개의 일정한 모양의 형태를 가진 사다리를 정상부 에서 결합하고 다리를 벌린 모 양으로 해서 발판으로 사용되 는 것으로, 건축공사에서 실내 외줄비계 겹비계 의 마무리, 도장작업 등의 발 와 돌출보 샤클 판으로 사용하는 비계 트 • 내부수평비계 : 마감공사 시 강 설비용 덕트 및 배관시설, 건 축용 천장 마감공사 등을 하기 위해 비계기둥을 바닥에 그리 250~ 드 형태로 배치하고, 입체적으 손 권 로 조립한 비계 이 기 쌍줄비계 달비계  단관(강관)비계의 설치 비계의 설치에 있어서 작업자가 발판으로 사용하는 경우는 필히 쌍 줄비계로 설치해야 하며, 외줄비계 는 기타 방호시설의 용도로 사용되 는 것이 바람직하다.</t>
         </is>
       </c>
       <c r="P81" s="1" t="inlineStr">
         <is>
-          <t>특징</t>
+          <t>분류</t>
         </is>
       </c>
       <c r="Q81" s="1" t="inlineStr"/>
@@ -7733,22 +7733,22 @@
       </c>
       <c r="M82" s="1" t="inlineStr">
         <is>
-          <t>비계에 사용되는 재료의 종류로는 통나무, 강관파이프, 그리고 강관틀이 주로 사용된다.</t>
+          <t>그리고 본 구 조물에서 비계의 이격거리는 대개 외줄비계는 50~70cm, 쌍줄비계 는 약 30~50cm 정도 이격되게 설 치해 작업자가 비계 위에서 작업을 원활하게 수행할 수 있도록 하는 말비계 틀비계 것이 바람직하다.</t>
         </is>
       </c>
       <c r="N82" s="1" t="inlineStr">
         <is>
-          <t>비계에 사용되는 재료의 종류로는 통나무, 강관파이프, 그리고 강관틀이 주로 사용된다.</t>
+          <t>그리고 본 구 조물에서 비계의 이격거리는 대개 외줄비계는 50~70cm, 쌍줄비계 는 약 30~50cm 정도 이격되게 설 치해 작업자가 비계 위에서 작업을 원활하게 수행할 수 있도록 하는 말비계 틀비계 것이 바람직하다.</t>
         </is>
       </c>
       <c r="O82" s="1" t="inlineStr">
         <is>
-          <t>비계에 사용되는 재료의 종류로는 통나무, 강관파이프, 그리고 강관틀이 주로 사용된다.</t>
+          <t>그리고 본 구 조물에서 비계의 이격거리는 대개 외줄비계는 50~70cm, 쌍줄비계 는 약 30~50cm 정도 이격되게 설 치해 작업자가 비계 위에서 작업을 원활하게 수행할 수 있도록 하는 말비계 틀비계 것이 바람직하다.</t>
         </is>
       </c>
       <c r="P82" s="1" t="inlineStr">
         <is>
-          <t>분류</t>
+          <t>수치</t>
         </is>
       </c>
       <c r="Q82" s="1" t="inlineStr"/>
@@ -7822,22 +7822,22 @@
       </c>
       <c r="M83" s="1" t="inlineStr">
         <is>
-          <t>러나 통나무는 비계 재료로서 거의 사용되지 않고 있는 실정이다.</t>
+          <t>그리고 쌍줄비계 의 경우 안쪽 비계틀과 바깥쪽 비 계틀의 간격, 즉 장선 방향의 비계기둥 이격거리는 45~55cm 정도로 하는 것이 바람직하다.</t>
         </is>
       </c>
       <c r="N83" s="1" t="inlineStr">
         <is>
-          <t>러나 통나무는 비계 재료로서 거의 사용되지 않고 있는 실정이다.</t>
+          <t>그리고 쌍줄비계 의 경우 안쪽 비계틀과 바깥쪽 비 계틀의 간격, 즉 장선 방향의 비계기둥 이격거리는 45~55cm 정도로 하는 것이 바람직하다.</t>
         </is>
       </c>
       <c r="O83" s="1" t="inlineStr">
         <is>
-          <t>러나 통나무는 비계 재료로서 거의 사용되지 않고 있는 실정이다.</t>
+          <t>그리고 쌍줄비계 의 경우 안쪽 비계틀과 바깥쪽 비 계틀의 간격, 즉 장선 방향의 비계기둥 이격거리는 45~55cm 정도로 하는 것이 바람직하다.</t>
         </is>
       </c>
       <c r="P83" s="1" t="inlineStr">
         <is>
-          <t>특징</t>
+          <t>수치</t>
         </is>
       </c>
       <c r="Q83" s="1" t="inlineStr"/>
@@ -7911,22 +7911,22 @@
       </c>
       <c r="M84" s="1" t="inlineStr">
         <is>
-          <t>는 KSF 8003의 기준에 합격한 재료를 사용한다.</t>
+          <t>그 이유는 ① 작업발판의 최소폭이 4cm인 규정을 만족시키고, ② 기성 경량유공발판의 폭이 45cm 제품이므로 약간의 여유를 두어서 작업하는 것이 바람직한데, 규준에서 정하고 있는 틈 새가 없도록 해야 한다는 규정을 만족시켜 틈새로 적 재한 자재나 기타 작업공구 등이 추락하는 것을 막기 위해서이다.</t>
         </is>
       </c>
       <c r="N84" s="1" t="inlineStr">
         <is>
-          <t>는 KSF 8003의 기준에 합격한 재료를 사용한다.</t>
+          <t>그 이유는 ① 작업발판의 최소폭이 4cm인 규정을 만족시키고, ② 기성 경량유공발판의 폭이 45cm 제품이므로 약간의 여유를 두어서 작업하는 것이 바람직한데, 규준에서 정하고 있는 틈 새가 없도록 해야 한다는 규정을 만족시켜 틈새로 적 재한 자재나 기타 작업공구 등이 추락하는 것을 막기 위해서이다.</t>
         </is>
       </c>
       <c r="O84" s="1" t="inlineStr">
         <is>
-          <t>는 KSF 8003의 기준에 합격한 재료를 사용한다.</t>
+          <t>그 이유는 ① 작업발판의 최소폭이 4cm인 규정을 만족시키고, ② 기성 경량유공발판의 폭이 45cm 제품이므로 약간의 여유를 두어서 작업하는 것이 바람직한데, 규준에서 정하고 있는 틈 새가 없도록 해야 한다는 규정을 만족시켜 틈새로 적 재한 자재나 기타 작업공구 등이 추락하는 것을 막기 위해서이다.</t>
         </is>
       </c>
       <c r="P84" s="1" t="inlineStr">
         <is>
-          <t>특징</t>
+          <t>수치</t>
         </is>
       </c>
       <c r="Q84" s="1" t="inlineStr"/>
@@ -8000,22 +8000,22 @@
       </c>
       <c r="M85" s="1" t="inlineStr">
         <is>
-          <t>를 방지하는 받침판 등으로 구성된다.</t>
+          <t>최근에는 단관비계를 설치할 때 비계기둥을 지상에 서부터 설치하지 않고 지상에서 1개 층 또는 2개 층 상부에서부터 설치해 향후 부대토목이나 조경공사를 진행하는 데 비계구조물이 지장을 초래하는 것을 방지 하는 방법이 널리 사용된다.</t>
         </is>
       </c>
       <c r="N85" s="1" t="inlineStr">
         <is>
-          <t>를 방지하는 받침판 등으로 구성된다.</t>
+          <t>최근에는 단관비계를 설치할 때 비계기둥을 지상에 서부터 설치하지 않고 지상에서 1개 층 또는 2개 층 상부에서부터 설치해 향후 부대토목이나 조경공사를 진행하는 데 비계구조물이 지장을 초래하는 것을 방지 하는 방법이 널리 사용된다.</t>
         </is>
       </c>
       <c r="O85" s="1" t="inlineStr">
         <is>
-          <t>를 방지하는 받침판 등으로 구성된다.</t>
+          <t>최근에는 단관비계를 설치할 때 비계기둥을 지상에 서부터 설치하지 않고 지상에서 1개 층 또는 2개 층 상부에서부터 설치해 향후 부대토목이나 조경공사를 진행하는 데 비계구조물이 지장을 초래하는 것을 방지 하는 방법이 널리 사용된다.</t>
         </is>
       </c>
       <c r="P85" s="1" t="inlineStr">
         <is>
-          <t>분류</t>
+          <t>특징</t>
         </is>
       </c>
       <c r="Q85" s="1" t="inlineStr"/>
@@ -8089,17 +8089,17 @@
       </c>
       <c r="M86" s="1" t="inlineStr">
         <is>
-          <t>하고 비계기둥 1개당의 하중한도를 700kgf 이내로 한다.</t>
+          <t>단관비계 브라켓을 이용한 비계 설치 슬래브 쌍줄용 브라켓 그리고 비계를 벽에 고정하는 벽고정은 수평·수직으로 5m 간격으로 해서 구조물에 비계틀 이 너무 근접하거나 바깥쪽으로 벌어지는 것을 방지해야 한다.</t>
         </is>
       </c>
       <c r="N86" s="1" t="inlineStr">
         <is>
-          <t>하고 비계기둥 1개당의 하중한도를 700kgf 이내로 한다.</t>
+          <t>단관비계 브라켓을 이용한 비계 설치 슬래브 쌍줄용 브라켓 그리고 비계를 벽에 고정하는 벽고정은 수평·수직으로 5m 간격으로 해서 구조물에 비계틀 이 너무 근접하거나 바깥쪽으로 벌어지는 것을 방지해야 한다.</t>
         </is>
       </c>
       <c r="O86" s="1" t="inlineStr">
         <is>
-          <t>하고 비계기둥 1개당의 하중한도를 700kgf 이내로 한다.</t>
+          <t>단관비계 브라켓을 이용한 비계 설치 슬래브 쌍줄용 브라켓 그리고 비계를 벽에 고정하는 벽고정은 수평·수직으로 5m 간격으로 해서 구조물에 비계틀 이 너무 근접하거나 바깥쪽으로 벌어지는 것을 방지해야 한다.</t>
         </is>
       </c>
       <c r="P86" s="1" t="inlineStr">
@@ -8178,17 +8178,17 @@
       </c>
       <c r="M87" s="1" t="inlineStr">
         <is>
-          <t>Ø48.</t>
+          <t>벽 연결에 사용되는 별도의 기 성제품을 사용하기도 한다.</t>
         </is>
       </c>
       <c r="N87" s="1" t="inlineStr">
         <is>
-          <t>Ø48.</t>
+          <t>벽 연결에 사용되는 별도의 기 성제품을 사용하기도 한다.</t>
         </is>
       </c>
       <c r="O87" s="1" t="inlineStr">
         <is>
-          <t>Ø48.</t>
+          <t>벽 연결에 사용되는 별도의 기 성제품을 사용하기도 한다.</t>
         </is>
       </c>
       <c r="P87" s="1" t="inlineStr">
@@ -8267,17 +8267,17 @@
       </c>
       <c r="M88" s="1" t="inlineStr">
         <is>
-          <t>6 X 48.</t>
+          <t>단관비계를 조립해 사용하는 과정에서는 다음 각 호의 사항을 준수해야 한다.</t>
         </is>
       </c>
       <c r="N88" s="1" t="inlineStr">
         <is>
-          <t>6 X 48.</t>
+          <t>단관비계를 조립해 사용하는 과정에서는 다음 각 호의 사항을 준수해야 한다.</t>
         </is>
       </c>
       <c r="O88" s="1" t="inlineStr">
         <is>
-          <t>6 X 48.</t>
+          <t>단관비계를 조립해 사용하는 과정에서는 다음 각 호의 사항을 준수해야 한다.</t>
         </is>
       </c>
       <c r="P88" s="1" t="inlineStr">
@@ -8356,17 +8356,17 @@
       </c>
       <c r="M89" s="1" t="inlineStr">
         <is>
-          <t>6(0.</t>
+          <t>① 하단부에는 깔판(밑받침철물), 받침목 등을 사용하고 밑둥잡이를 설치해야 한다.</t>
         </is>
       </c>
       <c r="N89" s="1" t="inlineStr">
         <is>
-          <t>6(0.</t>
+          <t>① 하단부에는 깔판(밑받침철물), 받침목 등을 사용하고 밑둥잡이를 설치해야 한다.</t>
         </is>
       </c>
       <c r="O89" s="1" t="inlineStr">
         <is>
-          <t>6(0.</t>
+          <t>① 하단부에는 깔판(밑받침철물), 받침목 등을 사용하고 밑둥잡이를 설치해야 한다.</t>
         </is>
       </c>
       <c r="P89" s="1" t="inlineStr">
@@ -8445,22 +8445,22 @@
       </c>
       <c r="M90" s="1" t="inlineStr">
         <is>
-          <t>Ø42 X 225(0.</t>
+          <t>② 비 계기둥 간격은 띠장 방향에서는 1.5m 내지 1.8m, 장선 방향에서는 1.5m 이하여야 하 며, 비계기둥의 최고부로부터 아래 방향으로 31m를 넘는 비계기둥은 2본의 강관으로 묶 어 세워야 한다.</t>
         </is>
       </c>
       <c r="N90" s="1" t="inlineStr">
         <is>
-          <t>Ø42 X 225(0.</t>
+          <t>② 비 계기둥 간격은 띠장 방향에서는 1.5m 내지 1.8m, 장선 방향에서는 1.5m 이하여야 하 며, 비계기둥의 최고부로부터 아래 방향으로 31m를 넘는 비계기둥은 2본의 강관으로 묶 어 세워야 한다.</t>
         </is>
       </c>
       <c r="O90" s="1" t="inlineStr">
         <is>
-          <t>Ø42 X 225(0.</t>
+          <t>② 비 계기둥 간격은 띠장 방향에서는 1.5m 내지 1.8m, 장선 방향에서는 1.5m 이하여야 하 며, 비계기둥의 최고부로부터 아래 방향으로 31m를 넘는 비계기둥은 2본의 강관으로 묶 어 세워야 한다.</t>
         </is>
       </c>
       <c r="P90" s="1" t="inlineStr">
         <is>
-          <t>특징</t>
+          <t>수치</t>
         </is>
       </c>
       <c r="Q90" s="1" t="inlineStr"/>
@@ -8534,22 +8534,22 @@
       </c>
       <c r="M91" s="1" t="inlineStr">
         <is>
-          <t>Ø42 X 95 Ø48.</t>
+          <t>③ 띠 장 간격은 1.5m 이하로 설치해야 하며, 지상에서 첫 번째 띠장은 높이 2m 이하의 위치 에 설치해야 한다.</t>
         </is>
       </c>
       <c r="N91" s="1" t="inlineStr">
         <is>
-          <t>Ø42 X 95 Ø48.</t>
+          <t>③ 띠 장 간격은 1.5m 이하로 설치해야 하며, 지상에서 첫 번째 띠장은 높이 2m 이하의 위치 에 설치해야 한다.</t>
         </is>
       </c>
       <c r="O91" s="1" t="inlineStr">
         <is>
-          <t>Ø42 X 95 Ø48.</t>
+          <t>③ 띠 장 간격은 1.5m 이하로 설치해야 하며, 지상에서 첫 번째 띠장은 높이 2m 이하의 위치 에 설치해야 한다.</t>
         </is>
       </c>
       <c r="P91" s="1" t="inlineStr">
         <is>
-          <t>특징</t>
+          <t>수치</t>
         </is>
       </c>
       <c r="Q91" s="1" t="inlineStr"/>
@@ -8623,22 +8623,22 @@
       </c>
       <c r="M92" s="1" t="inlineStr">
         <is>
-          <t>6 X 48.</t>
+          <t>이하 기둥 &lt;입면도&gt; 이하 비계 단관쌍줄비계의 &lt;평면도&gt; ④ 장선 간격은 1.5m 이하로 설치하며, 비계기둥과 띠장의 교차부에서는 비계기둥에 결속 하고, 그 중간 부분에서는 띠장에 결속한다.</t>
         </is>
       </c>
       <c r="N92" s="1" t="inlineStr">
         <is>
-          <t>6 X 48.</t>
+          <t>이하 기둥 &lt;입면도&gt; 이하 비계 단관쌍줄비계의 &lt;평면도&gt; ④ 장선 간격은 1.5m 이하로 설치하며, 비계기둥과 띠장의 교차부에서는 비계기둥에 결속 하고, 그 중간 부분에서는 띠장에 결속한다.</t>
         </is>
       </c>
       <c r="O92" s="1" t="inlineStr">
         <is>
-          <t>6 X 48.</t>
+          <t>이하 기둥 &lt;입면도&gt; 이하 비계 단관쌍줄비계의 &lt;평면도&gt; ④ 장선 간격은 1.5m 이하로 설치하며, 비계기둥과 띠장의 교차부에서는 비계기둥에 결속 하고, 그 중간 부분에서는 띠장에 결속한다.</t>
         </is>
       </c>
       <c r="P92" s="1" t="inlineStr">
         <is>
-          <t>특징</t>
+          <t>수치</t>
         </is>
       </c>
       <c r="Q92" s="1" t="inlineStr"/>
@@ -8712,17 +8712,17 @@
       </c>
       <c r="M93" s="1" t="inlineStr">
         <is>
-          <t>6(0.</t>
+          <t>⑤ 비계기둥 간의 적재하중은 400kg을 초과하지 않도록 해야 한다.</t>
         </is>
       </c>
       <c r="N93" s="1" t="inlineStr">
         <is>
-          <t>6(0.</t>
+          <t>⑤ 비계기둥 간의 적재하중은 400kg을 초과하지 않도록 해야 한다.</t>
         </is>
       </c>
       <c r="O93" s="1" t="inlineStr">
         <is>
-          <t>6(0.</t>
+          <t>⑤ 비계기둥 간의 적재하중은 400kg을 초과하지 않도록 해야 한다.</t>
         </is>
       </c>
       <c r="P93" s="1" t="inlineStr">
@@ -8801,22 +8801,22 @@
       </c>
       <c r="M94" s="1" t="inlineStr">
         <is>
-          <t>구성된다.</t>
+          <t>⑥ 벽 연결은 수직으로 5m, 수평으로 5m 이내마다 연결해야 한다.</t>
         </is>
       </c>
       <c r="N94" s="1" t="inlineStr">
         <is>
-          <t>구성된다.</t>
+          <t>⑥ 벽 연결은 수직으로 5m, 수평으로 5m 이내마다 연결해야 한다.</t>
         </is>
       </c>
       <c r="O94" s="1" t="inlineStr">
         <is>
-          <t>구성된다.</t>
+          <t>⑥ 벽 연결은 수직으로 5m, 수평으로 5m 이내마다 연결해야 한다.</t>
         </is>
       </c>
       <c r="P94" s="1" t="inlineStr">
         <is>
-          <t>분류</t>
+          <t>수치</t>
         </is>
       </c>
       <c r="Q94" s="1" t="inlineStr"/>
@@ -8890,22 +8890,22 @@
       </c>
       <c r="M95" s="1" t="inlineStr">
         <is>
-          <t>유공발판 등이 추가된다.</t>
+          <t>⑦ 기 둥 간격 10m마다 45° 각도의 처마 방향 가새를 설치해야 하며, 모든 비계기둥은 가새 에 결속해야 한다.</t>
         </is>
       </c>
       <c r="N95" s="1" t="inlineStr">
         <is>
-          <t>유공발판 등이 추가된다.</t>
+          <t>⑦ 기 둥 간격 10m마다 45° 각도의 처마 방향 가새를 설치해야 하며, 모든 비계기둥은 가새 에 결속해야 한다.</t>
         </is>
       </c>
       <c r="O95" s="1" t="inlineStr">
         <is>
-          <t>유공발판 등이 추가된다.</t>
+          <t>⑦ 기 둥 간격 10m마다 45° 각도의 처마 방향 가새를 설치해야 하며, 모든 비계기둥은 가새 에 결속해야 한다.</t>
         </is>
       </c>
       <c r="P95" s="1" t="inlineStr">
         <is>
-          <t>특징</t>
+          <t>수치</t>
         </is>
       </c>
       <c r="Q95" s="1" t="inlineStr"/>
@@ -8979,17 +8979,17 @@
       </c>
       <c r="M96" s="1" t="inlineStr">
         <is>
-          <t>데, 각각의 용도는 다음과 같다.</t>
+          <t>⑧ 작업대에는 표준안전난간을 설치해야 한다.</t>
         </is>
       </c>
       <c r="N96" s="1" t="inlineStr">
         <is>
-          <t>데, 각각의 용도는 다음과 같다.</t>
+          <t>⑧ 작업대에는 표준안전난간을 설치해야 한다.</t>
         </is>
       </c>
       <c r="O96" s="1" t="inlineStr">
         <is>
-          <t>데, 각각의 용도는 다음과 같다.</t>
+          <t>⑧ 작업대에는 표준안전난간을 설치해야 한다.</t>
         </is>
       </c>
       <c r="P96" s="1" t="inlineStr">
@@ -9068,17 +9068,17 @@
       </c>
       <c r="M97" s="1" t="inlineStr">
         <is>
-          <t>는 것이 바람직하다.</t>
+          <t>⑨ 작업대의 구조는 추락 및 낙하물 방지장치를 설치해야 한다.</t>
         </is>
       </c>
       <c r="N97" s="1" t="inlineStr">
         <is>
-          <t>는 것이 바람직하다.</t>
+          <t>⑨ 작업대의 구조는 추락 및 낙하물 방지장치를 설치해야 한다.</t>
         </is>
       </c>
       <c r="O97" s="1" t="inlineStr">
         <is>
-          <t>는 것이 바람직하다.</t>
+          <t>⑨ 작업대의 구조는 추락 및 낙하물 방지장치를 설치해야 한다.</t>
         </is>
       </c>
       <c r="P97" s="1" t="inlineStr">
@@ -9157,17 +9157,17 @@
       </c>
       <c r="M98" s="1" t="inlineStr">
         <is>
-          <t>것이 바람직하다.</t>
+          <t>⑩ 작업발판 설치가 필요한 경우에는 쌍줄비계여야 하며, 연결 및 이음철물은 가설 기자재 성능검정규격에 규정된 것을 사용해야 한다.  낙하물 방지망 산업안전보건기준에 관한 규칙 제14조와 42조의 규정에 의거 작업으로 인해 물체가 낙하 또 는 비래할 위험이 있는 때에는 낙하물 방지망 또는 방호선반의 설치, 출입금지구역의 설정, 보 호구의 착용 등 위험 방지를 위해 필요한 조치를 해야 한다.</t>
         </is>
       </c>
       <c r="N98" s="1" t="inlineStr">
         <is>
-          <t>것이 바람직하다.</t>
+          <t>⑩ 작업발판 설치가 필요한 경우에는 쌍줄비계여야 하며, 연결 및 이음철물은 가설 기자재 성능검정규격에 규정된 것을 사용해야 한다.  낙하물 방지망 산업안전보건기준에 관한 규칙 제14조와 42조의 규정에 의거 작업으로 인해 물체가 낙하 또 는 비래할 위험이 있는 때에는 낙하물 방지망 또는 방호선반의 설치, 출입금지구역의 설정, 보 호구의 착용 등 위험 방지를 위해 필요한 조치를 해야 한다.</t>
         </is>
       </c>
       <c r="O98" s="1" t="inlineStr">
         <is>
-          <t>것이 바람직하다.</t>
+          <t>⑩ 작업발판 설치가 필요한 경우에는 쌍줄비계여야 하며, 연결 및 이음철물은 가설 기자재 성능검정규격에 규정된 것을 사용해야 한다.  낙하물 방지망 산업안전보건기준에 관한 규칙 제14조와 42조의 규정에 의거 작업으로 인해 물체가 낙하 또 는 비래할 위험이 있는 때에는 낙하물 방지망 또는 방호선반의 설치, 출입금지구역의 설정, 보 호구의 착용 등 위험 방지를 위해 필요한 조치를 해야 한다.</t>
         </is>
       </c>
       <c r="P98" s="1" t="inlineStr">
@@ -9246,17 +9246,17 @@
       </c>
       <c r="M99" s="1" t="inlineStr">
         <is>
-          <t>계틀의 간격, 즉 장선 방향의 비계기둥 이격거리는 45~55cm 정도로 하는 것이 바람직하다.</t>
+          <t>낙하물 방지망을 설치할 때에는 높이 10m 이내마다 또는 3개 층 이내마다 설치하고 내민 길 이는 벽면으로부터 2m 이상으로 해야 하며 수평면과의 각도는 20° 내지 30°를 유지하도록 한 다.</t>
         </is>
       </c>
       <c r="N99" s="1" t="inlineStr">
         <is>
-          <t>계틀의 간격, 즉 장선 방향의 비계기둥 이격거리는 45~55cm 정도로 하는 것이 바람직하다.</t>
+          <t>낙하물 방지망을 설치할 때에는 높이 10m 이내마다 또는 3개 층 이내마다 설치하고 내민 길 이는 벽면으로부터 2m 이상으로 해야 하며 수평면과의 각도는 20° 내지 30°를 유지하도록 한 다.</t>
         </is>
       </c>
       <c r="O99" s="1" t="inlineStr">
         <is>
-          <t>계틀의 간격, 즉 장선 방향의 비계기둥 이격거리는 45~55cm 정도로 하는 것이 바람직하다.</t>
+          <t>낙하물 방지망을 설치할 때에는 높이 10m 이내마다 또는 3개 층 이내마다 설치하고 내민 길 이는 벽면으로부터 2m 이상으로 해야 하며 수평면과의 각도는 20° 내지 30°를 유지하도록 한 다.</t>
         </is>
       </c>
       <c r="P99" s="1" t="inlineStr">
@@ -9335,17 +9335,17 @@
       </c>
       <c r="M100" s="1" t="inlineStr">
         <is>
-          <t>위해서이다.</t>
+          <t>또한 외부비계와 벽체 사이에 틈새가 없도록 안전망을 설치한다.</t>
         </is>
       </c>
       <c r="N100" s="1" t="inlineStr">
         <is>
-          <t>위해서이다.</t>
+          <t>또한 외부비계와 벽체 사이에 틈새가 없도록 안전망을 설치한다.</t>
         </is>
       </c>
       <c r="O100" s="1" t="inlineStr">
         <is>
-          <t>위해서이다.</t>
+          <t>또한 외부비계와 벽체 사이에 틈새가 없도록 안전망을 설치한다.</t>
         </is>
       </c>
       <c r="P100" s="1" t="inlineStr">
@@ -9424,22 +9424,22 @@
       </c>
       <c r="M101" s="1" t="inlineStr">
         <is>
-          <t>하는 방법이 널리 사용된다.</t>
+          <t>낙하물 방지망 주 출입구 방호선반 호이스트 방호선반  틀비계 강관틀비계를 조립해 사용함에 있어서 다음의 각 사항을 준수해야 한다.</t>
         </is>
       </c>
       <c r="N101" s="1" t="inlineStr">
         <is>
-          <t>하는 방법이 널리 사용된다.</t>
+          <t>낙하물 방지망 주 출입구 방호선반 호이스트 방호선반  틀비계 강관틀비계를 조립해 사용함에 있어서 다음의 각 사항을 준수해야 한다.</t>
         </is>
       </c>
       <c r="O101" s="1" t="inlineStr">
         <is>
-          <t>하는 방법이 널리 사용된다.</t>
+          <t>낙하물 방지망 주 출입구 방호선반 호이스트 방호선반  틀비계 강관틀비계를 조립해 사용함에 있어서 다음의 각 사항을 준수해야 한다.</t>
         </is>
       </c>
       <c r="P101" s="1" t="inlineStr">
         <is>
-          <t>특징</t>
+          <t>순서</t>
         </is>
       </c>
       <c r="Q101" s="1" t="inlineStr"/>
@@ -9513,17 +9513,17 @@
       </c>
       <c r="M102" s="1" t="inlineStr">
         <is>
-          <t>이 너무 근접하거나 바깥쪽으로 벌어지는 것을 방지해야 한다.</t>
+          <t>① 비 계기둥의 밑둥에는 밑받침철물을 사용해야 하며, 밑받침에 고저차가 있는 경우 조절형 밑받침철물을 사용해 각각의 강관틀비계가 항상 수평·수직을 유지하도록 한다.</t>
         </is>
       </c>
       <c r="N102" s="1" t="inlineStr">
         <is>
-          <t>이 너무 근접하거나 바깥쪽으로 벌어지는 것을 방지해야 한다.</t>
+          <t>① 비 계기둥의 밑둥에는 밑받침철물을 사용해야 하며, 밑받침에 고저차가 있는 경우 조절형 밑받침철물을 사용해 각각의 강관틀비계가 항상 수평·수직을 유지하도록 한다.</t>
         </is>
       </c>
       <c r="O102" s="1" t="inlineStr">
         <is>
-          <t>이 너무 근접하거나 바깥쪽으로 벌어지는 것을 방지해야 한다.</t>
+          <t>① 비 계기둥의 밑둥에는 밑받침철물을 사용해야 하며, 밑받침에 고저차가 있는 경우 조절형 밑받침철물을 사용해 각각의 강관틀비계가 항상 수평·수직을 유지하도록 한다.</t>
         </is>
       </c>
       <c r="P102" s="1" t="inlineStr">
@@ -9602,22 +9602,22 @@
       </c>
       <c r="M103" s="1" t="inlineStr">
         <is>
-          <t>성제품을 사용하기도 한다.</t>
+          <t>② 전 체 높이는 40m를 초과할 수 없으며, 20m 를 초과할 경우 주틀의 높이를 2m 이내로 하고 주틀 간의 간격은 1.8m 이하로 한다.</t>
         </is>
       </c>
       <c r="N103" s="1" t="inlineStr">
         <is>
-          <t>성제품을 사용하기도 한다.</t>
+          <t>② 전 체 높이는 40m를 초과할 수 없으며, 20m 를 초과할 경우 주틀의 높이를 2m 이내로 하고 주틀 간의 간격은 1.8m 이하로 한다.</t>
         </is>
       </c>
       <c r="O103" s="1" t="inlineStr">
         <is>
-          <t>성제품을 사용하기도 한다.</t>
+          <t>② 전 체 높이는 40m를 초과할 수 없으며, 20m 를 초과할 경우 주틀의 높이를 2m 이내로 하고 주틀 간의 간격은 1.8m 이하로 한다.</t>
         </is>
       </c>
       <c r="P103" s="1" t="inlineStr">
         <is>
-          <t>특징</t>
+          <t>수치</t>
         </is>
       </c>
       <c r="Q103" s="1" t="inlineStr"/>
@@ -9691,17 +9691,17 @@
       </c>
       <c r="M104" s="1" t="inlineStr">
         <is>
-          <t>단관비계를 조립해 사용하는 과정에서는 다음 각 호의 사항을 준수해야 한다.</t>
+          <t>③ 주틀 간에 교차가새를 설치하고 최상층 및 5층 ③ 이내마다 수평재를 설치해야 한다.</t>
         </is>
       </c>
       <c r="N104" s="1" t="inlineStr">
         <is>
-          <t>단관비계를 조립해 사용하는 과정에서는 다음 각 호의 사항을 준수해야 한다.</t>
+          <t>③ 주틀 간에 교차가새를 설치하고 최상층 및 5층 ③ 이내마다 수평재를 설치해야 한다.</t>
         </is>
       </c>
       <c r="O104" s="1" t="inlineStr">
         <is>
-          <t>단관비계를 조립해 사용하는 과정에서는 다음 각 호의 사항을 준수해야 한다.</t>
+          <t>③ 주틀 간에 교차가새를 설치하고 최상층 및 5층 ③ 이내마다 수평재를 설치해야 한다.</t>
         </is>
       </c>
       <c r="P104" s="1" t="inlineStr">
@@ -9780,22 +9780,22 @@
       </c>
       <c r="M105" s="1" t="inlineStr">
         <is>
-          <t>① 하단부에는 깔판(밑받침철물), 받침목 등을 사용하고 밑둥잡이를 설치해야 한다.</t>
+          <t>④ ④ 벽 연결은 구조체와 수직 방향으로 6m, 수 평 방향으로 8m 이내마다 연결해야 한다.</t>
         </is>
       </c>
       <c r="N105" s="1" t="inlineStr">
         <is>
-          <t>① 하단부에는 깔판(밑받침철물), 받침목 등을 사용하고 밑둥잡이를 설치해야 한다.</t>
+          <t>④ ④ 벽 연결은 구조체와 수직 방향으로 6m, 수 평 방향으로 8m 이내마다 연결해야 한다.</t>
         </is>
       </c>
       <c r="O105" s="1" t="inlineStr">
         <is>
-          <t>① 하단부에는 깔판(밑받침철물), 받침목 등을 사용하고 밑둥잡이를 설치해야 한다.</t>
+          <t>④ ④ 벽 연결은 구조체와 수직 방향으로 6m, 수 평 방향으로 8m 이내마다 연결해야 한다.</t>
         </is>
       </c>
       <c r="P105" s="1" t="inlineStr">
         <is>
-          <t>특징</t>
+          <t>수치</t>
         </is>
       </c>
       <c r="Q105" s="1" t="inlineStr"/>
@@ -9869,17 +9869,17 @@
       </c>
       <c r="M106" s="1" t="inlineStr">
         <is>
-          <t>② 비 계기둥 간격은 띠장 방향에서는 1.</t>
+          <t>⑤ 띠장 방향으로 길이가 4m 이하이고 높이 10m를 초과하는 경우 높이 10m 이내마다 ① 띠장 방향으로 버팀기둥을 설치해야 한다.</t>
         </is>
       </c>
       <c r="N106" s="1" t="inlineStr">
         <is>
-          <t>② 비 계기둥 간격은 띠장 방향에서는 1.</t>
+          <t>⑤ 띠장 방향으로 길이가 4m 이하이고 높이 10m를 초과하는 경우 높이 10m 이내마다 ① 띠장 방향으로 버팀기둥을 설치해야 한다.</t>
         </is>
       </c>
       <c r="O106" s="1" t="inlineStr">
         <is>
-          <t>② 비 계기둥 간격은 띠장 방향에서는 1.</t>
+          <t>⑤ 띠장 방향으로 길이가 4m 이하이고 높이 10m를 초과하는 경우 높이 10m 이내마다 ① 띠장 방향으로 버팀기둥을 설치해야 한다.</t>
         </is>
       </c>
       <c r="P106" s="1" t="inlineStr">
@@ -9958,22 +9958,22 @@
       </c>
       <c r="M107" s="1" t="inlineStr">
         <is>
-          <t>5m 내지 1.</t>
+          <t>틀비계 ① 받침판 ② 수직틀 ③ 암록크 ④ 가새 ⑥ 그 외의 다른 사항은 단관비계에 준한다.</t>
         </is>
       </c>
       <c r="N107" s="1" t="inlineStr">
         <is>
-          <t>5m 내지 1.</t>
+          <t>틀비계 ① 받침판 ② 수직틀 ③ 암록크 ④ 가새 ⑥ 그 외의 다른 사항은 단관비계에 준한다.</t>
         </is>
       </c>
       <c r="O107" s="1" t="inlineStr">
         <is>
-          <t>5m 내지 1.</t>
+          <t>틀비계 ① 받침판 ② 수직틀 ③ 암록크 ④ 가새 ⑥ 그 외의 다른 사항은 단관비계에 준한다.</t>
         </is>
       </c>
       <c r="P107" s="1" t="inlineStr">
         <is>
-          <t>수치</t>
+          <t>특징</t>
         </is>
       </c>
       <c r="Q107" s="1" t="inlineStr"/>
@@ -10047,22 +10047,22 @@
       </c>
       <c r="M108" s="1" t="inlineStr">
         <is>
-          <t>8m, 장선 방향에서는 1.</t>
+          <t>⑤ 연결핀 ⑥ 수평틀  작업발판 작업자가 추락하거나 넘어질 위험이 있는 장소에서 작업을 할 때에는 작업발판을 설치해야 한다.</t>
         </is>
       </c>
       <c r="N108" s="1" t="inlineStr">
         <is>
-          <t>8m, 장선 방향에서는 1.</t>
+          <t>⑤ 연결핀 ⑥ 수평틀  작업발판 작업자가 추락하거나 넘어질 위험이 있는 장소에서 작업을 할 때에는 작업발판을 설치해야 한다.</t>
         </is>
       </c>
       <c r="O108" s="1" t="inlineStr">
         <is>
-          <t>8m, 장선 방향에서는 1.</t>
+          <t>⑤ 연결핀 ⑥ 수평틀  작업발판 작업자가 추락하거나 넘어질 위험이 있는 장소에서 작업을 할 때에는 작업발판을 설치해야 한다.</t>
         </is>
       </c>
       <c r="P108" s="1" t="inlineStr">
         <is>
-          <t>수치</t>
+          <t>특징</t>
         </is>
       </c>
       <c r="Q108" s="1" t="inlineStr"/>
@@ -10136,22 +10136,22 @@
       </c>
       <c r="M109" s="1" t="inlineStr">
         <is>
-          <t>어 세워야 한다.</t>
+          <t>작업발판 간의 틈은 3cm 이하로 해야 하고, 이탈되거나 탈락하지 않도록 2개 이상의 지 지물에 고정해야 한다.</t>
         </is>
       </c>
       <c r="N109" s="1" t="inlineStr">
         <is>
-          <t>어 세워야 한다.</t>
+          <t>작업발판 간의 틈은 3cm 이하로 해야 하고, 이탈되거나 탈락하지 않도록 2개 이상의 지 지물에 고정해야 한다.</t>
         </is>
       </c>
       <c r="O109" s="1" t="inlineStr">
         <is>
-          <t>어 세워야 한다.</t>
+          <t>작업발판 간의 틈은 3cm 이하로 해야 하고, 이탈되거나 탈락하지 않도록 2개 이상의 지 지물에 고정해야 한다.</t>
         </is>
       </c>
       <c r="P109" s="1" t="inlineStr">
         <is>
-          <t>특징</t>
+          <t>수치</t>
         </is>
       </c>
       <c r="Q109" s="1" t="inlineStr"/>
@@ -10225,17 +10225,17 @@
       </c>
       <c r="M110" s="1" t="inlineStr">
         <is>
-          <t>③ 띠 장 간격은 1.</t>
+          <t>작업발판 끝부분의 돌출길이는 10cm 이상 20cm 이하로 해야 한다.</t>
         </is>
       </c>
       <c r="N110" s="1" t="inlineStr">
         <is>
-          <t>③ 띠 장 간격은 1.</t>
+          <t>작업발판 끝부분의 돌출길이는 10cm 이상 20cm 이하로 해야 한다.</t>
         </is>
       </c>
       <c r="O110" s="1" t="inlineStr">
         <is>
-          <t>③ 띠 장 간격은 1.</t>
+          <t>작업발판 끝부분의 돌출길이는 10cm 이상 20cm 이하로 해야 한다.</t>
         </is>
       </c>
       <c r="P110" s="1" t="inlineStr">
@@ -10314,17 +10314,17 @@
       </c>
       <c r="M111" s="1" t="inlineStr">
         <is>
-          <t>에 설치해야 한다.</t>
+          <t>비계발판의 자재로는 최근에 기성제품인 경량유공발판을 주로 사용한다.</t>
         </is>
       </c>
       <c r="N111" s="1" t="inlineStr">
         <is>
-          <t>에 설치해야 한다.</t>
+          <t>비계발판의 자재로는 최근에 기성제품인 경량유공발판을 주로 사용한다.</t>
         </is>
       </c>
       <c r="O111" s="1" t="inlineStr">
         <is>
-          <t>에 설치해야 한다.</t>
+          <t>비계발판의 자재로는 최근에 기성제품인 경량유공발판을 주로 사용한다.</t>
         </is>
       </c>
       <c r="P111" s="1" t="inlineStr">
@@ -10364,7 +10364,7 @@
         </is>
       </c>
       <c r="E112" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F112" s="1" t="inlineStr">
         <is>
@@ -10388,32 +10388,32 @@
       </c>
       <c r="J112" s="1" t="inlineStr">
         <is>
-          <t>2.3.8</t>
+          <t>2.3.9</t>
         </is>
       </c>
       <c r="K112" s="1" t="inlineStr">
         <is>
-          <t>비계</t>
+          <t>가설통로</t>
         </is>
       </c>
       <c r="L112" s="1" t="inlineStr">
         <is>
-          <t>비계</t>
+          <t>가설통로</t>
         </is>
       </c>
       <c r="M112" s="1" t="inlineStr">
         <is>
-          <t>5~1.</t>
+          <t>가설통로를 설치할 경우는 다음 사항에 맞게 설치해 작업자가 원활하고 안전하게 이동할 수 있도록 한다.</t>
         </is>
       </c>
       <c r="N112" s="1" t="inlineStr">
         <is>
-          <t>5~1.</t>
+          <t>가설통로를 설치할 경우는 다음 사항에 맞게 설치해 작업자가 원활하고 안전하게 이동할 수 있도록 한다.</t>
         </is>
       </c>
       <c r="O112" s="1" t="inlineStr">
         <is>
-          <t>5~1.</t>
+          <t>가설통로를 설치할 경우는 다음 사항에 맞게 설치해 작업자가 원활하고 안전하게 이동할 수 있도록 한다.</t>
         </is>
       </c>
       <c r="P112" s="1" t="inlineStr">
@@ -10453,7 +10453,7 @@
         </is>
       </c>
       <c r="E113" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F113" s="1" t="inlineStr">
         <is>
@@ -10477,32 +10477,32 @@
       </c>
       <c r="J113" s="1" t="inlineStr">
         <is>
-          <t>2.3.8</t>
+          <t>2.3.9</t>
         </is>
       </c>
       <c r="K113" s="1" t="inlineStr">
         <is>
-          <t>비계</t>
+          <t>가설통로</t>
         </is>
       </c>
       <c r="L113" s="1" t="inlineStr">
         <is>
-          <t>비계</t>
+          <t>가설통로</t>
         </is>
       </c>
       <c r="M113" s="1" t="inlineStr">
         <is>
-          <t>5~1.</t>
+          <t>경사지게 가설통로를 설치할 경우 경사각은 30° 이내로 하며, 미끄럼막이를 설치한다.</t>
         </is>
       </c>
       <c r="N113" s="1" t="inlineStr">
         <is>
-          <t>5~1.</t>
+          <t>경사지게 가설통로를 설치할 경우 경사각은 30° 이내로 하며, 미끄럼막이를 설치한다.</t>
         </is>
       </c>
       <c r="O113" s="1" t="inlineStr">
         <is>
-          <t>5~1.</t>
+          <t>경사지게 가설통로를 설치할 경우 경사각은 30° 이내로 하며, 미끄럼막이를 설치한다.</t>
         </is>
       </c>
       <c r="P113" s="1" t="inlineStr">
@@ -10542,7 +10542,7 @@
         </is>
       </c>
       <c r="E114" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F114" s="1" t="inlineStr">
         <is>
@@ -10566,32 +10566,32 @@
       </c>
       <c r="J114" s="1" t="inlineStr">
         <is>
-          <t>2.3.8</t>
+          <t>2.3.9</t>
         </is>
       </c>
       <c r="K114" s="1" t="inlineStr">
         <is>
-          <t>비계</t>
+          <t>가설통로</t>
         </is>
       </c>
       <c r="L114" s="1" t="inlineStr">
         <is>
-          <t>비계</t>
+          <t>가설통로</t>
         </is>
       </c>
       <c r="M114" s="1" t="inlineStr">
         <is>
-          <t>④ 장선 간격은 1.</t>
+          <t>경사 로의 최소 폭은 90cm 이상으로 하고 경사로에는 높이 7m 이내마다 폭 90cm, 길이 180cm 이 상의 계단참을 설치한다.</t>
         </is>
       </c>
       <c r="N114" s="1" t="inlineStr">
         <is>
-          <t>④ 장선 간격은 1.</t>
+          <t>경사 로의 최소 폭은 90cm 이상으로 하고 경사로에는 높이 7m 이내마다 폭 90cm, 길이 180cm 이 상의 계단참을 설치한다.</t>
         </is>
       </c>
       <c r="O114" s="1" t="inlineStr">
         <is>
-          <t>④ 장선 간격은 1.</t>
+          <t>경사 로의 최소 폭은 90cm 이상으로 하고 경사로에는 높이 7m 이내마다 폭 90cm, 길이 180cm 이 상의 계단참을 설치한다.</t>
         </is>
       </c>
       <c r="P114" s="1" t="inlineStr">
@@ -10631,7 +10631,7 @@
         </is>
       </c>
       <c r="E115" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F115" s="1" t="inlineStr">
         <is>
@@ -10655,32 +10655,32 @@
       </c>
       <c r="J115" s="1" t="inlineStr">
         <is>
-          <t>2.3.8</t>
+          <t>2.3.9</t>
         </is>
       </c>
       <c r="K115" s="1" t="inlineStr">
         <is>
-          <t>비계</t>
+          <t>가설통로</t>
         </is>
       </c>
       <c r="L115" s="1" t="inlineStr">
         <is>
-          <t>비계</t>
+          <t>가설통로</t>
         </is>
       </c>
       <c r="M115" s="1" t="inlineStr">
         <is>
-          <t>하고, 그 중간 부분에서는 띠장에 결속한다.</t>
+          <t>또한 경사로의 연결부는 높이차가 없도록 설치한다.</t>
         </is>
       </c>
       <c r="N115" s="1" t="inlineStr">
         <is>
-          <t>하고, 그 중간 부분에서는 띠장에 결속한다.</t>
+          <t>또한 경사로의 연결부는 높이차가 없도록 설치한다.</t>
         </is>
       </c>
       <c r="O115" s="1" t="inlineStr">
         <is>
-          <t>하고, 그 중간 부분에서는 띠장에 결속한다.</t>
+          <t>또한 경사로의 연결부는 높이차가 없도록 설치한다.</t>
         </is>
       </c>
       <c r="P115" s="1" t="inlineStr">
@@ -10720,7 +10720,7 @@
         </is>
       </c>
       <c r="E116" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F116" s="1" t="inlineStr">
         <is>
@@ -10744,37 +10744,37 @@
       </c>
       <c r="J116" s="1" t="inlineStr">
         <is>
-          <t>2.3.8</t>
+          <t>2.3.9</t>
         </is>
       </c>
       <c r="K116" s="1" t="inlineStr">
         <is>
-          <t>비계</t>
+          <t>가설통로</t>
         </is>
       </c>
       <c r="L116" s="1" t="inlineStr">
         <is>
-          <t>비계</t>
+          <t>가설통로</t>
         </is>
       </c>
       <c r="M116" s="1" t="inlineStr">
         <is>
-          <t>⑤ 비계기둥 간의 적재하중은 400kg을 초과하지 않도록 해야 한다.</t>
+          <t>발판의 폭은 최 소 90cm 이상 발판 틈새는 3cm 이하로 한다.</t>
         </is>
       </c>
       <c r="N116" s="1" t="inlineStr">
         <is>
-          <t>⑤ 비계기둥 간의 적재하중은 400kg을 초과하지 않도록 해야 한다.</t>
+          <t>발판의 폭은 최 소 90cm 이상 발판 틈새는 3cm 이하로 한다.</t>
         </is>
       </c>
       <c r="O116" s="1" t="inlineStr">
         <is>
-          <t>⑤ 비계기둥 간의 적재하중은 400kg을 초과하지 않도록 해야 한다.</t>
+          <t>발판의 폭은 최 소 90cm 이상 발판 틈새는 3cm 이하로 한다.</t>
         </is>
       </c>
       <c r="P116" s="1" t="inlineStr">
         <is>
-          <t>특징</t>
+          <t>수치</t>
         </is>
       </c>
       <c r="Q116" s="1" t="inlineStr"/>
@@ -10809,7 +10809,7 @@
         </is>
       </c>
       <c r="E117" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F117" s="1" t="inlineStr">
         <is>
@@ -10833,32 +10833,32 @@
       </c>
       <c r="J117" s="1" t="inlineStr">
         <is>
-          <t>2.3.8</t>
+          <t>2.3.9</t>
         </is>
       </c>
       <c r="K117" s="1" t="inlineStr">
         <is>
-          <t>비계</t>
+          <t>가설통로</t>
         </is>
       </c>
       <c r="L117" s="1" t="inlineStr">
         <is>
-          <t>비계</t>
+          <t>가설통로</t>
         </is>
       </c>
       <c r="M117" s="1" t="inlineStr">
         <is>
-          <t>⑥ 벽 연결은 수직으로 5m, 수평으로 5m 이내마다 연결해야 한다.</t>
+          <t>경사로에는 높이 90cm 이상 120cm 이하의 난 간을 설치해야 한다.</t>
         </is>
       </c>
       <c r="N117" s="1" t="inlineStr">
         <is>
-          <t>⑥ 벽 연결은 수직으로 5m, 수평으로 5m 이내마다 연결해야 한다.</t>
+          <t>경사로에는 높이 90cm 이상 120cm 이하의 난 간을 설치해야 한다.</t>
         </is>
       </c>
       <c r="O117" s="1" t="inlineStr">
         <is>
-          <t>⑥ 벽 연결은 수직으로 5m, 수평으로 5m 이내마다 연결해야 한다.</t>
+          <t>경사로에는 높이 90cm 이상 120cm 이하의 난 간을 설치해야 한다.</t>
         </is>
       </c>
       <c r="P117" s="1" t="inlineStr">
@@ -10898,7 +10898,7 @@
         </is>
       </c>
       <c r="E118" s="1" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F118" s="1" t="inlineStr">
         <is>
@@ -10922,37 +10922,37 @@
       </c>
       <c r="J118" s="1" t="inlineStr">
         <is>
-          <t>2.3.8</t>
+          <t>2.3.10</t>
         </is>
       </c>
       <c r="K118" s="1" t="inlineStr">
         <is>
-          <t>비계</t>
+          <t>기타 안전시설</t>
         </is>
       </c>
       <c r="L118" s="1" t="inlineStr">
         <is>
-          <t>비계</t>
+          <t>기타 안전시설</t>
         </is>
       </c>
       <c r="M118" s="1" t="inlineStr">
         <is>
-          <t>에 결속해야 한다.</t>
+          <t>처리업무 신고시기 신고기관 대 상 구비서류 비 고 •지하 10m 이상을 굴착하는 건설공사 • 폭발물 사용으로 주변에 영향이 예상되 는 건설공사 건설업자 감독 또는 감 •10층 이상 16층 미만의 건축물 건설공사 작성기준 - 안전관리 등에게 리원의 • 10층 이상인 건축물의 리모델링 또는 해체 (건설기술 계획서 통보한 확인 후 공사 진흥법 제출 날부터 발주처에 •주택법에 다른 수직증축형 리모델링 시행규칙 7일 이내 제출 • 건설기계관리법 제3조에 등록된 건설기 별표 7) 계가 사용되는 건설공사 • 건설기술진흥법 시행령 제101조의2 제1항 의 가설구조물을 사용하는 건설공사 등 방화용품 보관소 유류저장소 •1 일 평균 300kg 이상의 사업장폐기물 배 착공 및 공사초기 필요한 서류 절차 사업장 배출예정일 출자 관할청 폐기물 처리방법 : 사업장폐기물 처리업체 폐기물 (착공일) • 대기·폐수·소음진동 배출시설이 설치 청소행정과 위탁 수집·운반·처리 처리업무 신고시기 신고기관 대 상 구비서류 비 고 배출신고 까지 신고 된 경우 : 1일 평균 100kg 이상 사업장폐 기물 배출자 건축물철거· 철거예정일 3일 전, 유해·위험 방지계획서 시, 군, 구청 모든 건축물 건축물 철거·멸실신고서 멸실신고 멸실 후 30일 이내 제출 대상 여부 확인 필요 감리원이 주재하는 공사에서 시공자는 공사 의 착공 시 아래의 일건의 서류를 감리원에 게 제출해 착공의 적정성 여부를 판단하게 경계복원 대지 내 한국국토정보공사 모든 건축물 지적측량신청서 되고 감리원은 이의 결과를 7일 이내에 발주 측량 건물 멸실 후 관할 출장소 건축관계자 자에게 통보하게 된다.</t>
         </is>
       </c>
       <c r="N118" s="1" t="inlineStr">
         <is>
-          <t>에 결속해야 한다.</t>
+          <t>처리업무 신고시기 신고기관 대 상 구비서류 비 고 •지하 10m 이상을 굴착하는 건설공사 • 폭발물 사용으로 주변에 영향이 예상되 는 건설공사 건설업자 감독 또는 감 •10층 이상 16층 미만의 건축물 건설공사 작성기준 - 안전관리 등에게 리원의 • 10층 이상인 건축물의 리모델링 또는 해체 (건설기술 계획서 통보한 확인 후 공사 진흥법 제출 날부터 발주처에 •주택법에 다른 수직증축형 리모델링 시행규칙 7일 이내 제출 • 건설기계관리법 제3조에 등록된 건설기 별표 7) 계가 사용되는 건설공사 • 건설기술진흥법 시행령 제101조의2 제1항 의 가설구조물을 사용하는 건설공사 등 방화용품 보관소 유류저장소 •1 일 평균 300kg 이상의 사업장폐기물 배 착공 및 공사초기 필요한 서류 절차 사업장 배출예정일 출자 관할청 폐기물 처리방법 : 사업장폐기물 처리업체 폐기물 (착공일) • 대기·폐수·소음진동 배출시설이 설치 청소행정과 위탁 수집·운반·처리 처리업무 신고시기 신고기관 대 상 구비서류 비 고 배출신고 까지 신고 된 경우 : 1일 평균 100kg 이상 사업장폐 기물 배출자 건축물철거· 철거예정일 3일 전, 유해·위험 방지계획서 시, 군, 구청 모든 건축물 건축물 철거·멸실신고서 멸실신고 멸실 후 30일 이내 제출 대상 여부 확인 필요 감리원이 주재하는 공사에서 시공자는 공사 의 착공 시 아래의 일건의 서류를 감리원에 게 제출해 착공의 적정성 여부를 판단하게 경계복원 대지 내 한국국토정보공사 모든 건축물 지적측량신청서 되고 감리원은 이의 결과를 7일 이내에 발주 측량 건물 멸실 후 관할 출장소 건축관계자 자에게 통보하게 된다.</t>
         </is>
       </c>
       <c r="O118" s="1" t="inlineStr">
         <is>
-          <t>에 결속해야 한다.</t>
+          <t>처리업무 신고시기 신고기관 대 상 구비서류 비 고 •지하 10m 이상을 굴착하는 건설공사 • 폭발물 사용으로 주변에 영향이 예상되 는 건설공사 건설업자 감독 또는 감 •10층 이상 16층 미만의 건축물 건설공사 작성기준 - 안전관리 등에게 리원의 • 10층 이상인 건축물의 리모델링 또는 해체 (건설기술 계획서 통보한 확인 후 공사 진흥법 제출 날부터 발주처에 •주택법에 다른 수직증축형 리모델링 시행규칙 7일 이내 제출 • 건설기계관리법 제3조에 등록된 건설기 별표 7) 계가 사용되는 건설공사 • 건설기술진흥법 시행령 제101조의2 제1항 의 가설구조물을 사용하는 건설공사 등 방화용품 보관소 유류저장소 •1 일 평균 300kg 이상의 사업장폐기물 배 착공 및 공사초기 필요한 서류 절차 사업장 배출예정일 출자 관할청 폐기물 처리방법 : 사업장폐기물 처리업체 폐기물 (착공일) • 대기·폐수·소음진동 배출시설이 설치 청소행정과 위탁 수집·운반·처리 처리업무 신고시기 신고기관 대 상 구비서류 비 고 배출신고 까지 신고 된 경우 : 1일 평균 100kg 이상 사업장폐 기물 배출자 건축물철거· 철거예정일 3일 전, 유해·위험 방지계획서 시, 군, 구청 모든 건축물 건축물 철거·멸실신고서 멸실신고 멸실 후 30일 이내 제출 대상 여부 확인 필요 감리원이 주재하는 공사에서 시공자는 공사 의 착공 시 아래의 일건의 서류를 감리원에 게 제출해 착공의 적정성 여부를 판단하게 경계복원 대지 내 한국국토정보공사 모든 건축물 지적측량신청서 되고 감리원은 이의 결과를 7일 이내에 발주 측량 건물 멸실 후 관할 출장소 건축관계자 자에게 통보하게 된다.</t>
         </is>
       </c>
       <c r="P118" s="1" t="inlineStr">
         <is>
-          <t>특징</t>
+          <t>수치</t>
         </is>
       </c>
       <c r="Q118" s="1" t="inlineStr"/>
@@ -10973,7 +10973,7 @@
       </c>
       <c r="B119" s="1" t="inlineStr">
         <is>
-          <t>S_00118</t>
+          <t>TBL_001</t>
         </is>
       </c>
       <c r="C119" s="1" t="inlineStr">
@@ -10983,11 +10983,11 @@
       </c>
       <c r="D119" s="1" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>table</t>
         </is>
       </c>
       <c r="E119" s="1" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F119" s="1" t="inlineStr">
         <is>
@@ -11011,2334 +11011,20 @@
       </c>
       <c r="J119" s="1" t="inlineStr">
         <is>
-          <t>2.3.8</t>
+          <t>2.3.10</t>
         </is>
       </c>
       <c r="K119" s="1" t="inlineStr">
         <is>
-          <t>비계</t>
+          <t>기타 안전시설</t>
         </is>
       </c>
       <c r="L119" s="1" t="inlineStr">
         <is>
-          <t>비계</t>
+          <t>[표 2-2] 착공 및 공사초기 필요한 서류 절차 사업장 배출예정일 출자</t>
         </is>
       </c>
       <c r="M119" s="1" t="inlineStr">
-        <is>
-          <t>⑧ 작업대에는 표준안전난간을 설치해야 한다.</t>
-        </is>
-      </c>
-      <c r="N119" s="1" t="inlineStr">
-        <is>
-          <t>⑧ 작업대에는 표준안전난간을 설치해야 한다.</t>
-        </is>
-      </c>
-      <c r="O119" s="1" t="inlineStr">
-        <is>
-          <t>⑧ 작업대에는 표준안전난간을 설치해야 한다.</t>
-        </is>
-      </c>
-      <c r="P119" s="1" t="inlineStr">
-        <is>
-          <t>특징</t>
-        </is>
-      </c>
-      <c r="Q119" s="1" t="inlineStr"/>
-      <c r="R119" s="1" t="inlineStr"/>
-      <c r="S119" s="1" t="inlineStr"/>
-      <c r="T119" s="1" t="inlineStr"/>
-      <c r="U119" s="1" t="inlineStr">
-        <is>
-          <t>2.가설공사(1).pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="1" t="inlineStr">
-        <is>
-          <t>GEN_0119</t>
-        </is>
-      </c>
-      <c r="B120" s="1" t="inlineStr">
-        <is>
-          <t>S_00119</t>
-        </is>
-      </c>
-      <c r="C120" s="1" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D120" s="1" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="E120" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="F120" s="1" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G120" s="1" t="inlineStr">
-        <is>
-          <t>가설공사(1)</t>
-        </is>
-      </c>
-      <c r="H120" s="1" t="inlineStr">
-        <is>
-          <t>2.3</t>
-        </is>
-      </c>
-      <c r="I120" s="1" t="inlineStr">
-        <is>
-          <t>가설공사의 세부사항</t>
-        </is>
-      </c>
-      <c r="J120" s="1" t="inlineStr">
-        <is>
-          <t>2.3.8</t>
-        </is>
-      </c>
-      <c r="K120" s="1" t="inlineStr">
-        <is>
-          <t>비계</t>
-        </is>
-      </c>
-      <c r="L120" s="1" t="inlineStr">
-        <is>
-          <t>비계</t>
-        </is>
-      </c>
-      <c r="M120" s="1" t="inlineStr">
-        <is>
-          <t>⑨ 작업대의 구조는 추락 및 낙하물 방지장치를 설치해야 한다.</t>
-        </is>
-      </c>
-      <c r="N120" s="1" t="inlineStr">
-        <is>
-          <t>⑨ 작업대의 구조는 추락 및 낙하물 방지장치를 설치해야 한다.</t>
-        </is>
-      </c>
-      <c r="O120" s="1" t="inlineStr">
-        <is>
-          <t>⑨ 작업대의 구조는 추락 및 낙하물 방지장치를 설치해야 한다.</t>
-        </is>
-      </c>
-      <c r="P120" s="1" t="inlineStr">
-        <is>
-          <t>특징</t>
-        </is>
-      </c>
-      <c r="Q120" s="1" t="inlineStr"/>
-      <c r="R120" s="1" t="inlineStr"/>
-      <c r="S120" s="1" t="inlineStr"/>
-      <c r="T120" s="1" t="inlineStr"/>
-      <c r="U120" s="1" t="inlineStr">
-        <is>
-          <t>2.가설공사(1).pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="1" t="inlineStr">
-        <is>
-          <t>GEN_0120</t>
-        </is>
-      </c>
-      <c r="B121" s="1" t="inlineStr">
-        <is>
-          <t>S_00120</t>
-        </is>
-      </c>
-      <c r="C121" s="1" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D121" s="1" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="E121" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="F121" s="1" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G121" s="1" t="inlineStr">
-        <is>
-          <t>가설공사(1)</t>
-        </is>
-      </c>
-      <c r="H121" s="1" t="inlineStr">
-        <is>
-          <t>2.3</t>
-        </is>
-      </c>
-      <c r="I121" s="1" t="inlineStr">
-        <is>
-          <t>가설공사의 세부사항</t>
-        </is>
-      </c>
-      <c r="J121" s="1" t="inlineStr">
-        <is>
-          <t>2.3.8</t>
-        </is>
-      </c>
-      <c r="K121" s="1" t="inlineStr">
-        <is>
-          <t>비계</t>
-        </is>
-      </c>
-      <c r="L121" s="1" t="inlineStr">
-        <is>
-          <t>비계</t>
-        </is>
-      </c>
-      <c r="M121" s="1" t="inlineStr">
-        <is>
-          <t>성능검정규격에 규정된 것을 사용해야 한다.</t>
-        </is>
-      </c>
-      <c r="N121" s="1" t="inlineStr">
-        <is>
-          <t>성능검정규격에 규정된 것을 사용해야 한다.</t>
-        </is>
-      </c>
-      <c r="O121" s="1" t="inlineStr">
-        <is>
-          <t>성능검정규격에 규정된 것을 사용해야 한다.</t>
-        </is>
-      </c>
-      <c r="P121" s="1" t="inlineStr">
-        <is>
-          <t>특징</t>
-        </is>
-      </c>
-      <c r="Q121" s="1" t="inlineStr"/>
-      <c r="R121" s="1" t="inlineStr"/>
-      <c r="S121" s="1" t="inlineStr"/>
-      <c r="T121" s="1" t="inlineStr"/>
-      <c r="U121" s="1" t="inlineStr">
-        <is>
-          <t>2.가설공사(1).pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="1" t="inlineStr">
-        <is>
-          <t>GEN_0121</t>
-        </is>
-      </c>
-      <c r="B122" s="1" t="inlineStr">
-        <is>
-          <t>S_00121</t>
-        </is>
-      </c>
-      <c r="C122" s="1" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D122" s="1" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="E122" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="F122" s="1" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G122" s="1" t="inlineStr">
-        <is>
-          <t>가설공사(1)</t>
-        </is>
-      </c>
-      <c r="H122" s="1" t="inlineStr">
-        <is>
-          <t>2.3</t>
-        </is>
-      </c>
-      <c r="I122" s="1" t="inlineStr">
-        <is>
-          <t>가설공사의 세부사항</t>
-        </is>
-      </c>
-      <c r="J122" s="1" t="inlineStr">
-        <is>
-          <t>2.3.8</t>
-        </is>
-      </c>
-      <c r="K122" s="1" t="inlineStr">
-        <is>
-          <t>비계</t>
-        </is>
-      </c>
-      <c r="L122" s="1" t="inlineStr">
-        <is>
-          <t>비계</t>
-        </is>
-      </c>
-      <c r="M122" s="1" t="inlineStr">
-        <is>
-          <t>호구의 착용 등 위험 방지를 위해 필요한 조치를 해야 한다.</t>
-        </is>
-      </c>
-      <c r="N122" s="1" t="inlineStr">
-        <is>
-          <t>호구의 착용 등 위험 방지를 위해 필요한 조치를 해야 한다.</t>
-        </is>
-      </c>
-      <c r="O122" s="1" t="inlineStr">
-        <is>
-          <t>호구의 착용 등 위험 방지를 위해 필요한 조치를 해야 한다.</t>
-        </is>
-      </c>
-      <c r="P122" s="1" t="inlineStr">
-        <is>
-          <t>특징</t>
-        </is>
-      </c>
-      <c r="Q122" s="1" t="inlineStr"/>
-      <c r="R122" s="1" t="inlineStr"/>
-      <c r="S122" s="1" t="inlineStr"/>
-      <c r="T122" s="1" t="inlineStr"/>
-      <c r="U122" s="1" t="inlineStr">
-        <is>
-          <t>2.가설공사(1).pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="1" t="inlineStr">
-        <is>
-          <t>GEN_0122</t>
-        </is>
-      </c>
-      <c r="B123" s="1" t="inlineStr">
-        <is>
-          <t>S_00122</t>
-        </is>
-      </c>
-      <c r="C123" s="1" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D123" s="1" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="E123" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="F123" s="1" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G123" s="1" t="inlineStr">
-        <is>
-          <t>가설공사(1)</t>
-        </is>
-      </c>
-      <c r="H123" s="1" t="inlineStr">
-        <is>
-          <t>2.3</t>
-        </is>
-      </c>
-      <c r="I123" s="1" t="inlineStr">
-        <is>
-          <t>가설공사의 세부사항</t>
-        </is>
-      </c>
-      <c r="J123" s="1" t="inlineStr">
-        <is>
-          <t>2.3.8</t>
-        </is>
-      </c>
-      <c r="K123" s="1" t="inlineStr">
-        <is>
-          <t>비계</t>
-        </is>
-      </c>
-      <c r="L123" s="1" t="inlineStr">
-        <is>
-          <t>비계</t>
-        </is>
-      </c>
-      <c r="M123" s="1" t="inlineStr">
-        <is>
-          <t>또한 외부비계와 벽체 사이에 틈새가 없도록 안전망을 설치한다.</t>
-        </is>
-      </c>
-      <c r="N123" s="1" t="inlineStr">
-        <is>
-          <t>또한 외부비계와 벽체 사이에 틈새가 없도록 안전망을 설치한다.</t>
-        </is>
-      </c>
-      <c r="O123" s="1" t="inlineStr">
-        <is>
-          <t>또한 외부비계와 벽체 사이에 틈새가 없도록 안전망을 설치한다.</t>
-        </is>
-      </c>
-      <c r="P123" s="1" t="inlineStr">
-        <is>
-          <t>특징</t>
-        </is>
-      </c>
-      <c r="Q123" s="1" t="inlineStr"/>
-      <c r="R123" s="1" t="inlineStr"/>
-      <c r="S123" s="1" t="inlineStr"/>
-      <c r="T123" s="1" t="inlineStr"/>
-      <c r="U123" s="1" t="inlineStr">
-        <is>
-          <t>2.가설공사(1).pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="1" t="inlineStr">
-        <is>
-          <t>GEN_0123</t>
-        </is>
-      </c>
-      <c r="B124" s="1" t="inlineStr">
-        <is>
-          <t>S_00123</t>
-        </is>
-      </c>
-      <c r="C124" s="1" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D124" s="1" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="E124" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="F124" s="1" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G124" s="1" t="inlineStr">
-        <is>
-          <t>가설공사(1)</t>
-        </is>
-      </c>
-      <c r="H124" s="1" t="inlineStr">
-        <is>
-          <t>2.3</t>
-        </is>
-      </c>
-      <c r="I124" s="1" t="inlineStr">
-        <is>
-          <t>가설공사의 세부사항</t>
-        </is>
-      </c>
-      <c r="J124" s="1" t="inlineStr">
-        <is>
-          <t>2.3.8</t>
-        </is>
-      </c>
-      <c r="K124" s="1" t="inlineStr">
-        <is>
-          <t>비계</t>
-        </is>
-      </c>
-      <c r="L124" s="1" t="inlineStr">
-        <is>
-          <t>비계</t>
-        </is>
-      </c>
-      <c r="M124" s="1" t="inlineStr">
-        <is>
-          <t>강관틀비계를 조립해 사용함에 있어서 다음의 각 사항을 준수해야 한다.</t>
-        </is>
-      </c>
-      <c r="N124" s="1" t="inlineStr">
-        <is>
-          <t>강관틀비계를 조립해 사용함에 있어서 다음의 각 사항을 준수해야 한다.</t>
-        </is>
-      </c>
-      <c r="O124" s="1" t="inlineStr">
-        <is>
-          <t>강관틀비계를 조립해 사용함에 있어서 다음의 각 사항을 준수해야 한다.</t>
-        </is>
-      </c>
-      <c r="P124" s="1" t="inlineStr">
-        <is>
-          <t>순서</t>
-        </is>
-      </c>
-      <c r="Q124" s="1" t="inlineStr"/>
-      <c r="R124" s="1" t="inlineStr"/>
-      <c r="S124" s="1" t="inlineStr"/>
-      <c r="T124" s="1" t="inlineStr"/>
-      <c r="U124" s="1" t="inlineStr">
-        <is>
-          <t>2.가설공사(1).pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="1" t="inlineStr">
-        <is>
-          <t>GEN_0124</t>
-        </is>
-      </c>
-      <c r="B125" s="1" t="inlineStr">
-        <is>
-          <t>S_00124</t>
-        </is>
-      </c>
-      <c r="C125" s="1" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D125" s="1" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="E125" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="F125" s="1" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G125" s="1" t="inlineStr">
-        <is>
-          <t>가설공사(1)</t>
-        </is>
-      </c>
-      <c r="H125" s="1" t="inlineStr">
-        <is>
-          <t>2.3</t>
-        </is>
-      </c>
-      <c r="I125" s="1" t="inlineStr">
-        <is>
-          <t>가설공사의 세부사항</t>
-        </is>
-      </c>
-      <c r="J125" s="1" t="inlineStr">
-        <is>
-          <t>2.3.8</t>
-        </is>
-      </c>
-      <c r="K125" s="1" t="inlineStr">
-        <is>
-          <t>비계</t>
-        </is>
-      </c>
-      <c r="L125" s="1" t="inlineStr">
-        <is>
-          <t>비계</t>
-        </is>
-      </c>
-      <c r="M125" s="1" t="inlineStr">
-        <is>
-          <t>밑받침철물을 사용해 각각의 강관틀비계가 항상 수평·수직을 유지하도록 한다.</t>
-        </is>
-      </c>
-      <c r="N125" s="1" t="inlineStr">
-        <is>
-          <t>밑받침철물을 사용해 각각의 강관틀비계가 항상 수평·수직을 유지하도록 한다.</t>
-        </is>
-      </c>
-      <c r="O125" s="1" t="inlineStr">
-        <is>
-          <t>밑받침철물을 사용해 각각의 강관틀비계가 항상 수평·수직을 유지하도록 한다.</t>
-        </is>
-      </c>
-      <c r="P125" s="1" t="inlineStr">
-        <is>
-          <t>특징</t>
-        </is>
-      </c>
-      <c r="Q125" s="1" t="inlineStr"/>
-      <c r="R125" s="1" t="inlineStr"/>
-      <c r="S125" s="1" t="inlineStr"/>
-      <c r="T125" s="1" t="inlineStr"/>
-      <c r="U125" s="1" t="inlineStr">
-        <is>
-          <t>2.가설공사(1).pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="1" t="inlineStr">
-        <is>
-          <t>GEN_0125</t>
-        </is>
-      </c>
-      <c r="B126" s="1" t="inlineStr">
-        <is>
-          <t>S_00125</t>
-        </is>
-      </c>
-      <c r="C126" s="1" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D126" s="1" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="E126" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="F126" s="1" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G126" s="1" t="inlineStr">
-        <is>
-          <t>가설공사(1)</t>
-        </is>
-      </c>
-      <c r="H126" s="1" t="inlineStr">
-        <is>
-          <t>2.3</t>
-        </is>
-      </c>
-      <c r="I126" s="1" t="inlineStr">
-        <is>
-          <t>가설공사의 세부사항</t>
-        </is>
-      </c>
-      <c r="J126" s="1" t="inlineStr">
-        <is>
-          <t>2.3.8</t>
-        </is>
-      </c>
-      <c r="K126" s="1" t="inlineStr">
-        <is>
-          <t>비계</t>
-        </is>
-      </c>
-      <c r="L126" s="1" t="inlineStr">
-        <is>
-          <t>비계</t>
-        </is>
-      </c>
-      <c r="M126" s="1" t="inlineStr">
-        <is>
-          <t>하고 주틀 간의 간격은 1.</t>
-        </is>
-      </c>
-      <c r="N126" s="1" t="inlineStr">
-        <is>
-          <t>하고 주틀 간의 간격은 1.</t>
-        </is>
-      </c>
-      <c r="O126" s="1" t="inlineStr">
-        <is>
-          <t>하고 주틀 간의 간격은 1.</t>
-        </is>
-      </c>
-      <c r="P126" s="1" t="inlineStr">
-        <is>
-          <t>수치</t>
-        </is>
-      </c>
-      <c r="Q126" s="1" t="inlineStr"/>
-      <c r="R126" s="1" t="inlineStr"/>
-      <c r="S126" s="1" t="inlineStr"/>
-      <c r="T126" s="1" t="inlineStr"/>
-      <c r="U126" s="1" t="inlineStr">
-        <is>
-          <t>2.가설공사(1).pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" s="1" t="inlineStr">
-        <is>
-          <t>GEN_0126</t>
-        </is>
-      </c>
-      <c r="B127" s="1" t="inlineStr">
-        <is>
-          <t>S_00126</t>
-        </is>
-      </c>
-      <c r="C127" s="1" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D127" s="1" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="E127" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="F127" s="1" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G127" s="1" t="inlineStr">
-        <is>
-          <t>가설공사(1)</t>
-        </is>
-      </c>
-      <c r="H127" s="1" t="inlineStr">
-        <is>
-          <t>2.3</t>
-        </is>
-      </c>
-      <c r="I127" s="1" t="inlineStr">
-        <is>
-          <t>가설공사의 세부사항</t>
-        </is>
-      </c>
-      <c r="J127" s="1" t="inlineStr">
-        <is>
-          <t>2.3.8</t>
-        </is>
-      </c>
-      <c r="K127" s="1" t="inlineStr">
-        <is>
-          <t>비계</t>
-        </is>
-      </c>
-      <c r="L127" s="1" t="inlineStr">
-        <is>
-          <t>비계</t>
-        </is>
-      </c>
-      <c r="M127" s="1" t="inlineStr">
-        <is>
-          <t>8m 이하로 한다.</t>
-        </is>
-      </c>
-      <c r="N127" s="1" t="inlineStr">
-        <is>
-          <t>8m 이하로 한다.</t>
-        </is>
-      </c>
-      <c r="O127" s="1" t="inlineStr">
-        <is>
-          <t>8m 이하로 한다.</t>
-        </is>
-      </c>
-      <c r="P127" s="1" t="inlineStr">
-        <is>
-          <t>수치</t>
-        </is>
-      </c>
-      <c r="Q127" s="1" t="inlineStr"/>
-      <c r="R127" s="1" t="inlineStr"/>
-      <c r="S127" s="1" t="inlineStr"/>
-      <c r="T127" s="1" t="inlineStr"/>
-      <c r="U127" s="1" t="inlineStr">
-        <is>
-          <t>2.가설공사(1).pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="1" t="inlineStr">
-        <is>
-          <t>GEN_0127</t>
-        </is>
-      </c>
-      <c r="B128" s="1" t="inlineStr">
-        <is>
-          <t>S_00127</t>
-        </is>
-      </c>
-      <c r="C128" s="1" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D128" s="1" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="E128" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="F128" s="1" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G128" s="1" t="inlineStr">
-        <is>
-          <t>가설공사(1)</t>
-        </is>
-      </c>
-      <c r="H128" s="1" t="inlineStr">
-        <is>
-          <t>2.3</t>
-        </is>
-      </c>
-      <c r="I128" s="1" t="inlineStr">
-        <is>
-          <t>가설공사의 세부사항</t>
-        </is>
-      </c>
-      <c r="J128" s="1" t="inlineStr">
-        <is>
-          <t>2.3.8</t>
-        </is>
-      </c>
-      <c r="K128" s="1" t="inlineStr">
-        <is>
-          <t>비계</t>
-        </is>
-      </c>
-      <c r="L128" s="1" t="inlineStr">
-        <is>
-          <t>비계</t>
-        </is>
-      </c>
-      <c r="M128" s="1" t="inlineStr">
-        <is>
-          <t>③ 이내마다 수평재를 설치해야 한다.</t>
-        </is>
-      </c>
-      <c r="N128" s="1" t="inlineStr">
-        <is>
-          <t>③ 이내마다 수평재를 설치해야 한다.</t>
-        </is>
-      </c>
-      <c r="O128" s="1" t="inlineStr">
-        <is>
-          <t>③ 이내마다 수평재를 설치해야 한다.</t>
-        </is>
-      </c>
-      <c r="P128" s="1" t="inlineStr">
-        <is>
-          <t>특징</t>
-        </is>
-      </c>
-      <c r="Q128" s="1" t="inlineStr"/>
-      <c r="R128" s="1" t="inlineStr"/>
-      <c r="S128" s="1" t="inlineStr"/>
-      <c r="T128" s="1" t="inlineStr"/>
-      <c r="U128" s="1" t="inlineStr">
-        <is>
-          <t>2.가설공사(1).pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="1" t="inlineStr">
-        <is>
-          <t>GEN_0128</t>
-        </is>
-      </c>
-      <c r="B129" s="1" t="inlineStr">
-        <is>
-          <t>S_00128</t>
-        </is>
-      </c>
-      <c r="C129" s="1" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D129" s="1" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="E129" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="F129" s="1" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G129" s="1" t="inlineStr">
-        <is>
-          <t>가설공사(1)</t>
-        </is>
-      </c>
-      <c r="H129" s="1" t="inlineStr">
-        <is>
-          <t>2.3</t>
-        </is>
-      </c>
-      <c r="I129" s="1" t="inlineStr">
-        <is>
-          <t>가설공사의 세부사항</t>
-        </is>
-      </c>
-      <c r="J129" s="1" t="inlineStr">
-        <is>
-          <t>2.3.8</t>
-        </is>
-      </c>
-      <c r="K129" s="1" t="inlineStr">
-        <is>
-          <t>비계</t>
-        </is>
-      </c>
-      <c r="L129" s="1" t="inlineStr">
-        <is>
-          <t>비계</t>
-        </is>
-      </c>
-      <c r="M129" s="1" t="inlineStr">
-        <is>
-          <t>평 방향으로 8m 이내마다 연결해야 한다.</t>
-        </is>
-      </c>
-      <c r="N129" s="1" t="inlineStr">
-        <is>
-          <t>평 방향으로 8m 이내마다 연결해야 한다.</t>
-        </is>
-      </c>
-      <c r="O129" s="1" t="inlineStr">
-        <is>
-          <t>평 방향으로 8m 이내마다 연결해야 한다.</t>
-        </is>
-      </c>
-      <c r="P129" s="1" t="inlineStr">
-        <is>
-          <t>수치</t>
-        </is>
-      </c>
-      <c r="Q129" s="1" t="inlineStr"/>
-      <c r="R129" s="1" t="inlineStr"/>
-      <c r="S129" s="1" t="inlineStr"/>
-      <c r="T129" s="1" t="inlineStr"/>
-      <c r="U129" s="1" t="inlineStr">
-        <is>
-          <t>2.가설공사(1).pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" s="1" t="inlineStr">
-        <is>
-          <t>GEN_0129</t>
-        </is>
-      </c>
-      <c r="B130" s="1" t="inlineStr">
-        <is>
-          <t>S_00129</t>
-        </is>
-      </c>
-      <c r="C130" s="1" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D130" s="1" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="E130" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="F130" s="1" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G130" s="1" t="inlineStr">
-        <is>
-          <t>가설공사(1)</t>
-        </is>
-      </c>
-      <c r="H130" s="1" t="inlineStr">
-        <is>
-          <t>2.3</t>
-        </is>
-      </c>
-      <c r="I130" s="1" t="inlineStr">
-        <is>
-          <t>가설공사의 세부사항</t>
-        </is>
-      </c>
-      <c r="J130" s="1" t="inlineStr">
-        <is>
-          <t>2.3.8</t>
-        </is>
-      </c>
-      <c r="K130" s="1" t="inlineStr">
-        <is>
-          <t>비계</t>
-        </is>
-      </c>
-      <c r="L130" s="1" t="inlineStr">
-        <is>
-          <t>비계</t>
-        </is>
-      </c>
-      <c r="M130" s="1" t="inlineStr">
-        <is>
-          <t>① 띠장 방향으로 버팀기둥을 설치해야 한다.</t>
-        </is>
-      </c>
-      <c r="N130" s="1" t="inlineStr">
-        <is>
-          <t>① 띠장 방향으로 버팀기둥을 설치해야 한다.</t>
-        </is>
-      </c>
-      <c r="O130" s="1" t="inlineStr">
-        <is>
-          <t>① 띠장 방향으로 버팀기둥을 설치해야 한다.</t>
-        </is>
-      </c>
-      <c r="P130" s="1" t="inlineStr">
-        <is>
-          <t>특징</t>
-        </is>
-      </c>
-      <c r="Q130" s="1" t="inlineStr"/>
-      <c r="R130" s="1" t="inlineStr"/>
-      <c r="S130" s="1" t="inlineStr"/>
-      <c r="T130" s="1" t="inlineStr"/>
-      <c r="U130" s="1" t="inlineStr">
-        <is>
-          <t>2.가설공사(1).pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="1" t="inlineStr">
-        <is>
-          <t>GEN_0130</t>
-        </is>
-      </c>
-      <c r="B131" s="1" t="inlineStr">
-        <is>
-          <t>S_00130</t>
-        </is>
-      </c>
-      <c r="C131" s="1" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D131" s="1" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="E131" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="F131" s="1" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G131" s="1" t="inlineStr">
-        <is>
-          <t>가설공사(1)</t>
-        </is>
-      </c>
-      <c r="H131" s="1" t="inlineStr">
-        <is>
-          <t>2.3</t>
-        </is>
-      </c>
-      <c r="I131" s="1" t="inlineStr">
-        <is>
-          <t>가설공사의 세부사항</t>
-        </is>
-      </c>
-      <c r="J131" s="1" t="inlineStr">
-        <is>
-          <t>2.3.8</t>
-        </is>
-      </c>
-      <c r="K131" s="1" t="inlineStr">
-        <is>
-          <t>비계</t>
-        </is>
-      </c>
-      <c r="L131" s="1" t="inlineStr">
-        <is>
-          <t>비계</t>
-        </is>
-      </c>
-      <c r="M131" s="1" t="inlineStr">
-        <is>
-          <t>틀비계 ① 받침판 ② 수직틀 ③ 암록크 ④ 가새 ⑥ 그 외의 다른 사항은 단관비계에 준한다.</t>
-        </is>
-      </c>
-      <c r="N131" s="1" t="inlineStr">
-        <is>
-          <t>틀비계 ① 받침판 ② 수직틀 ③ 암록크 ④ 가새 ⑥ 그 외의 다른 사항은 단관비계에 준한다.</t>
-        </is>
-      </c>
-      <c r="O131" s="1" t="inlineStr">
-        <is>
-          <t>틀비계 ① 받침판 ② 수직틀 ③ 암록크 ④ 가새 ⑥ 그 외의 다른 사항은 단관비계에 준한다.</t>
-        </is>
-      </c>
-      <c r="P131" s="1" t="inlineStr">
-        <is>
-          <t>특징</t>
-        </is>
-      </c>
-      <c r="Q131" s="1" t="inlineStr"/>
-      <c r="R131" s="1" t="inlineStr"/>
-      <c r="S131" s="1" t="inlineStr"/>
-      <c r="T131" s="1" t="inlineStr"/>
-      <c r="U131" s="1" t="inlineStr">
-        <is>
-          <t>2.가설공사(1).pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" s="1" t="inlineStr">
-        <is>
-          <t>GEN_0131</t>
-        </is>
-      </c>
-      <c r="B132" s="1" t="inlineStr">
-        <is>
-          <t>S_00131</t>
-        </is>
-      </c>
-      <c r="C132" s="1" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D132" s="1" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="E132" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="F132" s="1" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G132" s="1" t="inlineStr">
-        <is>
-          <t>가설공사(1)</t>
-        </is>
-      </c>
-      <c r="H132" s="1" t="inlineStr">
-        <is>
-          <t>2.3</t>
-        </is>
-      </c>
-      <c r="I132" s="1" t="inlineStr">
-        <is>
-          <t>가설공사의 세부사항</t>
-        </is>
-      </c>
-      <c r="J132" s="1" t="inlineStr">
-        <is>
-          <t>2.3.8</t>
-        </is>
-      </c>
-      <c r="K132" s="1" t="inlineStr">
-        <is>
-          <t>비계</t>
-        </is>
-      </c>
-      <c r="L132" s="1" t="inlineStr">
-        <is>
-          <t>비계</t>
-        </is>
-      </c>
-      <c r="M132" s="1" t="inlineStr">
-        <is>
-          <t>지물에 고정해야 한다.</t>
-        </is>
-      </c>
-      <c r="N132" s="1" t="inlineStr">
-        <is>
-          <t>지물에 고정해야 한다.</t>
-        </is>
-      </c>
-      <c r="O132" s="1" t="inlineStr">
-        <is>
-          <t>지물에 고정해야 한다.</t>
-        </is>
-      </c>
-      <c r="P132" s="1" t="inlineStr">
-        <is>
-          <t>특징</t>
-        </is>
-      </c>
-      <c r="Q132" s="1" t="inlineStr"/>
-      <c r="R132" s="1" t="inlineStr"/>
-      <c r="S132" s="1" t="inlineStr"/>
-      <c r="T132" s="1" t="inlineStr"/>
-      <c r="U132" s="1" t="inlineStr">
-        <is>
-          <t>2.가설공사(1).pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" s="1" t="inlineStr">
-        <is>
-          <t>GEN_0132</t>
-        </is>
-      </c>
-      <c r="B133" s="1" t="inlineStr">
-        <is>
-          <t>S_00132</t>
-        </is>
-      </c>
-      <c r="C133" s="1" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D133" s="1" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="E133" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="F133" s="1" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G133" s="1" t="inlineStr">
-        <is>
-          <t>가설공사(1)</t>
-        </is>
-      </c>
-      <c r="H133" s="1" t="inlineStr">
-        <is>
-          <t>2.3</t>
-        </is>
-      </c>
-      <c r="I133" s="1" t="inlineStr">
-        <is>
-          <t>가설공사의 세부사항</t>
-        </is>
-      </c>
-      <c r="J133" s="1" t="inlineStr">
-        <is>
-          <t>2.3.8</t>
-        </is>
-      </c>
-      <c r="K133" s="1" t="inlineStr">
-        <is>
-          <t>비계</t>
-        </is>
-      </c>
-      <c r="L133" s="1" t="inlineStr">
-        <is>
-          <t>비계</t>
-        </is>
-      </c>
-      <c r="M133" s="1" t="inlineStr">
-        <is>
-          <t>작업발판 끝부분의 돌출길이는 10cm 이상 20cm 이하로 해야 한다.</t>
-        </is>
-      </c>
-      <c r="N133" s="1" t="inlineStr">
-        <is>
-          <t>작업발판 끝부분의 돌출길이는 10cm 이상 20cm 이하로 해야 한다.</t>
-        </is>
-      </c>
-      <c r="O133" s="1" t="inlineStr">
-        <is>
-          <t>작업발판 끝부분의 돌출길이는 10cm 이상 20cm 이하로 해야 한다.</t>
-        </is>
-      </c>
-      <c r="P133" s="1" t="inlineStr">
-        <is>
-          <t>수치</t>
-        </is>
-      </c>
-      <c r="Q133" s="1" t="inlineStr"/>
-      <c r="R133" s="1" t="inlineStr"/>
-      <c r="S133" s="1" t="inlineStr"/>
-      <c r="T133" s="1" t="inlineStr"/>
-      <c r="U133" s="1" t="inlineStr">
-        <is>
-          <t>2.가설공사(1).pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" s="1" t="inlineStr">
-        <is>
-          <t>GEN_0133</t>
-        </is>
-      </c>
-      <c r="B134" s="1" t="inlineStr">
-        <is>
-          <t>S_00133</t>
-        </is>
-      </c>
-      <c r="C134" s="1" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D134" s="1" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="E134" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="F134" s="1" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G134" s="1" t="inlineStr">
-        <is>
-          <t>가설공사(1)</t>
-        </is>
-      </c>
-      <c r="H134" s="1" t="inlineStr">
-        <is>
-          <t>2.3</t>
-        </is>
-      </c>
-      <c r="I134" s="1" t="inlineStr">
-        <is>
-          <t>가설공사의 세부사항</t>
-        </is>
-      </c>
-      <c r="J134" s="1" t="inlineStr">
-        <is>
-          <t>2.3.8</t>
-        </is>
-      </c>
-      <c r="K134" s="1" t="inlineStr">
-        <is>
-          <t>비계</t>
-        </is>
-      </c>
-      <c r="L134" s="1" t="inlineStr">
-        <is>
-          <t>비계</t>
-        </is>
-      </c>
-      <c r="M134" s="1" t="inlineStr">
-        <is>
-          <t>비계발판의 자재로는 최근에 기성제품인 경량유공발판을 주로 사용한다.</t>
-        </is>
-      </c>
-      <c r="N134" s="1" t="inlineStr">
-        <is>
-          <t>비계발판의 자재로는 최근에 기성제품인 경량유공발판을 주로 사용한다.</t>
-        </is>
-      </c>
-      <c r="O134" s="1" t="inlineStr">
-        <is>
-          <t>비계발판의 자재로는 최근에 기성제품인 경량유공발판을 주로 사용한다.</t>
-        </is>
-      </c>
-      <c r="P134" s="1" t="inlineStr">
-        <is>
-          <t>특징</t>
-        </is>
-      </c>
-      <c r="Q134" s="1" t="inlineStr"/>
-      <c r="R134" s="1" t="inlineStr"/>
-      <c r="S134" s="1" t="inlineStr"/>
-      <c r="T134" s="1" t="inlineStr"/>
-      <c r="U134" s="1" t="inlineStr">
-        <is>
-          <t>2.가설공사(1).pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="1" t="inlineStr">
-        <is>
-          <t>GEN_0134</t>
-        </is>
-      </c>
-      <c r="B135" s="1" t="inlineStr">
-        <is>
-          <t>S_00134</t>
-        </is>
-      </c>
-      <c r="C135" s="1" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D135" s="1" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="E135" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="F135" s="1" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G135" s="1" t="inlineStr">
-        <is>
-          <t>가설공사(1)</t>
-        </is>
-      </c>
-      <c r="H135" s="1" t="inlineStr">
-        <is>
-          <t>2.3</t>
-        </is>
-      </c>
-      <c r="I135" s="1" t="inlineStr">
-        <is>
-          <t>가설공사의 세부사항</t>
-        </is>
-      </c>
-      <c r="J135" s="1" t="inlineStr">
-        <is>
-          <t>2.3.9</t>
-        </is>
-      </c>
-      <c r="K135" s="1" t="inlineStr">
-        <is>
-          <t>가설통로</t>
-        </is>
-      </c>
-      <c r="L135" s="1" t="inlineStr">
-        <is>
-          <t>가설통로</t>
-        </is>
-      </c>
-      <c r="M135" s="1" t="inlineStr">
-        <is>
-          <t>있도록 한다.</t>
-        </is>
-      </c>
-      <c r="N135" s="1" t="inlineStr">
-        <is>
-          <t>있도록 한다.</t>
-        </is>
-      </c>
-      <c r="O135" s="1" t="inlineStr">
-        <is>
-          <t>있도록 한다.</t>
-        </is>
-      </c>
-      <c r="P135" s="1" t="inlineStr">
-        <is>
-          <t>특징</t>
-        </is>
-      </c>
-      <c r="Q135" s="1" t="inlineStr"/>
-      <c r="R135" s="1" t="inlineStr"/>
-      <c r="S135" s="1" t="inlineStr"/>
-      <c r="T135" s="1" t="inlineStr"/>
-      <c r="U135" s="1" t="inlineStr">
-        <is>
-          <t>2.가설공사(1).pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="1" t="inlineStr">
-        <is>
-          <t>GEN_0135</t>
-        </is>
-      </c>
-      <c r="B136" s="1" t="inlineStr">
-        <is>
-          <t>S_00135</t>
-        </is>
-      </c>
-      <c r="C136" s="1" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D136" s="1" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="E136" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="F136" s="1" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G136" s="1" t="inlineStr">
-        <is>
-          <t>가설공사(1)</t>
-        </is>
-      </c>
-      <c r="H136" s="1" t="inlineStr">
-        <is>
-          <t>2.3</t>
-        </is>
-      </c>
-      <c r="I136" s="1" t="inlineStr">
-        <is>
-          <t>가설공사의 세부사항</t>
-        </is>
-      </c>
-      <c r="J136" s="1" t="inlineStr">
-        <is>
-          <t>2.3.9</t>
-        </is>
-      </c>
-      <c r="K136" s="1" t="inlineStr">
-        <is>
-          <t>가설통로</t>
-        </is>
-      </c>
-      <c r="L136" s="1" t="inlineStr">
-        <is>
-          <t>가설통로</t>
-        </is>
-      </c>
-      <c r="M136" s="1" t="inlineStr">
-        <is>
-          <t>경사지게 가설통로를 설치할 경우 경사각은 30° 이내로 하며, 미끄럼막이를 설치한다.</t>
-        </is>
-      </c>
-      <c r="N136" s="1" t="inlineStr">
-        <is>
-          <t>경사지게 가설통로를 설치할 경우 경사각은 30° 이내로 하며, 미끄럼막이를 설치한다.</t>
-        </is>
-      </c>
-      <c r="O136" s="1" t="inlineStr">
-        <is>
-          <t>경사지게 가설통로를 설치할 경우 경사각은 30° 이내로 하며, 미끄럼막이를 설치한다.</t>
-        </is>
-      </c>
-      <c r="P136" s="1" t="inlineStr">
-        <is>
-          <t>특징</t>
-        </is>
-      </c>
-      <c r="Q136" s="1" t="inlineStr"/>
-      <c r="R136" s="1" t="inlineStr"/>
-      <c r="S136" s="1" t="inlineStr"/>
-      <c r="T136" s="1" t="inlineStr"/>
-      <c r="U136" s="1" t="inlineStr">
-        <is>
-          <t>2.가설공사(1).pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="1" t="inlineStr">
-        <is>
-          <t>GEN_0136</t>
-        </is>
-      </c>
-      <c r="B137" s="1" t="inlineStr">
-        <is>
-          <t>S_00136</t>
-        </is>
-      </c>
-      <c r="C137" s="1" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D137" s="1" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="E137" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="F137" s="1" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G137" s="1" t="inlineStr">
-        <is>
-          <t>가설공사(1)</t>
-        </is>
-      </c>
-      <c r="H137" s="1" t="inlineStr">
-        <is>
-          <t>2.3</t>
-        </is>
-      </c>
-      <c r="I137" s="1" t="inlineStr">
-        <is>
-          <t>가설공사의 세부사항</t>
-        </is>
-      </c>
-      <c r="J137" s="1" t="inlineStr">
-        <is>
-          <t>2.3.9</t>
-        </is>
-      </c>
-      <c r="K137" s="1" t="inlineStr">
-        <is>
-          <t>가설통로</t>
-        </is>
-      </c>
-      <c r="L137" s="1" t="inlineStr">
-        <is>
-          <t>가설통로</t>
-        </is>
-      </c>
-      <c r="M137" s="1" t="inlineStr">
-        <is>
-          <t>상의 계단참을 설치한다.</t>
-        </is>
-      </c>
-      <c r="N137" s="1" t="inlineStr">
-        <is>
-          <t>상의 계단참을 설치한다.</t>
-        </is>
-      </c>
-      <c r="O137" s="1" t="inlineStr">
-        <is>
-          <t>상의 계단참을 설치한다.</t>
-        </is>
-      </c>
-      <c r="P137" s="1" t="inlineStr">
-        <is>
-          <t>특징</t>
-        </is>
-      </c>
-      <c r="Q137" s="1" t="inlineStr"/>
-      <c r="R137" s="1" t="inlineStr"/>
-      <c r="S137" s="1" t="inlineStr"/>
-      <c r="T137" s="1" t="inlineStr"/>
-      <c r="U137" s="1" t="inlineStr">
-        <is>
-          <t>2.가설공사(1).pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" s="1" t="inlineStr">
-        <is>
-          <t>GEN_0137</t>
-        </is>
-      </c>
-      <c r="B138" s="1" t="inlineStr">
-        <is>
-          <t>S_00137</t>
-        </is>
-      </c>
-      <c r="C138" s="1" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D138" s="1" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="E138" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="F138" s="1" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G138" s="1" t="inlineStr">
-        <is>
-          <t>가설공사(1)</t>
-        </is>
-      </c>
-      <c r="H138" s="1" t="inlineStr">
-        <is>
-          <t>2.3</t>
-        </is>
-      </c>
-      <c r="I138" s="1" t="inlineStr">
-        <is>
-          <t>가설공사의 세부사항</t>
-        </is>
-      </c>
-      <c r="J138" s="1" t="inlineStr">
-        <is>
-          <t>2.3.9</t>
-        </is>
-      </c>
-      <c r="K138" s="1" t="inlineStr">
-        <is>
-          <t>가설통로</t>
-        </is>
-      </c>
-      <c r="L138" s="1" t="inlineStr">
-        <is>
-          <t>가설통로</t>
-        </is>
-      </c>
-      <c r="M138" s="1" t="inlineStr">
-        <is>
-          <t>또한 경사로의 연결부는 높이차가 없도록 설치한다.</t>
-        </is>
-      </c>
-      <c r="N138" s="1" t="inlineStr">
-        <is>
-          <t>또한 경사로의 연결부는 높이차가 없도록 설치한다.</t>
-        </is>
-      </c>
-      <c r="O138" s="1" t="inlineStr">
-        <is>
-          <t>또한 경사로의 연결부는 높이차가 없도록 설치한다.</t>
-        </is>
-      </c>
-      <c r="P138" s="1" t="inlineStr">
-        <is>
-          <t>특징</t>
-        </is>
-      </c>
-      <c r="Q138" s="1" t="inlineStr"/>
-      <c r="R138" s="1" t="inlineStr"/>
-      <c r="S138" s="1" t="inlineStr"/>
-      <c r="T138" s="1" t="inlineStr"/>
-      <c r="U138" s="1" t="inlineStr">
-        <is>
-          <t>2.가설공사(1).pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" s="1" t="inlineStr">
-        <is>
-          <t>GEN_0138</t>
-        </is>
-      </c>
-      <c r="B139" s="1" t="inlineStr">
-        <is>
-          <t>S_00138</t>
-        </is>
-      </c>
-      <c r="C139" s="1" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D139" s="1" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="E139" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="F139" s="1" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G139" s="1" t="inlineStr">
-        <is>
-          <t>가설공사(1)</t>
-        </is>
-      </c>
-      <c r="H139" s="1" t="inlineStr">
-        <is>
-          <t>2.3</t>
-        </is>
-      </c>
-      <c r="I139" s="1" t="inlineStr">
-        <is>
-          <t>가설공사의 세부사항</t>
-        </is>
-      </c>
-      <c r="J139" s="1" t="inlineStr">
-        <is>
-          <t>2.3.9</t>
-        </is>
-      </c>
-      <c r="K139" s="1" t="inlineStr">
-        <is>
-          <t>가설통로</t>
-        </is>
-      </c>
-      <c r="L139" s="1" t="inlineStr">
-        <is>
-          <t>가설통로</t>
-        </is>
-      </c>
-      <c r="M139" s="1" t="inlineStr">
-        <is>
-          <t>소 90cm 이상 발판 틈새는 3cm 이하로 한다.</t>
-        </is>
-      </c>
-      <c r="N139" s="1" t="inlineStr">
-        <is>
-          <t>소 90cm 이상 발판 틈새는 3cm 이하로 한다.</t>
-        </is>
-      </c>
-      <c r="O139" s="1" t="inlineStr">
-        <is>
-          <t>소 90cm 이상 발판 틈새는 3cm 이하로 한다.</t>
-        </is>
-      </c>
-      <c r="P139" s="1" t="inlineStr">
-        <is>
-          <t>수치</t>
-        </is>
-      </c>
-      <c r="Q139" s="1" t="inlineStr"/>
-      <c r="R139" s="1" t="inlineStr"/>
-      <c r="S139" s="1" t="inlineStr"/>
-      <c r="T139" s="1" t="inlineStr"/>
-      <c r="U139" s="1" t="inlineStr">
-        <is>
-          <t>2.가설공사(1).pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" s="1" t="inlineStr">
-        <is>
-          <t>GEN_0139</t>
-        </is>
-      </c>
-      <c r="B140" s="1" t="inlineStr">
-        <is>
-          <t>S_00139</t>
-        </is>
-      </c>
-      <c r="C140" s="1" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D140" s="1" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="E140" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="F140" s="1" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G140" s="1" t="inlineStr">
-        <is>
-          <t>가설공사(1)</t>
-        </is>
-      </c>
-      <c r="H140" s="1" t="inlineStr">
-        <is>
-          <t>2.3</t>
-        </is>
-      </c>
-      <c r="I140" s="1" t="inlineStr">
-        <is>
-          <t>가설공사의 세부사항</t>
-        </is>
-      </c>
-      <c r="J140" s="1" t="inlineStr">
-        <is>
-          <t>2.3.9</t>
-        </is>
-      </c>
-      <c r="K140" s="1" t="inlineStr">
-        <is>
-          <t>가설통로</t>
-        </is>
-      </c>
-      <c r="L140" s="1" t="inlineStr">
-        <is>
-          <t>가설통로</t>
-        </is>
-      </c>
-      <c r="M140" s="1" t="inlineStr">
-        <is>
-          <t>간을 설치해야 한다.</t>
-        </is>
-      </c>
-      <c r="N140" s="1" t="inlineStr">
-        <is>
-          <t>간을 설치해야 한다.</t>
-        </is>
-      </c>
-      <c r="O140" s="1" t="inlineStr">
-        <is>
-          <t>간을 설치해야 한다.</t>
-        </is>
-      </c>
-      <c r="P140" s="1" t="inlineStr">
-        <is>
-          <t>특징</t>
-        </is>
-      </c>
-      <c r="Q140" s="1" t="inlineStr"/>
-      <c r="R140" s="1" t="inlineStr"/>
-      <c r="S140" s="1" t="inlineStr"/>
-      <c r="T140" s="1" t="inlineStr"/>
-      <c r="U140" s="1" t="inlineStr">
-        <is>
-          <t>2.가설공사(1).pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" s="1" t="inlineStr">
-        <is>
-          <t>GEN_0140</t>
-        </is>
-      </c>
-      <c r="B141" s="1" t="inlineStr">
-        <is>
-          <t>S_00140</t>
-        </is>
-      </c>
-      <c r="C141" s="1" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D141" s="1" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="E141" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="F141" s="1" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G141" s="1" t="inlineStr">
-        <is>
-          <t>가설공사(1)</t>
-        </is>
-      </c>
-      <c r="H141" s="1" t="inlineStr">
-        <is>
-          <t>2.3</t>
-        </is>
-      </c>
-      <c r="I141" s="1" t="inlineStr">
-        <is>
-          <t>가설공사의 세부사항</t>
-        </is>
-      </c>
-      <c r="J141" s="1" t="inlineStr">
-        <is>
-          <t>2.3.10</t>
-        </is>
-      </c>
-      <c r="K141" s="1" t="inlineStr">
-        <is>
-          <t>기타 안전시설</t>
-        </is>
-      </c>
-      <c r="L141" s="1" t="inlineStr">
-        <is>
-          <t>기타 안전시설</t>
-        </is>
-      </c>
-      <c r="M141" s="1" t="inlineStr">
-        <is>
-          <t>자에게 통보하게 된다.</t>
-        </is>
-      </c>
-      <c r="N141" s="1" t="inlineStr">
-        <is>
-          <t>자에게 통보하게 된다.</t>
-        </is>
-      </c>
-      <c r="O141" s="1" t="inlineStr">
-        <is>
-          <t>자에게 통보하게 된다.</t>
-        </is>
-      </c>
-      <c r="P141" s="1" t="inlineStr">
-        <is>
-          <t>특징</t>
-        </is>
-      </c>
-      <c r="Q141" s="1" t="inlineStr"/>
-      <c r="R141" s="1" t="inlineStr"/>
-      <c r="S141" s="1" t="inlineStr"/>
-      <c r="T141" s="1" t="inlineStr"/>
-      <c r="U141" s="1" t="inlineStr">
-        <is>
-          <t>2.가설공사(1).pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" s="1" t="inlineStr">
-        <is>
-          <t>GEN_0141</t>
-        </is>
-      </c>
-      <c r="B142" s="1" t="inlineStr">
-        <is>
-          <t>S_00141</t>
-        </is>
-      </c>
-      <c r="C142" s="1" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D142" s="1" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="E142" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="F142" s="1" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G142" s="1" t="inlineStr">
-        <is>
-          <t>가설공사(1)</t>
-        </is>
-      </c>
-      <c r="H142" s="1" t="inlineStr">
-        <is>
-          <t>2.3</t>
-        </is>
-      </c>
-      <c r="I142" s="1" t="inlineStr">
-        <is>
-          <t>가설공사의 세부사항</t>
-        </is>
-      </c>
-      <c r="J142" s="1" t="inlineStr">
-        <is>
-          <t>2.3.10</t>
-        </is>
-      </c>
-      <c r="K142" s="1" t="inlineStr">
-        <is>
-          <t>기타 안전시설</t>
-        </is>
-      </c>
-      <c r="L142" s="1" t="inlineStr">
-        <is>
-          <t>기타 안전시설</t>
-        </is>
-      </c>
-      <c r="M142" s="1" t="inlineStr">
-        <is>
-          <t>•소 음 진 동저감대책 2 .</t>
-        </is>
-      </c>
-      <c r="N142" s="1" t="inlineStr">
-        <is>
-          <t>•소 음 진 동저감대책 2 .</t>
-        </is>
-      </c>
-      <c r="O142" s="1" t="inlineStr">
-        <is>
-          <t>•소 음 진 동저감대책 2 .</t>
-        </is>
-      </c>
-      <c r="P142" s="1" t="inlineStr">
-        <is>
-          <t>특징</t>
-        </is>
-      </c>
-      <c r="Q142" s="1" t="inlineStr"/>
-      <c r="R142" s="1" t="inlineStr"/>
-      <c r="S142" s="1" t="inlineStr"/>
-      <c r="T142" s="1" t="inlineStr"/>
-      <c r="U142" s="1" t="inlineStr">
-        <is>
-          <t>2.가설공사(1).pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" s="1" t="inlineStr">
-        <is>
-          <t>GEN_0142</t>
-        </is>
-      </c>
-      <c r="B143" s="1" t="inlineStr">
-        <is>
-          <t>S_00142</t>
-        </is>
-      </c>
-      <c r="C143" s="1" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D143" s="1" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="E143" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="F143" s="1" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G143" s="1" t="inlineStr">
-        <is>
-          <t>가설공사(1)</t>
-        </is>
-      </c>
-      <c r="H143" s="1" t="inlineStr">
-        <is>
-          <t>2.3</t>
-        </is>
-      </c>
-      <c r="I143" s="1" t="inlineStr">
-        <is>
-          <t>가설공사의 세부사항</t>
-        </is>
-      </c>
-      <c r="J143" s="1" t="inlineStr">
-        <is>
-          <t>2.3.10</t>
-        </is>
-      </c>
-      <c r="K143" s="1" t="inlineStr">
-        <is>
-          <t>기타 안전시설</t>
-        </is>
-      </c>
-      <c r="L143" s="1" t="inlineStr">
-        <is>
-          <t>기타 안전시설</t>
-        </is>
-      </c>
-      <c r="M143" s="1" t="inlineStr">
-        <is>
-          <t>제출 •깊 이 10.</t>
-        </is>
-      </c>
-      <c r="N143" s="1" t="inlineStr">
-        <is>
-          <t>제출 •깊 이 10.</t>
-        </is>
-      </c>
-      <c r="O143" s="1" t="inlineStr">
-        <is>
-          <t>제출 •깊 이 10.</t>
-        </is>
-      </c>
-      <c r="P143" s="1" t="inlineStr">
-        <is>
-          <t>특징</t>
-        </is>
-      </c>
-      <c r="Q143" s="1" t="inlineStr"/>
-      <c r="R143" s="1" t="inlineStr"/>
-      <c r="S143" s="1" t="inlineStr"/>
-      <c r="T143" s="1" t="inlineStr"/>
-      <c r="U143" s="1" t="inlineStr">
-        <is>
-          <t>2.가설공사(1).pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" s="1" t="inlineStr">
-        <is>
-          <t>GEN_0143</t>
-        </is>
-      </c>
-      <c r="B144" s="1" t="inlineStr">
-        <is>
-          <t>S_00143</t>
-        </is>
-      </c>
-      <c r="C144" s="1" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D144" s="1" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="E144" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="F144" s="1" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G144" s="1" t="inlineStr">
-        <is>
-          <t>가설공사(1)</t>
-        </is>
-      </c>
-      <c r="H144" s="1" t="inlineStr">
-        <is>
-          <t>2.3</t>
-        </is>
-      </c>
-      <c r="I144" s="1" t="inlineStr">
-        <is>
-          <t>가설공사의 세부사항</t>
-        </is>
-      </c>
-      <c r="J144" s="1" t="inlineStr">
-        <is>
-          <t>2.3.10</t>
-        </is>
-      </c>
-      <c r="K144" s="1" t="inlineStr">
-        <is>
-          <t>기타 안전시설</t>
-        </is>
-      </c>
-      <c r="L144" s="1" t="inlineStr">
-        <is>
-          <t>기타 안전시설</t>
-        </is>
-      </c>
-      <c r="M144" s="1" t="inlineStr">
-        <is>
-          <t>기준 600명 증가 시마다 1명씩 추가 선임)</t>
-        </is>
-      </c>
-      <c r="N144" s="1" t="inlineStr">
-        <is>
-          <t>기준 600명 증가 시마다 1명씩 추가 선임)</t>
-        </is>
-      </c>
-      <c r="O144" s="1" t="inlineStr">
-        <is>
-          <t>기준 600명 증가 시마다 1명씩 추가 선임)</t>
-        </is>
-      </c>
-      <c r="P144" s="1" t="inlineStr">
-        <is>
-          <t>특징</t>
-        </is>
-      </c>
-      <c r="Q144" s="1" t="inlineStr"/>
-      <c r="R144" s="1" t="inlineStr"/>
-      <c r="S144" s="1" t="inlineStr"/>
-      <c r="T144" s="1" t="inlineStr"/>
-      <c r="U144" s="1" t="inlineStr">
-        <is>
-          <t>2.가설공사(1).pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" s="1" t="inlineStr">
-        <is>
-          <t>GEN_0144</t>
-        </is>
-      </c>
-      <c r="B145" s="1" t="inlineStr">
-        <is>
-          <t>TBL_001</t>
-        </is>
-      </c>
-      <c r="C145" s="1" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D145" s="1" t="inlineStr">
-        <is>
-          <t>table</t>
-        </is>
-      </c>
-      <c r="E145" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="F145" s="1" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G145" s="1" t="inlineStr">
-        <is>
-          <t>가설공사(1)</t>
-        </is>
-      </c>
-      <c r="H145" s="1" t="inlineStr">
-        <is>
-          <t>2.3</t>
-        </is>
-      </c>
-      <c r="I145" s="1" t="inlineStr">
-        <is>
-          <t>가설공사의 세부사항</t>
-        </is>
-      </c>
-      <c r="J145" s="1" t="inlineStr">
-        <is>
-          <t>2.3.10</t>
-        </is>
-      </c>
-      <c r="K145" s="1" t="inlineStr">
-        <is>
-          <t>기타 안전시설</t>
-        </is>
-      </c>
-      <c r="L145" s="1" t="inlineStr">
-        <is>
-          <t>[표 2-2] 착공 및 공사초기 필요한 서류 절차 사업장 배출예정일 출자</t>
-        </is>
-      </c>
-      <c r="M145" s="1" t="inlineStr">
         <is>
           <t>처리업무|신고시기|신고기관|대 상|구비서류|비 고
 처리업무|철거예정일 3일 전,
@@ -13394,7 +11080,7 @@
 •붕 괴방지계획 등</t>
         </is>
       </c>
-      <c r="N145" s="1" t="inlineStr">
+      <c r="N119" s="1" t="inlineStr">
         <is>
           <t>처리업무|신고시기|신고기관|대 상|구비서류|비 고
 처리업무|철거예정일 3일 전,
@@ -13450,7 +11136,7 @@
 •붕 괴방지계획 등</t>
         </is>
       </c>
-      <c r="O145" s="1" t="inlineStr">
+      <c r="O119" s="1" t="inlineStr">
         <is>
           <t>처리업무|신고시기|신고기관|대 상|구비서류|비 고
 처리업무|철거예정일 3일 전,
@@ -13506,24 +11192,24 @@
 •붕 괴방지계획 등</t>
         </is>
       </c>
-      <c r="P145" s="1" t="inlineStr">
+      <c r="P119" s="1" t="inlineStr">
         <is>
           <t>순서</t>
         </is>
       </c>
-      <c r="Q145" s="1" t="inlineStr">
+      <c r="Q119" s="1" t="inlineStr">
         <is>
           <t>[표 2-2] 착공 및 공사초기 필요한 서류 절차 사업장 배출예정일 출자</t>
         </is>
       </c>
-      <c r="R145" s="1" t="inlineStr">
+      <c r="R119" s="1" t="inlineStr">
         <is>
           <t>[["처리업무", "신고시기", "신고기관", "대 상", "구비서류", "비 고"], ["처리업무", "철거예정일 3일 전,\n멸실 후 30일 이내", "시, 군, 구청", "모든 건축물", "건축물 철거·멸실신고서", "건축물 철거·멸실신고서"], ["처리업무", "대지 내\n건물 멸실 후", "한국국토정보공사\n관할 출장소", "모든 건축물", "지적측량신청서", "지적측량신청서"], ["처리업무", "착공 5일 전", "관할시, 군, 구", "현장 내 가설건물", "•가 설물축조신고서\n•배 치도, 평면도\n•대 지사용승낙서\n(타인 소유 토지인 경우)", "•가 설물축조신고서\n•배 치도, 평면도\n•대 지사용승낙서\n(타인 소유 토지인 경우)"], ["처리업무", "착공 전까지", "관할청\n환경위생과", "•건 축연면적 1,000m2 이상\n건축공사\n•연면적 3,000m2 이상 철거\n•굴착토사량 200m3 이상", "공사계요, 공사장 위치도,\n방진시설 등 설치 명세 및\n도면, 그 밖의 저감대책", "공사계요, 공사장 위치도,\n방진시설 등 설치 명세 및\n도면, 그 밖의 저감대책"], ["처리업무", "공사시행\n3일 전까지", "관할청\n환경위생과", "•연 면적 1,000m2 이상\n건축공사\n•연 면적 3,000m2 이상\n건축물 해체공사\n•굴 착토사량 합계\n200m3 이상인 굴정공사", "•특 정공사개요\n•공 사장 위치도, 방음·\n방진시설 설치내역 및\n도면\n•소 음진동저감대책", "•특 정공사개요\n•공 사장 위치도, 방음·\n방진시설 설치내역 및\n도면\n•소 음진동저감대책"], ["처리업무", "착공 전일까지", "한국산업안전공단\n관할지부", "•지 상높이가 31m 이상인\n건축물 또는 공작물의\n건설·개조 또는 해체\n•깊 이 10.5m 이상인\n굴착공사", "•공 사개요\n•안 전보건관리계획\n•추 락방지계획\n•낙 하 및 비래 예방계획\n•붕 괴방지계획 등", "•공 사개요\n•안 전보건관리계획\n•추 락방지계획\n•낙 하 및 비래 예방계획\n•붕 괴방지계획 등"]]</t>
         </is>
       </c>
-      <c r="S145" s="1" t="inlineStr"/>
-      <c r="T145" s="1" t="inlineStr"/>
-      <c r="U145" s="1" t="inlineStr">
+      <c r="S119" s="1" t="inlineStr"/>
+      <c r="T119" s="1" t="inlineStr"/>
+      <c r="U119" s="1" t="inlineStr">
         <is>
           <t>2.가설공사(1).pdf</t>
         </is>
@@ -15869,7 +13555,7 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>extract_pdf_v6_sentence_level.py</t>
+          <t>extract_pdf_v7_complete_sentences.py</t>
         </is>
       </c>
     </row>
@@ -15917,7 +13603,7 @@
       </c>
       <c r="B6" s="1" t="inlineStr">
         <is>
-          <t>문장 단위 (1 row = 1 sentence)</t>
+          <t>완결 문장 단위 (1 row = 1 complete sentence)</t>
         </is>
       </c>
     </row>
@@ -15929,55 +13615,55 @@
       </c>
       <c r="B7" s="1" t="inlineStr">
         <is>
-          <t>마침표/느낌표/물음표 기준 + 종결형</t>
+          <t>한국어 종결형 기준 (소수점 무시)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>번호 제목</t>
+          <t>토막 필터</t>
         </is>
       </c>
       <c r="B8" s="1" t="inlineStr">
         <is>
-          <t>다음 문장과만 1회 병합</t>
+          <t>불완전 문장/도면라벨/숫자조각 제외</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>Figure Caption</t>
+          <t>검증</t>
         </is>
       </c>
       <c r="B9" s="1" t="inlineStr">
         <is>
-          <t>캡션별 개별 row (1 row = 1 caption)</t>
+          <t>저장 전 완결성 검증</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Table</t>
+          <t>Figure Caption</t>
         </is>
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>표별 개별 row (1 row = 1 table)</t>
+          <t>캡션별 개별 row</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>Subsection 매핑</t>
+          <t>Table</t>
         </is>
       </c>
       <c r="B11" s="1" t="inlineStr">
         <is>
-          <t>page + position + top (보정 포함)</t>
+          <t>표별 개별 row</t>
         </is>
       </c>
     </row>
